--- a/SESTicket/SESTicket/bin/Debug/Reports/xlsx/ticketFrontera.xlsx
+++ b/SESTicket/SESTicket/bin/Debug/Reports/xlsx/ticketFrontera.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SESTicket\app\Reports\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DEVOPS-ADM\source\repos\INNTicket\SESTicket\SESTicket\Reports\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D7BA5F9-AB8A-486A-B5AE-D512AD12E0F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA2AFEB6-EA52-4F50-B138-DC1291F1F4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TICKET" sheetId="3" r:id="rId1"/>
@@ -656,8 +656,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@"/>
   </numFmts>
   <fonts count="22" x14ac:knownFonts="1">
     <font>
@@ -1063,11 +1063,11 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+  <cellXfs count="88">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1089,7 +1089,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1102,8 +1101,7 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1114,7 +1112,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1131,10 +1129,37 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="14" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1147,7 +1172,7 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1187,7 +1212,7 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1249,33 +1274,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1574,26 +1572,25 @@
   <dimension ref="A1:BK1001"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.6640625" style="8" customWidth="1"/>
-    <col min="2" max="2" width="1.109375" style="8" customWidth="1"/>
-    <col min="3" max="4" width="3.109375" style="8" customWidth="1"/>
-    <col min="5" max="6" width="4.33203125" style="8" customWidth="1"/>
-    <col min="7" max="7" width="4.109375" style="8" customWidth="1"/>
-    <col min="8" max="8" width="0.5546875" style="8" customWidth="1"/>
-    <col min="9" max="37" width="3.109375" style="8" customWidth="1"/>
-    <col min="38" max="38" width="12.44140625" style="8" customWidth="1"/>
-    <col min="39" max="39" width="0.44140625" style="8" customWidth="1"/>
-    <col min="40" max="41" width="4.88671875" style="8" customWidth="1"/>
-    <col min="42" max="43" width="5" style="8" customWidth="1"/>
-    <col min="44" max="44" width="2.88671875" style="8" customWidth="1"/>
-    <col min="45" max="45" width="6.88671875" style="8" customWidth="1"/>
-    <col min="46" max="51" width="3.109375" style="8" customWidth="1"/>
-    <col min="52" max="52" width="10" style="8" customWidth="1"/>
-    <col min="53" max="58" width="3.109375" style="8" customWidth="1"/>
-    <col min="59" max="59" width="0.5546875" style="8" customWidth="1"/>
-    <col min="60" max="60" width="1.109375" style="8" customWidth="1"/>
-    <col min="61" max="62" width="3.109375" style="8" customWidth="1"/>
-    <col min="63" max="16384" width="14.44140625" style="8"/>
+    <col min="1" max="1" width="1.6640625" customWidth="1"/>
+    <col min="2" max="2" width="1.109375" customWidth="1"/>
+    <col min="3" max="4" width="3.109375" customWidth="1"/>
+    <col min="5" max="6" width="4.33203125" customWidth="1"/>
+    <col min="7" max="7" width="4.109375" customWidth="1"/>
+    <col min="8" max="8" width="0.5546875" customWidth="1"/>
+    <col min="9" max="37" width="3.109375" customWidth="1"/>
+    <col min="38" max="38" width="12.44140625" customWidth="1"/>
+    <col min="39" max="39" width="0.44140625" customWidth="1"/>
+    <col min="40" max="41" width="4.88671875" customWidth="1"/>
+    <col min="42" max="43" width="5" customWidth="1"/>
+    <col min="44" max="44" width="2.88671875" customWidth="1"/>
+    <col min="45" max="45" width="6.88671875" customWidth="1"/>
+    <col min="46" max="51" width="3.109375" customWidth="1"/>
+    <col min="52" max="52" width="10" customWidth="1"/>
+    <col min="53" max="58" width="3.109375" customWidth="1"/>
+    <col min="59" max="59" width="0.5546875" customWidth="1"/>
+    <col min="60" max="60" width="1.109375" customWidth="1"/>
+    <col min="61" max="62" width="3.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:62" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -1727,69 +1724,69 @@
     <row r="3" spans="1:62" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="23"/>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
-      <c r="J3" s="23"/>
-      <c r="K3" s="23"/>
-      <c r="L3" s="23"/>
-      <c r="M3" s="23"/>
-      <c r="N3" s="29"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="21"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="21"/>
+      <c r="L3" s="21"/>
+      <c r="M3" s="21"/>
+      <c r="N3" s="27"/>
       <c r="O3" s="7"/>
-      <c r="P3" s="75" t="s">
+      <c r="P3" s="82" t="s">
         <v>1</v>
       </c>
-      <c r="Q3" s="23"/>
-      <c r="R3" s="23"/>
-      <c r="S3" s="23"/>
-      <c r="T3" s="23"/>
-      <c r="U3" s="23"/>
-      <c r="V3" s="23"/>
-      <c r="W3" s="23"/>
-      <c r="X3" s="23"/>
-      <c r="Y3" s="23"/>
-      <c r="Z3" s="23"/>
-      <c r="AA3" s="23"/>
-      <c r="AB3" s="23"/>
-      <c r="AC3" s="23"/>
-      <c r="AD3" s="23"/>
-      <c r="AE3" s="23"/>
-      <c r="AF3" s="23"/>
-      <c r="AG3" s="23"/>
-      <c r="AH3" s="23"/>
-      <c r="AI3" s="23"/>
-      <c r="AJ3" s="23"/>
-      <c r="AK3" s="23"/>
-      <c r="AL3" s="23"/>
-      <c r="AM3" s="29"/>
+      <c r="Q3" s="21"/>
+      <c r="R3" s="21"/>
+      <c r="S3" s="21"/>
+      <c r="T3" s="21"/>
+      <c r="U3" s="21"/>
+      <c r="V3" s="21"/>
+      <c r="W3" s="21"/>
+      <c r="X3" s="21"/>
+      <c r="Y3" s="21"/>
+      <c r="Z3" s="21"/>
+      <c r="AA3" s="21"/>
+      <c r="AB3" s="21"/>
+      <c r="AC3" s="21"/>
+      <c r="AD3" s="21"/>
+      <c r="AE3" s="21"/>
+      <c r="AF3" s="21"/>
+      <c r="AG3" s="21"/>
+      <c r="AH3" s="21"/>
+      <c r="AI3" s="21"/>
+      <c r="AJ3" s="21"/>
+      <c r="AK3" s="21"/>
+      <c r="AL3" s="21"/>
+      <c r="AM3" s="27"/>
       <c r="AN3" s="1"/>
-      <c r="AO3" s="22" t="s">
+      <c r="AO3" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="AP3" s="23"/>
-      <c r="AQ3" s="23"/>
-      <c r="AR3" s="23"/>
-      <c r="AS3" s="23"/>
-      <c r="AT3" s="23"/>
-      <c r="AU3" s="23"/>
-      <c r="AV3" s="23"/>
-      <c r="AW3" s="23"/>
-      <c r="AX3" s="23"/>
-      <c r="AY3" s="23"/>
-      <c r="AZ3" s="23"/>
-      <c r="BA3" s="23"/>
-      <c r="BB3" s="23"/>
-      <c r="BC3" s="23"/>
-      <c r="BD3" s="23"/>
-      <c r="BE3" s="23"/>
-      <c r="BF3" s="23"/>
-      <c r="BG3" s="29"/>
+      <c r="AP3" s="21"/>
+      <c r="AQ3" s="21"/>
+      <c r="AR3" s="21"/>
+      <c r="AS3" s="21"/>
+      <c r="AT3" s="21"/>
+      <c r="AU3" s="21"/>
+      <c r="AV3" s="21"/>
+      <c r="AW3" s="21"/>
+      <c r="AX3" s="21"/>
+      <c r="AY3" s="21"/>
+      <c r="AZ3" s="21"/>
+      <c r="BA3" s="21"/>
+      <c r="BB3" s="21"/>
+      <c r="BC3" s="21"/>
+      <c r="BD3" s="21"/>
+      <c r="BE3" s="21"/>
+      <c r="BF3" s="21"/>
+      <c r="BG3" s="27"/>
       <c r="BH3" s="7"/>
       <c r="BI3" s="7"/>
       <c r="BJ3" s="7"/>
@@ -1797,67 +1794,67 @@
     <row r="4" spans="1:62" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
-      <c r="C4" s="79" t="s">
+      <c r="C4" s="86" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="72"/>
-      <c r="E4" s="72"/>
-      <c r="F4" s="72"/>
-      <c r="G4" s="72"/>
-      <c r="H4" s="72"/>
-      <c r="I4" s="72"/>
-      <c r="J4" s="72"/>
-      <c r="K4" s="72"/>
-      <c r="L4" s="72"/>
-      <c r="M4" s="72"/>
-      <c r="N4" s="78"/>
+      <c r="D4" s="79"/>
+      <c r="E4" s="79"/>
+      <c r="F4" s="79"/>
+      <c r="G4" s="79"/>
+      <c r="H4" s="79"/>
+      <c r="I4" s="79"/>
+      <c r="J4" s="79"/>
+      <c r="K4" s="79"/>
+      <c r="L4" s="79"/>
+      <c r="M4" s="79"/>
+      <c r="N4" s="85"/>
       <c r="O4" s="7"/>
-      <c r="P4" s="52"/>
-      <c r="Q4" s="76"/>
-      <c r="R4" s="76"/>
-      <c r="S4" s="76"/>
-      <c r="T4" s="76"/>
-      <c r="U4" s="76"/>
-      <c r="V4" s="76"/>
-      <c r="W4" s="76"/>
-      <c r="X4" s="76"/>
-      <c r="Y4" s="76"/>
-      <c r="Z4" s="76"/>
-      <c r="AA4" s="76"/>
-      <c r="AB4" s="76"/>
-      <c r="AC4" s="76"/>
-      <c r="AD4" s="76"/>
-      <c r="AE4" s="76"/>
-      <c r="AF4" s="76"/>
-      <c r="AG4" s="76"/>
-      <c r="AH4" s="76"/>
-      <c r="AI4" s="76"/>
-      <c r="AJ4" s="76"/>
-      <c r="AK4" s="76"/>
-      <c r="AL4" s="76"/>
-      <c r="AM4" s="53"/>
+      <c r="P4" s="59"/>
+      <c r="Q4" s="83"/>
+      <c r="R4" s="83"/>
+      <c r="S4" s="83"/>
+      <c r="T4" s="83"/>
+      <c r="U4" s="83"/>
+      <c r="V4" s="83"/>
+      <c r="W4" s="83"/>
+      <c r="X4" s="83"/>
+      <c r="Y4" s="83"/>
+      <c r="Z4" s="83"/>
+      <c r="AA4" s="83"/>
+      <c r="AB4" s="83"/>
+      <c r="AC4" s="83"/>
+      <c r="AD4" s="83"/>
+      <c r="AE4" s="83"/>
+      <c r="AF4" s="83"/>
+      <c r="AG4" s="83"/>
+      <c r="AH4" s="83"/>
+      <c r="AI4" s="83"/>
+      <c r="AJ4" s="83"/>
+      <c r="AK4" s="83"/>
+      <c r="AL4" s="83"/>
+      <c r="AM4" s="60"/>
       <c r="AN4" s="1"/>
-      <c r="AO4" s="79" t="s">
+      <c r="AO4" s="86" t="s">
         <v>4</v>
       </c>
-      <c r="AP4" s="72"/>
-      <c r="AQ4" s="72"/>
-      <c r="AR4" s="72"/>
-      <c r="AS4" s="72"/>
-      <c r="AT4" s="72"/>
-      <c r="AU4" s="72"/>
-      <c r="AV4" s="72"/>
-      <c r="AW4" s="72"/>
-      <c r="AX4" s="72"/>
-      <c r="AY4" s="72"/>
-      <c r="AZ4" s="72"/>
-      <c r="BA4" s="72"/>
-      <c r="BB4" s="72"/>
-      <c r="BC4" s="72"/>
-      <c r="BD4" s="72"/>
-      <c r="BE4" s="72"/>
-      <c r="BF4" s="72"/>
-      <c r="BG4" s="78"/>
+      <c r="AP4" s="79"/>
+      <c r="AQ4" s="79"/>
+      <c r="AR4" s="79"/>
+      <c r="AS4" s="79"/>
+      <c r="AT4" s="79"/>
+      <c r="AU4" s="79"/>
+      <c r="AV4" s="79"/>
+      <c r="AW4" s="79"/>
+      <c r="AX4" s="79"/>
+      <c r="AY4" s="79"/>
+      <c r="AZ4" s="79"/>
+      <c r="BA4" s="79"/>
+      <c r="BB4" s="79"/>
+      <c r="BC4" s="79"/>
+      <c r="BD4" s="79"/>
+      <c r="BE4" s="79"/>
+      <c r="BF4" s="79"/>
+      <c r="BG4" s="85"/>
       <c r="BH4" s="7"/>
       <c r="BI4" s="7"/>
       <c r="BJ4" s="7"/>
@@ -1878,30 +1875,30 @@
       <c r="M5" s="1"/>
       <c r="N5" s="7"/>
       <c r="O5" s="7"/>
-      <c r="P5" s="52"/>
-      <c r="Q5" s="76"/>
-      <c r="R5" s="76"/>
-      <c r="S5" s="76"/>
-      <c r="T5" s="76"/>
-      <c r="U5" s="76"/>
-      <c r="V5" s="76"/>
-      <c r="W5" s="76"/>
-      <c r="X5" s="76"/>
-      <c r="Y5" s="76"/>
-      <c r="Z5" s="76"/>
-      <c r="AA5" s="76"/>
-      <c r="AB5" s="76"/>
-      <c r="AC5" s="76"/>
-      <c r="AD5" s="76"/>
-      <c r="AE5" s="76"/>
-      <c r="AF5" s="76"/>
-      <c r="AG5" s="76"/>
-      <c r="AH5" s="76"/>
-      <c r="AI5" s="76"/>
-      <c r="AJ5" s="76"/>
-      <c r="AK5" s="76"/>
-      <c r="AL5" s="76"/>
-      <c r="AM5" s="53"/>
+      <c r="P5" s="59"/>
+      <c r="Q5" s="83"/>
+      <c r="R5" s="83"/>
+      <c r="S5" s="83"/>
+      <c r="T5" s="83"/>
+      <c r="U5" s="83"/>
+      <c r="V5" s="83"/>
+      <c r="W5" s="83"/>
+      <c r="X5" s="83"/>
+      <c r="Y5" s="83"/>
+      <c r="Z5" s="83"/>
+      <c r="AA5" s="83"/>
+      <c r="AB5" s="83"/>
+      <c r="AC5" s="83"/>
+      <c r="AD5" s="83"/>
+      <c r="AE5" s="83"/>
+      <c r="AF5" s="83"/>
+      <c r="AG5" s="83"/>
+      <c r="AH5" s="83"/>
+      <c r="AI5" s="83"/>
+      <c r="AJ5" s="83"/>
+      <c r="AK5" s="83"/>
+      <c r="AL5" s="83"/>
+      <c r="AM5" s="60"/>
       <c r="AN5" s="1"/>
       <c r="AO5" s="1"/>
       <c r="AP5" s="1"/>
@@ -1929,67 +1926,67 @@
     <row r="6" spans="1:62" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="23"/>
-      <c r="H6" s="23"/>
-      <c r="I6" s="23"/>
-      <c r="J6" s="23"/>
-      <c r="K6" s="23"/>
-      <c r="L6" s="23"/>
-      <c r="M6" s="23"/>
-      <c r="N6" s="29"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="21"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="21"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="21"/>
+      <c r="K6" s="21"/>
+      <c r="L6" s="21"/>
+      <c r="M6" s="21"/>
+      <c r="N6" s="27"/>
       <c r="O6" s="7"/>
-      <c r="P6" s="77"/>
-      <c r="Q6" s="72"/>
-      <c r="R6" s="72"/>
-      <c r="S6" s="72"/>
-      <c r="T6" s="72"/>
-      <c r="U6" s="72"/>
-      <c r="V6" s="72"/>
-      <c r="W6" s="72"/>
-      <c r="X6" s="72"/>
-      <c r="Y6" s="72"/>
-      <c r="Z6" s="72"/>
-      <c r="AA6" s="72"/>
-      <c r="AB6" s="72"/>
-      <c r="AC6" s="72"/>
-      <c r="AD6" s="72"/>
-      <c r="AE6" s="72"/>
-      <c r="AF6" s="72"/>
-      <c r="AG6" s="72"/>
-      <c r="AH6" s="72"/>
-      <c r="AI6" s="72"/>
-      <c r="AJ6" s="72"/>
-      <c r="AK6" s="72"/>
-      <c r="AL6" s="72"/>
-      <c r="AM6" s="78"/>
+      <c r="P6" s="84"/>
+      <c r="Q6" s="79"/>
+      <c r="R6" s="79"/>
+      <c r="S6" s="79"/>
+      <c r="T6" s="79"/>
+      <c r="U6" s="79"/>
+      <c r="V6" s="79"/>
+      <c r="W6" s="79"/>
+      <c r="X6" s="79"/>
+      <c r="Y6" s="79"/>
+      <c r="Z6" s="79"/>
+      <c r="AA6" s="79"/>
+      <c r="AB6" s="79"/>
+      <c r="AC6" s="79"/>
+      <c r="AD6" s="79"/>
+      <c r="AE6" s="79"/>
+      <c r="AF6" s="79"/>
+      <c r="AG6" s="79"/>
+      <c r="AH6" s="79"/>
+      <c r="AI6" s="79"/>
+      <c r="AJ6" s="79"/>
+      <c r="AK6" s="79"/>
+      <c r="AL6" s="79"/>
+      <c r="AM6" s="85"/>
       <c r="AN6" s="1"/>
-      <c r="AO6" s="22" t="s">
+      <c r="AO6" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="AP6" s="23"/>
-      <c r="AQ6" s="23"/>
-      <c r="AR6" s="23"/>
-      <c r="AS6" s="23"/>
-      <c r="AT6" s="23"/>
-      <c r="AU6" s="23"/>
-      <c r="AV6" s="23"/>
-      <c r="AW6" s="23"/>
-      <c r="AX6" s="23"/>
-      <c r="AY6" s="23"/>
-      <c r="AZ6" s="23"/>
-      <c r="BA6" s="23"/>
-      <c r="BB6" s="23"/>
-      <c r="BC6" s="23"/>
-      <c r="BD6" s="23"/>
-      <c r="BE6" s="23"/>
-      <c r="BF6" s="23"/>
-      <c r="BG6" s="29"/>
+      <c r="AP6" s="21"/>
+      <c r="AQ6" s="21"/>
+      <c r="AR6" s="21"/>
+      <c r="AS6" s="21"/>
+      <c r="AT6" s="21"/>
+      <c r="AU6" s="21"/>
+      <c r="AV6" s="21"/>
+      <c r="AW6" s="21"/>
+      <c r="AX6" s="21"/>
+      <c r="AY6" s="21"/>
+      <c r="AZ6" s="21"/>
+      <c r="BA6" s="21"/>
+      <c r="BB6" s="21"/>
+      <c r="BC6" s="21"/>
+      <c r="BD6" s="21"/>
+      <c r="BE6" s="21"/>
+      <c r="BF6" s="21"/>
+      <c r="BG6" s="27"/>
       <c r="BH6" s="7"/>
       <c r="BI6" s="7"/>
       <c r="BJ6" s="7"/>
@@ -1997,69 +1994,69 @@
     <row r="7" spans="1:62" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
-      <c r="C7" s="79" t="s">
+      <c r="C7" s="86" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="72"/>
-      <c r="E7" s="72"/>
-      <c r="F7" s="72"/>
-      <c r="G7" s="72"/>
-      <c r="H7" s="72"/>
-      <c r="I7" s="72"/>
-      <c r="J7" s="72"/>
-      <c r="K7" s="72"/>
-      <c r="L7" s="72"/>
-      <c r="M7" s="72"/>
-      <c r="N7" s="78"/>
+      <c r="D7" s="79"/>
+      <c r="E7" s="79"/>
+      <c r="F7" s="79"/>
+      <c r="G7" s="79"/>
+      <c r="H7" s="79"/>
+      <c r="I7" s="79"/>
+      <c r="J7" s="79"/>
+      <c r="K7" s="79"/>
+      <c r="L7" s="79"/>
+      <c r="M7" s="79"/>
+      <c r="N7" s="85"/>
       <c r="O7" s="7"/>
-      <c r="P7" s="80" t="s">
+      <c r="P7" s="87" t="s">
         <v>178</v>
       </c>
-      <c r="Q7" s="16"/>
-      <c r="R7" s="16"/>
-      <c r="S7" s="16"/>
-      <c r="T7" s="16"/>
-      <c r="U7" s="16"/>
-      <c r="V7" s="16"/>
-      <c r="W7" s="16"/>
-      <c r="X7" s="16"/>
-      <c r="Y7" s="16"/>
-      <c r="Z7" s="16"/>
-      <c r="AA7" s="16"/>
-      <c r="AB7" s="16"/>
-      <c r="AC7" s="16"/>
-      <c r="AD7" s="16"/>
-      <c r="AE7" s="16"/>
-      <c r="AF7" s="16"/>
-      <c r="AG7" s="16"/>
-      <c r="AH7" s="16"/>
-      <c r="AI7" s="16"/>
-      <c r="AJ7" s="16"/>
-      <c r="AK7" s="16"/>
-      <c r="AL7" s="16"/>
-      <c r="AM7" s="17"/>
+      <c r="Q7" s="14"/>
+      <c r="R7" s="14"/>
+      <c r="S7" s="14"/>
+      <c r="T7" s="14"/>
+      <c r="U7" s="14"/>
+      <c r="V7" s="14"/>
+      <c r="W7" s="14"/>
+      <c r="X7" s="14"/>
+      <c r="Y7" s="14"/>
+      <c r="Z7" s="14"/>
+      <c r="AA7" s="14"/>
+      <c r="AB7" s="14"/>
+      <c r="AC7" s="14"/>
+      <c r="AD7" s="14"/>
+      <c r="AE7" s="14"/>
+      <c r="AF7" s="14"/>
+      <c r="AG7" s="14"/>
+      <c r="AH7" s="14"/>
+      <c r="AI7" s="14"/>
+      <c r="AJ7" s="14"/>
+      <c r="AK7" s="14"/>
+      <c r="AL7" s="14"/>
+      <c r="AM7" s="15"/>
       <c r="AN7" s="2"/>
-      <c r="AO7" s="79">
+      <c r="AO7" s="86">
         <v>4</v>
       </c>
-      <c r="AP7" s="72"/>
-      <c r="AQ7" s="72"/>
-      <c r="AR7" s="72"/>
-      <c r="AS7" s="72"/>
-      <c r="AT7" s="72"/>
-      <c r="AU7" s="72"/>
-      <c r="AV7" s="72"/>
-      <c r="AW7" s="72"/>
-      <c r="AX7" s="72"/>
-      <c r="AY7" s="72"/>
-      <c r="AZ7" s="72"/>
-      <c r="BA7" s="72"/>
-      <c r="BB7" s="72"/>
-      <c r="BC7" s="72"/>
-      <c r="BD7" s="72"/>
-      <c r="BE7" s="72"/>
-      <c r="BF7" s="72"/>
-      <c r="BG7" s="78"/>
+      <c r="AP7" s="79"/>
+      <c r="AQ7" s="79"/>
+      <c r="AR7" s="79"/>
+      <c r="AS7" s="79"/>
+      <c r="AT7" s="79"/>
+      <c r="AU7" s="79"/>
+      <c r="AV7" s="79"/>
+      <c r="AW7" s="79"/>
+      <c r="AX7" s="79"/>
+      <c r="AY7" s="79"/>
+      <c r="AZ7" s="79"/>
+      <c r="BA7" s="79"/>
+      <c r="BB7" s="79"/>
+      <c r="BC7" s="79"/>
+      <c r="BD7" s="79"/>
+      <c r="BE7" s="79"/>
+      <c r="BF7" s="79"/>
+      <c r="BG7" s="85"/>
       <c r="BH7" s="7"/>
       <c r="BI7" s="7"/>
       <c r="BJ7" s="7"/>
@@ -2105,25 +2102,25 @@
       <c r="AL8" s="7"/>
       <c r="AM8" s="7"/>
       <c r="AN8" s="7"/>
-      <c r="AO8" s="71"/>
-      <c r="AP8" s="72"/>
-      <c r="AQ8" s="72"/>
-      <c r="AR8" s="72"/>
-      <c r="AS8" s="72"/>
-      <c r="AT8" s="72"/>
-      <c r="AU8" s="72"/>
-      <c r="AV8" s="72"/>
-      <c r="AW8" s="72"/>
-      <c r="AX8" s="72"/>
-      <c r="AY8" s="72"/>
-      <c r="AZ8" s="72"/>
-      <c r="BA8" s="72"/>
-      <c r="BB8" s="72"/>
-      <c r="BC8" s="72"/>
-      <c r="BD8" s="72"/>
-      <c r="BE8" s="72"/>
-      <c r="BF8" s="72"/>
-      <c r="BG8" s="72"/>
+      <c r="AO8" s="78"/>
+      <c r="AP8" s="79"/>
+      <c r="AQ8" s="79"/>
+      <c r="AR8" s="79"/>
+      <c r="AS8" s="79"/>
+      <c r="AT8" s="79"/>
+      <c r="AU8" s="79"/>
+      <c r="AV8" s="79"/>
+      <c r="AW8" s="79"/>
+      <c r="AX8" s="79"/>
+      <c r="AY8" s="79"/>
+      <c r="AZ8" s="79"/>
+      <c r="BA8" s="79"/>
+      <c r="BB8" s="79"/>
+      <c r="BC8" s="79"/>
+      <c r="BD8" s="79"/>
+      <c r="BE8" s="79"/>
+      <c r="BF8" s="79"/>
+      <c r="BG8" s="79"/>
       <c r="BH8" s="7"/>
       <c r="BI8" s="7"/>
       <c r="BJ8" s="7"/>
@@ -2131,71 +2128,71 @@
     <row r="9" spans="1:62" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
-      <c r="C9" s="73" t="s">
+      <c r="C9" s="80" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="46"/>
-      <c r="E9" s="46"/>
-      <c r="F9" s="46"/>
-      <c r="G9" s="46"/>
-      <c r="H9" s="46"/>
-      <c r="I9" s="46"/>
-      <c r="J9" s="62" t="s">
+      <c r="D9" s="53"/>
+      <c r="E9" s="53"/>
+      <c r="F9" s="53"/>
+      <c r="G9" s="53"/>
+      <c r="H9" s="53"/>
+      <c r="I9" s="53"/>
+      <c r="J9" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="K9" s="43"/>
-      <c r="L9" s="43"/>
-      <c r="M9" s="43"/>
-      <c r="N9" s="43"/>
-      <c r="O9" s="43"/>
-      <c r="P9" s="43"/>
-      <c r="Q9" s="43"/>
-      <c r="R9" s="43"/>
-      <c r="S9" s="44"/>
-      <c r="T9" s="59" t="s">
+      <c r="K9" s="50"/>
+      <c r="L9" s="50"/>
+      <c r="M9" s="50"/>
+      <c r="N9" s="50"/>
+      <c r="O9" s="50"/>
+      <c r="P9" s="50"/>
+      <c r="Q9" s="50"/>
+      <c r="R9" s="50"/>
+      <c r="S9" s="51"/>
+      <c r="T9" s="66" t="s">
         <v>9</v>
       </c>
-      <c r="U9" s="43"/>
-      <c r="V9" s="43"/>
-      <c r="W9" s="43"/>
-      <c r="X9" s="43"/>
-      <c r="Y9" s="43"/>
-      <c r="Z9" s="43"/>
-      <c r="AA9" s="44"/>
-      <c r="AB9" s="62" t="s">
+      <c r="U9" s="50"/>
+      <c r="V9" s="50"/>
+      <c r="W9" s="50"/>
+      <c r="X9" s="50"/>
+      <c r="Y9" s="50"/>
+      <c r="Z9" s="50"/>
+      <c r="AA9" s="51"/>
+      <c r="AB9" s="69" t="s">
         <v>41</v>
       </c>
-      <c r="AC9" s="43"/>
-      <c r="AD9" s="43"/>
-      <c r="AE9" s="43"/>
-      <c r="AF9" s="43"/>
-      <c r="AG9" s="43"/>
-      <c r="AH9" s="43"/>
-      <c r="AI9" s="43"/>
-      <c r="AJ9" s="43"/>
-      <c r="AK9" s="43"/>
-      <c r="AL9" s="43"/>
-      <c r="AM9" s="44"/>
-      <c r="AN9" s="9"/>
-      <c r="AO9" s="74"/>
-      <c r="AP9" s="43"/>
-      <c r="AQ9" s="43"/>
-      <c r="AR9" s="43"/>
-      <c r="AS9" s="43"/>
-      <c r="AT9" s="43"/>
-      <c r="AU9" s="43"/>
-      <c r="AV9" s="43"/>
-      <c r="AW9" s="43"/>
-      <c r="AX9" s="43"/>
-      <c r="AY9" s="43"/>
-      <c r="AZ9" s="43"/>
-      <c r="BA9" s="43"/>
-      <c r="BB9" s="43"/>
-      <c r="BC9" s="43"/>
-      <c r="BD9" s="43"/>
-      <c r="BE9" s="43"/>
-      <c r="BF9" s="43"/>
-      <c r="BG9" s="44"/>
+      <c r="AC9" s="50"/>
+      <c r="AD9" s="50"/>
+      <c r="AE9" s="50"/>
+      <c r="AF9" s="50"/>
+      <c r="AG9" s="50"/>
+      <c r="AH9" s="50"/>
+      <c r="AI9" s="50"/>
+      <c r="AJ9" s="50"/>
+      <c r="AK9" s="50"/>
+      <c r="AL9" s="50"/>
+      <c r="AM9" s="51"/>
+      <c r="AN9" s="8"/>
+      <c r="AO9" s="81"/>
+      <c r="AP9" s="50"/>
+      <c r="AQ9" s="50"/>
+      <c r="AR9" s="50"/>
+      <c r="AS9" s="50"/>
+      <c r="AT9" s="50"/>
+      <c r="AU9" s="50"/>
+      <c r="AV9" s="50"/>
+      <c r="AW9" s="50"/>
+      <c r="AX9" s="50"/>
+      <c r="AY9" s="50"/>
+      <c r="AZ9" s="50"/>
+      <c r="BA9" s="50"/>
+      <c r="BB9" s="50"/>
+      <c r="BC9" s="50"/>
+      <c r="BD9" s="50"/>
+      <c r="BE9" s="50"/>
+      <c r="BF9" s="50"/>
+      <c r="BG9" s="51"/>
       <c r="BH9" s="7"/>
       <c r="BI9" s="7"/>
       <c r="BJ9" s="7"/>
@@ -2203,63 +2200,63 @@
     <row r="10" spans="1:62" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
-      <c r="C10" s="67"/>
-      <c r="D10" s="43"/>
-      <c r="E10" s="43"/>
-      <c r="F10" s="43"/>
-      <c r="G10" s="43"/>
-      <c r="H10" s="43"/>
-      <c r="I10" s="43"/>
-      <c r="J10" s="67"/>
-      <c r="K10" s="43"/>
-      <c r="L10" s="43"/>
-      <c r="M10" s="43"/>
-      <c r="N10" s="43"/>
-      <c r="O10" s="43"/>
-      <c r="P10" s="43"/>
-      <c r="Q10" s="43"/>
-      <c r="R10" s="43"/>
-      <c r="S10" s="43"/>
-      <c r="T10" s="68"/>
-      <c r="U10" s="69"/>
-      <c r="V10" s="69"/>
-      <c r="W10" s="69"/>
-      <c r="X10" s="69"/>
-      <c r="Y10" s="69"/>
-      <c r="Z10" s="69"/>
-      <c r="AA10" s="68"/>
-      <c r="AB10" s="69"/>
-      <c r="AC10" s="69"/>
-      <c r="AD10" s="69"/>
-      <c r="AE10" s="69"/>
-      <c r="AF10" s="69"/>
-      <c r="AG10" s="69"/>
-      <c r="AH10" s="69"/>
-      <c r="AI10" s="69"/>
-      <c r="AJ10" s="69"/>
-      <c r="AK10" s="69"/>
-      <c r="AL10" s="69"/>
-      <c r="AM10" s="69"/>
-      <c r="AN10" s="9"/>
-      <c r="AO10" s="70"/>
-      <c r="AP10" s="43"/>
-      <c r="AQ10" s="43"/>
-      <c r="AR10" s="43"/>
-      <c r="AS10" s="43"/>
-      <c r="AT10" s="43"/>
-      <c r="AU10" s="43"/>
-      <c r="AV10" s="43"/>
-      <c r="AW10" s="43"/>
-      <c r="AX10" s="43"/>
-      <c r="AY10" s="43"/>
-      <c r="AZ10" s="43"/>
-      <c r="BA10" s="43"/>
-      <c r="BB10" s="43"/>
-      <c r="BC10" s="43"/>
-      <c r="BD10" s="43"/>
-      <c r="BE10" s="43"/>
-      <c r="BF10" s="43"/>
-      <c r="BG10" s="43"/>
+      <c r="C10" s="74"/>
+      <c r="D10" s="50"/>
+      <c r="E10" s="50"/>
+      <c r="F10" s="50"/>
+      <c r="G10" s="50"/>
+      <c r="H10" s="50"/>
+      <c r="I10" s="50"/>
+      <c r="J10" s="74"/>
+      <c r="K10" s="50"/>
+      <c r="L10" s="50"/>
+      <c r="M10" s="50"/>
+      <c r="N10" s="50"/>
+      <c r="O10" s="50"/>
+      <c r="P10" s="50"/>
+      <c r="Q10" s="50"/>
+      <c r="R10" s="50"/>
+      <c r="S10" s="50"/>
+      <c r="T10" s="75"/>
+      <c r="U10" s="76"/>
+      <c r="V10" s="76"/>
+      <c r="W10" s="76"/>
+      <c r="X10" s="76"/>
+      <c r="Y10" s="76"/>
+      <c r="Z10" s="76"/>
+      <c r="AA10" s="75"/>
+      <c r="AB10" s="76"/>
+      <c r="AC10" s="76"/>
+      <c r="AD10" s="76"/>
+      <c r="AE10" s="76"/>
+      <c r="AF10" s="76"/>
+      <c r="AG10" s="76"/>
+      <c r="AH10" s="76"/>
+      <c r="AI10" s="76"/>
+      <c r="AJ10" s="76"/>
+      <c r="AK10" s="76"/>
+      <c r="AL10" s="76"/>
+      <c r="AM10" s="76"/>
+      <c r="AN10" s="8"/>
+      <c r="AO10" s="77"/>
+      <c r="AP10" s="50"/>
+      <c r="AQ10" s="50"/>
+      <c r="AR10" s="50"/>
+      <c r="AS10" s="50"/>
+      <c r="AT10" s="50"/>
+      <c r="AU10" s="50"/>
+      <c r="AV10" s="50"/>
+      <c r="AW10" s="50"/>
+      <c r="AX10" s="50"/>
+      <c r="AY10" s="50"/>
+      <c r="AZ10" s="50"/>
+      <c r="BA10" s="50"/>
+      <c r="BB10" s="50"/>
+      <c r="BC10" s="50"/>
+      <c r="BD10" s="50"/>
+      <c r="BE10" s="50"/>
+      <c r="BF10" s="50"/>
+      <c r="BG10" s="50"/>
       <c r="BH10" s="7"/>
       <c r="BI10" s="7"/>
       <c r="BJ10" s="7"/>
@@ -2267,71 +2264,71 @@
     <row r="11" spans="1:62" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
-      <c r="C11" s="59" t="s">
+      <c r="C11" s="66" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="43"/>
-      <c r="E11" s="43"/>
-      <c r="F11" s="43"/>
-      <c r="G11" s="43"/>
-      <c r="H11" s="43"/>
-      <c r="I11" s="43"/>
-      <c r="J11" s="43"/>
-      <c r="K11" s="43"/>
-      <c r="L11" s="43"/>
-      <c r="M11" s="43"/>
-      <c r="N11" s="43"/>
-      <c r="O11" s="43"/>
-      <c r="P11" s="43"/>
-      <c r="Q11" s="43"/>
-      <c r="R11" s="43"/>
-      <c r="S11" s="44"/>
-      <c r="T11" s="59" t="s">
+      <c r="D11" s="50"/>
+      <c r="E11" s="50"/>
+      <c r="F11" s="50"/>
+      <c r="G11" s="50"/>
+      <c r="H11" s="50"/>
+      <c r="I11" s="50"/>
+      <c r="J11" s="50"/>
+      <c r="K11" s="50"/>
+      <c r="L11" s="50"/>
+      <c r="M11" s="50"/>
+      <c r="N11" s="50"/>
+      <c r="O11" s="50"/>
+      <c r="P11" s="50"/>
+      <c r="Q11" s="50"/>
+      <c r="R11" s="50"/>
+      <c r="S11" s="51"/>
+      <c r="T11" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="U11" s="43"/>
-      <c r="V11" s="43"/>
-      <c r="W11" s="43"/>
-      <c r="X11" s="43"/>
-      <c r="Y11" s="43"/>
-      <c r="Z11" s="43"/>
-      <c r="AA11" s="43"/>
-      <c r="AB11" s="43"/>
-      <c r="AC11" s="44"/>
-      <c r="AD11" s="59" t="s">
+      <c r="U11" s="50"/>
+      <c r="V11" s="50"/>
+      <c r="W11" s="50"/>
+      <c r="X11" s="50"/>
+      <c r="Y11" s="50"/>
+      <c r="Z11" s="50"/>
+      <c r="AA11" s="50"/>
+      <c r="AB11" s="50"/>
+      <c r="AC11" s="51"/>
+      <c r="AD11" s="66" t="s">
         <v>12</v>
       </c>
-      <c r="AE11" s="43"/>
-      <c r="AF11" s="43"/>
-      <c r="AG11" s="43"/>
-      <c r="AH11" s="43"/>
-      <c r="AI11" s="43"/>
-      <c r="AJ11" s="43"/>
-      <c r="AK11" s="43"/>
-      <c r="AL11" s="43"/>
-      <c r="AM11" s="44"/>
-      <c r="AN11" s="9"/>
-      <c r="AO11" s="59" t="s">
+      <c r="AE11" s="50"/>
+      <c r="AF11" s="50"/>
+      <c r="AG11" s="50"/>
+      <c r="AH11" s="50"/>
+      <c r="AI11" s="50"/>
+      <c r="AJ11" s="50"/>
+      <c r="AK11" s="50"/>
+      <c r="AL11" s="50"/>
+      <c r="AM11" s="51"/>
+      <c r="AN11" s="8"/>
+      <c r="AO11" s="66" t="s">
         <v>13</v>
       </c>
-      <c r="AP11" s="43"/>
-      <c r="AQ11" s="43"/>
-      <c r="AR11" s="43"/>
-      <c r="AS11" s="43"/>
-      <c r="AT11" s="43"/>
-      <c r="AU11" s="43"/>
-      <c r="AV11" s="43"/>
-      <c r="AW11" s="43"/>
-      <c r="AX11" s="43"/>
-      <c r="AY11" s="43"/>
-      <c r="AZ11" s="43"/>
-      <c r="BA11" s="43"/>
-      <c r="BB11" s="43"/>
-      <c r="BC11" s="43"/>
-      <c r="BD11" s="43"/>
-      <c r="BE11" s="43"/>
-      <c r="BF11" s="43"/>
-      <c r="BG11" s="44"/>
+      <c r="AP11" s="50"/>
+      <c r="AQ11" s="50"/>
+      <c r="AR11" s="50"/>
+      <c r="AS11" s="50"/>
+      <c r="AT11" s="50"/>
+      <c r="AU11" s="50"/>
+      <c r="AV11" s="50"/>
+      <c r="AW11" s="50"/>
+      <c r="AX11" s="50"/>
+      <c r="AY11" s="50"/>
+      <c r="AZ11" s="50"/>
+      <c r="BA11" s="50"/>
+      <c r="BB11" s="50"/>
+      <c r="BC11" s="50"/>
+      <c r="BD11" s="50"/>
+      <c r="BE11" s="50"/>
+      <c r="BF11" s="50"/>
+      <c r="BG11" s="51"/>
       <c r="BH11" s="7"/>
       <c r="BI11" s="7"/>
       <c r="BJ11" s="7"/>
@@ -2339,69 +2336,69 @@
     <row r="12" spans="1:62" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
-      <c r="C12" s="61" t="s">
+      <c r="C12" s="68" t="s">
         <v>180</v>
       </c>
-      <c r="D12" s="43"/>
-      <c r="E12" s="43"/>
-      <c r="F12" s="43"/>
-      <c r="G12" s="43"/>
-      <c r="H12" s="43"/>
-      <c r="I12" s="43"/>
-      <c r="J12" s="43"/>
-      <c r="K12" s="43"/>
-      <c r="L12" s="43"/>
-      <c r="M12" s="43"/>
-      <c r="N12" s="43"/>
-      <c r="O12" s="43"/>
-      <c r="P12" s="43"/>
-      <c r="Q12" s="43"/>
-      <c r="R12" s="43"/>
-      <c r="S12" s="44"/>
-      <c r="T12" s="62" t="s">
+      <c r="D12" s="50"/>
+      <c r="E12" s="50"/>
+      <c r="F12" s="50"/>
+      <c r="G12" s="50"/>
+      <c r="H12" s="50"/>
+      <c r="I12" s="50"/>
+      <c r="J12" s="50"/>
+      <c r="K12" s="50"/>
+      <c r="L12" s="50"/>
+      <c r="M12" s="50"/>
+      <c r="N12" s="50"/>
+      <c r="O12" s="50"/>
+      <c r="P12" s="50"/>
+      <c r="Q12" s="50"/>
+      <c r="R12" s="50"/>
+      <c r="S12" s="51"/>
+      <c r="T12" s="69" t="s">
         <v>167</v>
       </c>
-      <c r="U12" s="43"/>
-      <c r="V12" s="43"/>
-      <c r="W12" s="43"/>
-      <c r="X12" s="43"/>
-      <c r="Y12" s="43"/>
-      <c r="Z12" s="43"/>
-      <c r="AA12" s="43"/>
-      <c r="AB12" s="43"/>
-      <c r="AC12" s="44"/>
-      <c r="AD12" s="64" t="s">
+      <c r="U12" s="50"/>
+      <c r="V12" s="50"/>
+      <c r="W12" s="50"/>
+      <c r="X12" s="50"/>
+      <c r="Y12" s="50"/>
+      <c r="Z12" s="50"/>
+      <c r="AA12" s="50"/>
+      <c r="AB12" s="50"/>
+      <c r="AC12" s="51"/>
+      <c r="AD12" s="71" t="s">
         <v>166</v>
       </c>
-      <c r="AE12" s="65"/>
-      <c r="AF12" s="65"/>
-      <c r="AG12" s="65"/>
-      <c r="AH12" s="65"/>
-      <c r="AI12" s="65"/>
-      <c r="AJ12" s="65"/>
-      <c r="AK12" s="65"/>
-      <c r="AL12" s="65"/>
-      <c r="AM12" s="66"/>
-      <c r="AN12" s="9"/>
-      <c r="AO12" s="60"/>
-      <c r="AP12" s="49"/>
-      <c r="AQ12" s="49"/>
-      <c r="AR12" s="49"/>
-      <c r="AS12" s="49"/>
-      <c r="AT12" s="49"/>
-      <c r="AU12" s="49"/>
-      <c r="AV12" s="49"/>
-      <c r="AW12" s="49"/>
-      <c r="AX12" s="49"/>
-      <c r="AY12" s="49"/>
-      <c r="AZ12" s="49"/>
-      <c r="BA12" s="49"/>
-      <c r="BB12" s="49"/>
-      <c r="BC12" s="49"/>
-      <c r="BD12" s="49"/>
-      <c r="BE12" s="49"/>
-      <c r="BF12" s="49"/>
-      <c r="BG12" s="50"/>
+      <c r="AE12" s="72"/>
+      <c r="AF12" s="72"/>
+      <c r="AG12" s="72"/>
+      <c r="AH12" s="72"/>
+      <c r="AI12" s="72"/>
+      <c r="AJ12" s="72"/>
+      <c r="AK12" s="72"/>
+      <c r="AL12" s="72"/>
+      <c r="AM12" s="73"/>
+      <c r="AN12" s="8"/>
+      <c r="AO12" s="67"/>
+      <c r="AP12" s="56"/>
+      <c r="AQ12" s="56"/>
+      <c r="AR12" s="56"/>
+      <c r="AS12" s="56"/>
+      <c r="AT12" s="56"/>
+      <c r="AU12" s="56"/>
+      <c r="AV12" s="56"/>
+      <c r="AW12" s="56"/>
+      <c r="AX12" s="56"/>
+      <c r="AY12" s="56"/>
+      <c r="AZ12" s="56"/>
+      <c r="BA12" s="56"/>
+      <c r="BB12" s="56"/>
+      <c r="BC12" s="56"/>
+      <c r="BD12" s="56"/>
+      <c r="BE12" s="56"/>
+      <c r="BF12" s="56"/>
+      <c r="BG12" s="57"/>
       <c r="BH12" s="7"/>
       <c r="BI12" s="7"/>
       <c r="BJ12" s="7"/>
@@ -2409,63 +2406,63 @@
     <row r="13" spans="1:62" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7"/>
       <c r="B13" s="7"/>
-      <c r="C13" s="67"/>
-      <c r="D13" s="43"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="43"/>
-      <c r="G13" s="43"/>
-      <c r="H13" s="43"/>
-      <c r="I13" s="43"/>
-      <c r="J13" s="67"/>
-      <c r="K13" s="43"/>
-      <c r="L13" s="43"/>
-      <c r="M13" s="43"/>
-      <c r="N13" s="43"/>
-      <c r="O13" s="43"/>
-      <c r="P13" s="43"/>
-      <c r="Q13" s="43"/>
-      <c r="R13" s="43"/>
-      <c r="S13" s="43"/>
-      <c r="T13" s="68"/>
-      <c r="U13" s="69"/>
-      <c r="V13" s="69"/>
-      <c r="W13" s="69"/>
-      <c r="X13" s="69"/>
-      <c r="Y13" s="69"/>
-      <c r="Z13" s="69"/>
-      <c r="AA13" s="68"/>
-      <c r="AB13" s="69"/>
-      <c r="AC13" s="69"/>
-      <c r="AD13" s="69"/>
-      <c r="AE13" s="69"/>
-      <c r="AF13" s="69"/>
-      <c r="AG13" s="69"/>
-      <c r="AH13" s="69"/>
-      <c r="AI13" s="69"/>
-      <c r="AJ13" s="69"/>
-      <c r="AK13" s="69"/>
-      <c r="AL13" s="69"/>
-      <c r="AM13" s="69"/>
-      <c r="AN13" s="9"/>
-      <c r="AO13" s="70"/>
-      <c r="AP13" s="43"/>
-      <c r="AQ13" s="43"/>
-      <c r="AR13" s="43"/>
-      <c r="AS13" s="43"/>
-      <c r="AT13" s="43"/>
-      <c r="AU13" s="43"/>
-      <c r="AV13" s="43"/>
-      <c r="AW13" s="43"/>
-      <c r="AX13" s="43"/>
-      <c r="AY13" s="43"/>
-      <c r="AZ13" s="43"/>
-      <c r="BA13" s="43"/>
-      <c r="BB13" s="43"/>
-      <c r="BC13" s="43"/>
-      <c r="BD13" s="43"/>
-      <c r="BE13" s="43"/>
-      <c r="BF13" s="43"/>
-      <c r="BG13" s="43"/>
+      <c r="C13" s="74"/>
+      <c r="D13" s="50"/>
+      <c r="E13" s="50"/>
+      <c r="F13" s="50"/>
+      <c r="G13" s="50"/>
+      <c r="H13" s="50"/>
+      <c r="I13" s="50"/>
+      <c r="J13" s="74"/>
+      <c r="K13" s="50"/>
+      <c r="L13" s="50"/>
+      <c r="M13" s="50"/>
+      <c r="N13" s="50"/>
+      <c r="O13" s="50"/>
+      <c r="P13" s="50"/>
+      <c r="Q13" s="50"/>
+      <c r="R13" s="50"/>
+      <c r="S13" s="50"/>
+      <c r="T13" s="75"/>
+      <c r="U13" s="76"/>
+      <c r="V13" s="76"/>
+      <c r="W13" s="76"/>
+      <c r="X13" s="76"/>
+      <c r="Y13" s="76"/>
+      <c r="Z13" s="76"/>
+      <c r="AA13" s="75"/>
+      <c r="AB13" s="76"/>
+      <c r="AC13" s="76"/>
+      <c r="AD13" s="76"/>
+      <c r="AE13" s="76"/>
+      <c r="AF13" s="76"/>
+      <c r="AG13" s="76"/>
+      <c r="AH13" s="76"/>
+      <c r="AI13" s="76"/>
+      <c r="AJ13" s="76"/>
+      <c r="AK13" s="76"/>
+      <c r="AL13" s="76"/>
+      <c r="AM13" s="76"/>
+      <c r="AN13" s="8"/>
+      <c r="AO13" s="77"/>
+      <c r="AP13" s="50"/>
+      <c r="AQ13" s="50"/>
+      <c r="AR13" s="50"/>
+      <c r="AS13" s="50"/>
+      <c r="AT13" s="50"/>
+      <c r="AU13" s="50"/>
+      <c r="AV13" s="50"/>
+      <c r="AW13" s="50"/>
+      <c r="AX13" s="50"/>
+      <c r="AY13" s="50"/>
+      <c r="AZ13" s="50"/>
+      <c r="BA13" s="50"/>
+      <c r="BB13" s="50"/>
+      <c r="BC13" s="50"/>
+      <c r="BD13" s="50"/>
+      <c r="BE13" s="50"/>
+      <c r="BF13" s="50"/>
+      <c r="BG13" s="50"/>
       <c r="BH13" s="7"/>
       <c r="BI13" s="7"/>
       <c r="BJ13" s="7"/>
@@ -2473,71 +2470,71 @@
     <row r="14" spans="1:62" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
-      <c r="C14" s="59" t="s">
+      <c r="C14" s="66" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="43"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="43"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="43"/>
-      <c r="I14" s="43"/>
-      <c r="J14" s="43"/>
-      <c r="K14" s="43"/>
-      <c r="L14" s="43"/>
-      <c r="M14" s="43"/>
-      <c r="N14" s="43"/>
-      <c r="O14" s="43"/>
-      <c r="P14" s="43"/>
-      <c r="Q14" s="43"/>
-      <c r="R14" s="43"/>
-      <c r="S14" s="44"/>
-      <c r="T14" s="59" t="s">
+      <c r="D14" s="50"/>
+      <c r="E14" s="50"/>
+      <c r="F14" s="50"/>
+      <c r="G14" s="50"/>
+      <c r="H14" s="50"/>
+      <c r="I14" s="50"/>
+      <c r="J14" s="50"/>
+      <c r="K14" s="50"/>
+      <c r="L14" s="50"/>
+      <c r="M14" s="50"/>
+      <c r="N14" s="50"/>
+      <c r="O14" s="50"/>
+      <c r="P14" s="50"/>
+      <c r="Q14" s="50"/>
+      <c r="R14" s="50"/>
+      <c r="S14" s="51"/>
+      <c r="T14" s="66" t="s">
         <v>15</v>
       </c>
-      <c r="U14" s="43"/>
-      <c r="V14" s="43"/>
-      <c r="W14" s="43"/>
-      <c r="X14" s="43"/>
-      <c r="Y14" s="43"/>
-      <c r="Z14" s="43"/>
-      <c r="AA14" s="43"/>
-      <c r="AB14" s="43"/>
-      <c r="AC14" s="44"/>
-      <c r="AD14" s="59" t="s">
+      <c r="U14" s="50"/>
+      <c r="V14" s="50"/>
+      <c r="W14" s="50"/>
+      <c r="X14" s="50"/>
+      <c r="Y14" s="50"/>
+      <c r="Z14" s="50"/>
+      <c r="AA14" s="50"/>
+      <c r="AB14" s="50"/>
+      <c r="AC14" s="51"/>
+      <c r="AD14" s="66" t="s">
         <v>16</v>
       </c>
-      <c r="AE14" s="43"/>
-      <c r="AF14" s="43"/>
-      <c r="AG14" s="43"/>
-      <c r="AH14" s="43"/>
-      <c r="AI14" s="43"/>
-      <c r="AJ14" s="43"/>
-      <c r="AK14" s="43"/>
-      <c r="AL14" s="43"/>
-      <c r="AM14" s="44"/>
-      <c r="AN14" s="9"/>
-      <c r="AO14" s="59" t="s">
+      <c r="AE14" s="50"/>
+      <c r="AF14" s="50"/>
+      <c r="AG14" s="50"/>
+      <c r="AH14" s="50"/>
+      <c r="AI14" s="50"/>
+      <c r="AJ14" s="50"/>
+      <c r="AK14" s="50"/>
+      <c r="AL14" s="50"/>
+      <c r="AM14" s="51"/>
+      <c r="AN14" s="8"/>
+      <c r="AO14" s="66" t="s">
         <v>17</v>
       </c>
-      <c r="AP14" s="43"/>
-      <c r="AQ14" s="43"/>
-      <c r="AR14" s="43"/>
-      <c r="AS14" s="43"/>
-      <c r="AT14" s="43"/>
-      <c r="AU14" s="43"/>
-      <c r="AV14" s="43"/>
-      <c r="AW14" s="43"/>
-      <c r="AX14" s="43"/>
-      <c r="AY14" s="43"/>
-      <c r="AZ14" s="43"/>
-      <c r="BA14" s="43"/>
-      <c r="BB14" s="43"/>
-      <c r="BC14" s="43"/>
-      <c r="BD14" s="43"/>
-      <c r="BE14" s="43"/>
-      <c r="BF14" s="43"/>
-      <c r="BG14" s="44"/>
+      <c r="AP14" s="50"/>
+      <c r="AQ14" s="50"/>
+      <c r="AR14" s="50"/>
+      <c r="AS14" s="50"/>
+      <c r="AT14" s="50"/>
+      <c r="AU14" s="50"/>
+      <c r="AV14" s="50"/>
+      <c r="AW14" s="50"/>
+      <c r="AX14" s="50"/>
+      <c r="AY14" s="50"/>
+      <c r="AZ14" s="50"/>
+      <c r="BA14" s="50"/>
+      <c r="BB14" s="50"/>
+      <c r="BC14" s="50"/>
+      <c r="BD14" s="50"/>
+      <c r="BE14" s="50"/>
+      <c r="BF14" s="50"/>
+      <c r="BG14" s="51"/>
       <c r="BH14" s="7"/>
       <c r="BI14" s="7"/>
       <c r="BJ14" s="7"/>
@@ -2545,71 +2542,71 @@
     <row r="15" spans="1:62" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7"/>
       <c r="B15" s="7"/>
-      <c r="C15" s="61" t="s">
+      <c r="C15" s="68" t="s">
         <v>168</v>
       </c>
-      <c r="D15" s="43"/>
-      <c r="E15" s="43"/>
-      <c r="F15" s="43"/>
-      <c r="G15" s="43"/>
-      <c r="H15" s="43"/>
-      <c r="I15" s="43"/>
-      <c r="J15" s="43"/>
-      <c r="K15" s="43"/>
-      <c r="L15" s="43"/>
-      <c r="M15" s="43"/>
-      <c r="N15" s="43"/>
-      <c r="O15" s="43"/>
-      <c r="P15" s="43"/>
-      <c r="Q15" s="43"/>
-      <c r="R15" s="43"/>
-      <c r="S15" s="44"/>
-      <c r="T15" s="62" t="s">
+      <c r="D15" s="50"/>
+      <c r="E15" s="50"/>
+      <c r="F15" s="50"/>
+      <c r="G15" s="50"/>
+      <c r="H15" s="50"/>
+      <c r="I15" s="50"/>
+      <c r="J15" s="50"/>
+      <c r="K15" s="50"/>
+      <c r="L15" s="50"/>
+      <c r="M15" s="50"/>
+      <c r="N15" s="50"/>
+      <c r="O15" s="50"/>
+      <c r="P15" s="50"/>
+      <c r="Q15" s="50"/>
+      <c r="R15" s="50"/>
+      <c r="S15" s="51"/>
+      <c r="T15" s="69" t="s">
         <v>177</v>
       </c>
-      <c r="U15" s="43"/>
-      <c r="V15" s="43"/>
-      <c r="W15" s="43"/>
-      <c r="X15" s="43"/>
-      <c r="Y15" s="43"/>
-      <c r="Z15" s="43"/>
-      <c r="AA15" s="43"/>
-      <c r="AB15" s="43"/>
-      <c r="AC15" s="44"/>
-      <c r="AD15" s="63" t="s">
+      <c r="U15" s="50"/>
+      <c r="V15" s="50"/>
+      <c r="W15" s="50"/>
+      <c r="X15" s="50"/>
+      <c r="Y15" s="50"/>
+      <c r="Z15" s="50"/>
+      <c r="AA15" s="50"/>
+      <c r="AB15" s="50"/>
+      <c r="AC15" s="51"/>
+      <c r="AD15" s="70" t="s">
         <v>176</v>
       </c>
-      <c r="AE15" s="43"/>
-      <c r="AF15" s="43"/>
-      <c r="AG15" s="43"/>
-      <c r="AH15" s="43"/>
-      <c r="AI15" s="43"/>
-      <c r="AJ15" s="43"/>
-      <c r="AK15" s="43"/>
-      <c r="AL15" s="43"/>
-      <c r="AM15" s="44"/>
-      <c r="AN15" s="9"/>
-      <c r="AO15" s="60" t="s">
+      <c r="AE15" s="50"/>
+      <c r="AF15" s="50"/>
+      <c r="AG15" s="50"/>
+      <c r="AH15" s="50"/>
+      <c r="AI15" s="50"/>
+      <c r="AJ15" s="50"/>
+      <c r="AK15" s="50"/>
+      <c r="AL15" s="50"/>
+      <c r="AM15" s="51"/>
+      <c r="AN15" s="8"/>
+      <c r="AO15" s="67" t="s">
         <v>171</v>
       </c>
-      <c r="AP15" s="49"/>
-      <c r="AQ15" s="49"/>
-      <c r="AR15" s="49"/>
-      <c r="AS15" s="49"/>
-      <c r="AT15" s="49"/>
-      <c r="AU15" s="49"/>
-      <c r="AV15" s="49"/>
-      <c r="AW15" s="49"/>
-      <c r="AX15" s="49"/>
-      <c r="AY15" s="49"/>
-      <c r="AZ15" s="49"/>
-      <c r="BA15" s="49"/>
-      <c r="BB15" s="49"/>
-      <c r="BC15" s="49"/>
-      <c r="BD15" s="49"/>
-      <c r="BE15" s="49"/>
-      <c r="BF15" s="49"/>
-      <c r="BG15" s="50"/>
+      <c r="AP15" s="56"/>
+      <c r="AQ15" s="56"/>
+      <c r="AR15" s="56"/>
+      <c r="AS15" s="56"/>
+      <c r="AT15" s="56"/>
+      <c r="AU15" s="56"/>
+      <c r="AV15" s="56"/>
+      <c r="AW15" s="56"/>
+      <c r="AX15" s="56"/>
+      <c r="AY15" s="56"/>
+      <c r="AZ15" s="56"/>
+      <c r="BA15" s="56"/>
+      <c r="BB15" s="56"/>
+      <c r="BC15" s="56"/>
+      <c r="BD15" s="56"/>
+      <c r="BE15" s="56"/>
+      <c r="BF15" s="56"/>
+      <c r="BG15" s="57"/>
       <c r="BH15" s="7"/>
       <c r="BI15" s="7"/>
       <c r="BJ15" s="7"/>
@@ -2617,63 +2614,63 @@
     <row r="16" spans="1:62" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="9"/>
-      <c r="O16" s="9"/>
-      <c r="P16" s="9"/>
-      <c r="Q16" s="9"/>
-      <c r="R16" s="9"/>
-      <c r="S16" s="9"/>
-      <c r="T16" s="9"/>
-      <c r="U16" s="9"/>
-      <c r="V16" s="9"/>
-      <c r="W16" s="9"/>
-      <c r="X16" s="9"/>
-      <c r="Y16" s="9"/>
-      <c r="Z16" s="9"/>
-      <c r="AA16" s="9"/>
-      <c r="AB16" s="9"/>
-      <c r="AC16" s="9"/>
-      <c r="AD16" s="9"/>
-      <c r="AE16" s="9"/>
-      <c r="AF16" s="9"/>
-      <c r="AG16" s="9"/>
-      <c r="AH16" s="9"/>
-      <c r="AI16" s="9"/>
-      <c r="AJ16" s="9"/>
-      <c r="AK16" s="9"/>
-      <c r="AL16" s="9"/>
-      <c r="AM16" s="9"/>
-      <c r="AN16" s="9"/>
-      <c r="AO16" s="9"/>
-      <c r="AP16" s="9"/>
-      <c r="AQ16" s="9"/>
-      <c r="AR16" s="9"/>
-      <c r="AS16" s="9"/>
-      <c r="AT16" s="9"/>
-      <c r="AU16" s="9"/>
-      <c r="AV16" s="9"/>
-      <c r="AW16" s="9"/>
-      <c r="AX16" s="9"/>
-      <c r="AY16" s="9"/>
-      <c r="AZ16" s="9"/>
-      <c r="BA16" s="9"/>
-      <c r="BB16" s="9"/>
-      <c r="BC16" s="9"/>
-      <c r="BD16" s="9"/>
-      <c r="BE16" s="9"/>
-      <c r="BF16" s="9"/>
-      <c r="BG16" s="9"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="8"/>
+      <c r="O16" s="8"/>
+      <c r="P16" s="8"/>
+      <c r="Q16" s="8"/>
+      <c r="R16" s="8"/>
+      <c r="S16" s="8"/>
+      <c r="T16" s="8"/>
+      <c r="U16" s="8"/>
+      <c r="V16" s="8"/>
+      <c r="W16" s="8"/>
+      <c r="X16" s="8"/>
+      <c r="Y16" s="8"/>
+      <c r="Z16" s="8"/>
+      <c r="AA16" s="8"/>
+      <c r="AB16" s="8"/>
+      <c r="AC16" s="8"/>
+      <c r="AD16" s="8"/>
+      <c r="AE16" s="8"/>
+      <c r="AF16" s="8"/>
+      <c r="AG16" s="8"/>
+      <c r="AH16" s="8"/>
+      <c r="AI16" s="8"/>
+      <c r="AJ16" s="8"/>
+      <c r="AK16" s="8"/>
+      <c r="AL16" s="8"/>
+      <c r="AM16" s="8"/>
+      <c r="AN16" s="8"/>
+      <c r="AO16" s="8"/>
+      <c r="AP16" s="8"/>
+      <c r="AQ16" s="8"/>
+      <c r="AR16" s="8"/>
+      <c r="AS16" s="8"/>
+      <c r="AT16" s="8"/>
+      <c r="AU16" s="8"/>
+      <c r="AV16" s="8"/>
+      <c r="AW16" s="8"/>
+      <c r="AX16" s="8"/>
+      <c r="AY16" s="8"/>
+      <c r="AZ16" s="8"/>
+      <c r="BA16" s="8"/>
+      <c r="BB16" s="8"/>
+      <c r="BC16" s="8"/>
+      <c r="BD16" s="8"/>
+      <c r="BE16" s="8"/>
+      <c r="BF16" s="8"/>
+      <c r="BG16" s="8"/>
       <c r="BH16" s="7"/>
       <c r="BI16" s="7"/>
       <c r="BJ16" s="7"/>
@@ -2681,73 +2678,73 @@
     <row r="17" spans="1:62" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
-      <c r="C17" s="56" t="s">
+      <c r="C17" s="63" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="46"/>
-      <c r="E17" s="46"/>
-      <c r="F17" s="46"/>
-      <c r="G17" s="46"/>
-      <c r="H17" s="46"/>
-      <c r="I17" s="46"/>
-      <c r="J17" s="57" t="s">
+      <c r="D17" s="53"/>
+      <c r="E17" s="53"/>
+      <c r="F17" s="53"/>
+      <c r="G17" s="53"/>
+      <c r="H17" s="53"/>
+      <c r="I17" s="53"/>
+      <c r="J17" s="64" t="s">
         <v>179</v>
       </c>
-      <c r="K17" s="46"/>
-      <c r="L17" s="46"/>
-      <c r="M17" s="46"/>
-      <c r="N17" s="46"/>
-      <c r="O17" s="46"/>
-      <c r="P17" s="46"/>
-      <c r="Q17" s="46"/>
-      <c r="R17" s="46"/>
-      <c r="S17" s="47"/>
-      <c r="T17" s="56" t="s">
+      <c r="K17" s="53"/>
+      <c r="L17" s="53"/>
+      <c r="M17" s="53"/>
+      <c r="N17" s="53"/>
+      <c r="O17" s="53"/>
+      <c r="P17" s="53"/>
+      <c r="Q17" s="53"/>
+      <c r="R17" s="53"/>
+      <c r="S17" s="54"/>
+      <c r="T17" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="U17" s="46"/>
-      <c r="V17" s="46"/>
-      <c r="W17" s="46"/>
-      <c r="X17" s="46"/>
-      <c r="Y17" s="46"/>
-      <c r="Z17" s="46"/>
-      <c r="AA17" s="58" t="s">
+      <c r="U17" s="53"/>
+      <c r="V17" s="53"/>
+      <c r="W17" s="53"/>
+      <c r="X17" s="53"/>
+      <c r="Y17" s="53"/>
+      <c r="Z17" s="53"/>
+      <c r="AA17" s="65" t="s">
         <v>170</v>
       </c>
-      <c r="AB17" s="58"/>
-      <c r="AC17" s="58"/>
-      <c r="AD17" s="58"/>
-      <c r="AE17" s="58"/>
-      <c r="AF17" s="58"/>
-      <c r="AG17" s="58"/>
-      <c r="AH17" s="58"/>
-      <c r="AI17" s="58"/>
-      <c r="AJ17" s="58"/>
-      <c r="AK17" s="58"/>
-      <c r="AL17" s="58"/>
-      <c r="AM17" s="9"/>
-      <c r="AN17" s="9"/>
-      <c r="AO17" s="59" t="s">
+      <c r="AB17" s="65"/>
+      <c r="AC17" s="65"/>
+      <c r="AD17" s="65"/>
+      <c r="AE17" s="65"/>
+      <c r="AF17" s="65"/>
+      <c r="AG17" s="65"/>
+      <c r="AH17" s="65"/>
+      <c r="AI17" s="65"/>
+      <c r="AJ17" s="65"/>
+      <c r="AK17" s="65"/>
+      <c r="AL17" s="65"/>
+      <c r="AM17" s="8"/>
+      <c r="AN17" s="8"/>
+      <c r="AO17" s="66" t="s">
         <v>20</v>
       </c>
-      <c r="AP17" s="43"/>
-      <c r="AQ17" s="43"/>
-      <c r="AR17" s="43"/>
-      <c r="AS17" s="43"/>
-      <c r="AT17" s="43"/>
-      <c r="AU17" s="43"/>
-      <c r="AV17" s="43"/>
-      <c r="AW17" s="43"/>
-      <c r="AX17" s="43"/>
-      <c r="AY17" s="43"/>
-      <c r="AZ17" s="43"/>
-      <c r="BA17" s="43"/>
-      <c r="BB17" s="43"/>
-      <c r="BC17" s="43"/>
-      <c r="BD17" s="43"/>
-      <c r="BE17" s="43"/>
-      <c r="BF17" s="43"/>
-      <c r="BG17" s="44"/>
+      <c r="AP17" s="50"/>
+      <c r="AQ17" s="50"/>
+      <c r="AR17" s="50"/>
+      <c r="AS17" s="50"/>
+      <c r="AT17" s="50"/>
+      <c r="AU17" s="50"/>
+      <c r="AV17" s="50"/>
+      <c r="AW17" s="50"/>
+      <c r="AX17" s="50"/>
+      <c r="AY17" s="50"/>
+      <c r="AZ17" s="50"/>
+      <c r="BA17" s="50"/>
+      <c r="BB17" s="50"/>
+      <c r="BC17" s="50"/>
+      <c r="BD17" s="50"/>
+      <c r="BE17" s="50"/>
+      <c r="BF17" s="50"/>
+      <c r="BG17" s="51"/>
       <c r="BH17" s="7"/>
       <c r="BI17" s="7"/>
       <c r="BJ17" s="7"/>
@@ -2755,65 +2752,65 @@
     <row r="18" spans="1:62" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
-      <c r="C18" s="48"/>
-      <c r="D18" s="49"/>
-      <c r="E18" s="49"/>
-      <c r="F18" s="49"/>
-      <c r="G18" s="49"/>
-      <c r="H18" s="49"/>
-      <c r="I18" s="49"/>
-      <c r="J18" s="48"/>
-      <c r="K18" s="49"/>
-      <c r="L18" s="49"/>
-      <c r="M18" s="49"/>
-      <c r="N18" s="49"/>
-      <c r="O18" s="49"/>
-      <c r="P18" s="49"/>
-      <c r="Q18" s="49"/>
-      <c r="R18" s="49"/>
-      <c r="S18" s="50"/>
-      <c r="T18" s="48"/>
-      <c r="U18" s="49"/>
-      <c r="V18" s="49"/>
-      <c r="W18" s="49"/>
-      <c r="X18" s="49"/>
-      <c r="Y18" s="49"/>
-      <c r="Z18" s="49"/>
-      <c r="AA18" s="58"/>
-      <c r="AB18" s="58"/>
-      <c r="AC18" s="58"/>
-      <c r="AD18" s="58"/>
-      <c r="AE18" s="58"/>
-      <c r="AF18" s="58"/>
-      <c r="AG18" s="58"/>
-      <c r="AH18" s="58"/>
-      <c r="AI18" s="58"/>
-      <c r="AJ18" s="58"/>
-      <c r="AK18" s="58"/>
-      <c r="AL18" s="58"/>
-      <c r="AM18" s="9"/>
-      <c r="AN18" s="9"/>
-      <c r="AO18" s="60" t="s">
+      <c r="C18" s="55"/>
+      <c r="D18" s="56"/>
+      <c r="E18" s="56"/>
+      <c r="F18" s="56"/>
+      <c r="G18" s="56"/>
+      <c r="H18" s="56"/>
+      <c r="I18" s="56"/>
+      <c r="J18" s="55"/>
+      <c r="K18" s="56"/>
+      <c r="L18" s="56"/>
+      <c r="M18" s="56"/>
+      <c r="N18" s="56"/>
+      <c r="O18" s="56"/>
+      <c r="P18" s="56"/>
+      <c r="Q18" s="56"/>
+      <c r="R18" s="56"/>
+      <c r="S18" s="57"/>
+      <c r="T18" s="55"/>
+      <c r="U18" s="56"/>
+      <c r="V18" s="56"/>
+      <c r="W18" s="56"/>
+      <c r="X18" s="56"/>
+      <c r="Y18" s="56"/>
+      <c r="Z18" s="56"/>
+      <c r="AA18" s="65"/>
+      <c r="AB18" s="65"/>
+      <c r="AC18" s="65"/>
+      <c r="AD18" s="65"/>
+      <c r="AE18" s="65"/>
+      <c r="AF18" s="65"/>
+      <c r="AG18" s="65"/>
+      <c r="AH18" s="65"/>
+      <c r="AI18" s="65"/>
+      <c r="AJ18" s="65"/>
+      <c r="AK18" s="65"/>
+      <c r="AL18" s="65"/>
+      <c r="AM18" s="8"/>
+      <c r="AN18" s="8"/>
+      <c r="AO18" s="67" t="s">
         <v>172</v>
       </c>
-      <c r="AP18" s="49"/>
-      <c r="AQ18" s="49"/>
-      <c r="AR18" s="49"/>
-      <c r="AS18" s="49"/>
-      <c r="AT18" s="49"/>
-      <c r="AU18" s="49"/>
-      <c r="AV18" s="49"/>
-      <c r="AW18" s="49"/>
-      <c r="AX18" s="49"/>
-      <c r="AY18" s="49"/>
-      <c r="AZ18" s="49"/>
-      <c r="BA18" s="49"/>
-      <c r="BB18" s="49"/>
-      <c r="BC18" s="49"/>
-      <c r="BD18" s="49"/>
-      <c r="BE18" s="49"/>
-      <c r="BF18" s="49"/>
-      <c r="BG18" s="50"/>
+      <c r="AP18" s="56"/>
+      <c r="AQ18" s="56"/>
+      <c r="AR18" s="56"/>
+      <c r="AS18" s="56"/>
+      <c r="AT18" s="56"/>
+      <c r="AU18" s="56"/>
+      <c r="AV18" s="56"/>
+      <c r="AW18" s="56"/>
+      <c r="AX18" s="56"/>
+      <c r="AY18" s="56"/>
+      <c r="AZ18" s="56"/>
+      <c r="BA18" s="56"/>
+      <c r="BB18" s="56"/>
+      <c r="BC18" s="56"/>
+      <c r="BD18" s="56"/>
+      <c r="BE18" s="56"/>
+      <c r="BF18" s="56"/>
+      <c r="BG18" s="57"/>
       <c r="BH18" s="7"/>
       <c r="BI18" s="7"/>
       <c r="BJ18" s="7"/>
@@ -2821,63 +2818,63 @@
     <row r="19" spans="1:62" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="7"/>
       <c r="B19" s="7"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
-      <c r="K19" s="9"/>
-      <c r="L19" s="9"/>
-      <c r="M19" s="9"/>
-      <c r="N19" s="9"/>
-      <c r="O19" s="9"/>
-      <c r="P19" s="9"/>
-      <c r="Q19" s="9"/>
-      <c r="R19" s="9"/>
-      <c r="S19" s="9"/>
-      <c r="T19" s="9"/>
-      <c r="U19" s="9"/>
-      <c r="V19" s="9"/>
-      <c r="W19" s="9"/>
-      <c r="X19" s="9"/>
-      <c r="Y19" s="9"/>
-      <c r="Z19" s="9"/>
-      <c r="AA19" s="9"/>
-      <c r="AB19" s="9"/>
-      <c r="AC19" s="9"/>
-      <c r="AD19" s="9"/>
-      <c r="AE19" s="9"/>
-      <c r="AF19" s="9"/>
-      <c r="AG19" s="9"/>
-      <c r="AH19" s="9"/>
-      <c r="AI19" s="9"/>
-      <c r="AJ19" s="9"/>
-      <c r="AK19" s="9"/>
-      <c r="AL19" s="9"/>
-      <c r="AM19" s="9"/>
-      <c r="AN19" s="9"/>
-      <c r="AO19" s="9"/>
-      <c r="AP19" s="9"/>
-      <c r="AQ19" s="9"/>
-      <c r="AR19" s="9"/>
-      <c r="AS19" s="9"/>
-      <c r="AT19" s="9"/>
-      <c r="AU19" s="9"/>
-      <c r="AV19" s="9"/>
-      <c r="AW19" s="9"/>
-      <c r="AX19" s="9"/>
-      <c r="AY19" s="9"/>
-      <c r="AZ19" s="9"/>
-      <c r="BA19" s="9"/>
-      <c r="BB19" s="9"/>
-      <c r="BC19" s="9"/>
-      <c r="BD19" s="9"/>
-      <c r="BE19" s="9"/>
-      <c r="BF19" s="9"/>
-      <c r="BG19" s="9"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="8"/>
+      <c r="M19" s="8"/>
+      <c r="N19" s="8"/>
+      <c r="O19" s="8"/>
+      <c r="P19" s="8"/>
+      <c r="Q19" s="8"/>
+      <c r="R19" s="8"/>
+      <c r="S19" s="8"/>
+      <c r="T19" s="8"/>
+      <c r="U19" s="8"/>
+      <c r="V19" s="8"/>
+      <c r="W19" s="8"/>
+      <c r="X19" s="8"/>
+      <c r="Y19" s="8"/>
+      <c r="Z19" s="8"/>
+      <c r="AA19" s="8"/>
+      <c r="AB19" s="8"/>
+      <c r="AC19" s="8"/>
+      <c r="AD19" s="8"/>
+      <c r="AE19" s="8"/>
+      <c r="AF19" s="8"/>
+      <c r="AG19" s="8"/>
+      <c r="AH19" s="8"/>
+      <c r="AI19" s="8"/>
+      <c r="AJ19" s="8"/>
+      <c r="AK19" s="8"/>
+      <c r="AL19" s="8"/>
+      <c r="AM19" s="8"/>
+      <c r="AN19" s="8"/>
+      <c r="AO19" s="8"/>
+      <c r="AP19" s="8"/>
+      <c r="AQ19" s="8"/>
+      <c r="AR19" s="8"/>
+      <c r="AS19" s="8"/>
+      <c r="AT19" s="8"/>
+      <c r="AU19" s="8"/>
+      <c r="AV19" s="8"/>
+      <c r="AW19" s="8"/>
+      <c r="AX19" s="8"/>
+      <c r="AY19" s="8"/>
+      <c r="AZ19" s="8"/>
+      <c r="BA19" s="8"/>
+      <c r="BB19" s="8"/>
+      <c r="BC19" s="8"/>
+      <c r="BD19" s="8"/>
+      <c r="BE19" s="8"/>
+      <c r="BF19" s="8"/>
+      <c r="BG19" s="8"/>
       <c r="BH19" s="7"/>
       <c r="BI19" s="7"/>
       <c r="BJ19" s="7"/>
@@ -2885,65 +2882,65 @@
     <row r="20" spans="1:62" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
-      <c r="C20" s="42" t="s">
+      <c r="C20" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="D20" s="43"/>
-      <c r="E20" s="43"/>
-      <c r="F20" s="43"/>
-      <c r="G20" s="43"/>
-      <c r="H20" s="43"/>
-      <c r="I20" s="43"/>
-      <c r="J20" s="43"/>
-      <c r="K20" s="43"/>
-      <c r="L20" s="43"/>
-      <c r="M20" s="43"/>
-      <c r="N20" s="43"/>
-      <c r="O20" s="43"/>
-      <c r="P20" s="43"/>
-      <c r="Q20" s="43"/>
-      <c r="R20" s="43"/>
-      <c r="S20" s="43"/>
-      <c r="T20" s="43"/>
-      <c r="U20" s="43"/>
-      <c r="V20" s="43"/>
-      <c r="W20" s="43"/>
-      <c r="X20" s="43"/>
-      <c r="Y20" s="43"/>
-      <c r="Z20" s="43"/>
-      <c r="AA20" s="43"/>
-      <c r="AB20" s="43"/>
-      <c r="AC20" s="43"/>
-      <c r="AD20" s="43"/>
-      <c r="AE20" s="43"/>
-      <c r="AF20" s="43"/>
-      <c r="AG20" s="43"/>
-      <c r="AH20" s="43"/>
-      <c r="AI20" s="43"/>
-      <c r="AJ20" s="43"/>
-      <c r="AK20" s="43"/>
-      <c r="AL20" s="43"/>
-      <c r="AM20" s="43"/>
-      <c r="AN20" s="43"/>
-      <c r="AO20" s="43"/>
-      <c r="AP20" s="43"/>
-      <c r="AQ20" s="43"/>
-      <c r="AR20" s="43"/>
-      <c r="AS20" s="43"/>
-      <c r="AT20" s="43"/>
-      <c r="AU20" s="43"/>
-      <c r="AV20" s="43"/>
-      <c r="AW20" s="43"/>
-      <c r="AX20" s="43"/>
-      <c r="AY20" s="43"/>
-      <c r="AZ20" s="43"/>
-      <c r="BA20" s="43"/>
-      <c r="BB20" s="43"/>
-      <c r="BC20" s="43"/>
-      <c r="BD20" s="43"/>
-      <c r="BE20" s="43"/>
-      <c r="BF20" s="43"/>
-      <c r="BG20" s="44"/>
+      <c r="D20" s="50"/>
+      <c r="E20" s="50"/>
+      <c r="F20" s="50"/>
+      <c r="G20" s="50"/>
+      <c r="H20" s="50"/>
+      <c r="I20" s="50"/>
+      <c r="J20" s="50"/>
+      <c r="K20" s="50"/>
+      <c r="L20" s="50"/>
+      <c r="M20" s="50"/>
+      <c r="N20" s="50"/>
+      <c r="O20" s="50"/>
+      <c r="P20" s="50"/>
+      <c r="Q20" s="50"/>
+      <c r="R20" s="50"/>
+      <c r="S20" s="50"/>
+      <c r="T20" s="50"/>
+      <c r="U20" s="50"/>
+      <c r="V20" s="50"/>
+      <c r="W20" s="50"/>
+      <c r="X20" s="50"/>
+      <c r="Y20" s="50"/>
+      <c r="Z20" s="50"/>
+      <c r="AA20" s="50"/>
+      <c r="AB20" s="50"/>
+      <c r="AC20" s="50"/>
+      <c r="AD20" s="50"/>
+      <c r="AE20" s="50"/>
+      <c r="AF20" s="50"/>
+      <c r="AG20" s="50"/>
+      <c r="AH20" s="50"/>
+      <c r="AI20" s="50"/>
+      <c r="AJ20" s="50"/>
+      <c r="AK20" s="50"/>
+      <c r="AL20" s="50"/>
+      <c r="AM20" s="50"/>
+      <c r="AN20" s="50"/>
+      <c r="AO20" s="50"/>
+      <c r="AP20" s="50"/>
+      <c r="AQ20" s="50"/>
+      <c r="AR20" s="50"/>
+      <c r="AS20" s="50"/>
+      <c r="AT20" s="50"/>
+      <c r="AU20" s="50"/>
+      <c r="AV20" s="50"/>
+      <c r="AW20" s="50"/>
+      <c r="AX20" s="50"/>
+      <c r="AY20" s="50"/>
+      <c r="AZ20" s="50"/>
+      <c r="BA20" s="50"/>
+      <c r="BB20" s="50"/>
+      <c r="BC20" s="50"/>
+      <c r="BD20" s="50"/>
+      <c r="BE20" s="50"/>
+      <c r="BF20" s="50"/>
+      <c r="BG20" s="51"/>
       <c r="BH20" s="7"/>
       <c r="BI20" s="7"/>
       <c r="BJ20" s="7"/>
@@ -2951,65 +2948,65 @@
     <row r="21" spans="1:62" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
-      <c r="C21" s="45" t="s">
+      <c r="C21" s="52" t="s">
         <v>175</v>
       </c>
-      <c r="D21" s="46"/>
-      <c r="E21" s="46"/>
-      <c r="F21" s="46"/>
-      <c r="G21" s="46"/>
-      <c r="H21" s="46"/>
-      <c r="I21" s="46"/>
-      <c r="J21" s="46"/>
-      <c r="K21" s="46"/>
-      <c r="L21" s="46"/>
-      <c r="M21" s="46"/>
-      <c r="N21" s="46"/>
-      <c r="O21" s="46"/>
-      <c r="P21" s="46"/>
-      <c r="Q21" s="46"/>
-      <c r="R21" s="46"/>
-      <c r="S21" s="46"/>
-      <c r="T21" s="46"/>
-      <c r="U21" s="46"/>
-      <c r="V21" s="46"/>
-      <c r="W21" s="46"/>
-      <c r="X21" s="46"/>
-      <c r="Y21" s="46"/>
-      <c r="Z21" s="46"/>
-      <c r="AA21" s="46"/>
-      <c r="AB21" s="46"/>
-      <c r="AC21" s="46"/>
-      <c r="AD21" s="46"/>
-      <c r="AE21" s="46"/>
-      <c r="AF21" s="46"/>
-      <c r="AG21" s="46"/>
-      <c r="AH21" s="46"/>
-      <c r="AI21" s="46"/>
-      <c r="AJ21" s="46"/>
-      <c r="AK21" s="46"/>
-      <c r="AL21" s="46"/>
-      <c r="AM21" s="46"/>
-      <c r="AN21" s="46"/>
-      <c r="AO21" s="46"/>
-      <c r="AP21" s="46"/>
-      <c r="AQ21" s="46"/>
-      <c r="AR21" s="46"/>
-      <c r="AS21" s="46"/>
-      <c r="AT21" s="46"/>
-      <c r="AU21" s="46"/>
-      <c r="AV21" s="46"/>
-      <c r="AW21" s="46"/>
-      <c r="AX21" s="46"/>
-      <c r="AY21" s="46"/>
-      <c r="AZ21" s="46"/>
-      <c r="BA21" s="46"/>
-      <c r="BB21" s="46"/>
-      <c r="BC21" s="46"/>
-      <c r="BD21" s="46"/>
-      <c r="BE21" s="46"/>
-      <c r="BF21" s="46"/>
-      <c r="BG21" s="47"/>
+      <c r="D21" s="53"/>
+      <c r="E21" s="53"/>
+      <c r="F21" s="53"/>
+      <c r="G21" s="53"/>
+      <c r="H21" s="53"/>
+      <c r="I21" s="53"/>
+      <c r="J21" s="53"/>
+      <c r="K21" s="53"/>
+      <c r="L21" s="53"/>
+      <c r="M21" s="53"/>
+      <c r="N21" s="53"/>
+      <c r="O21" s="53"/>
+      <c r="P21" s="53"/>
+      <c r="Q21" s="53"/>
+      <c r="R21" s="53"/>
+      <c r="S21" s="53"/>
+      <c r="T21" s="53"/>
+      <c r="U21" s="53"/>
+      <c r="V21" s="53"/>
+      <c r="W21" s="53"/>
+      <c r="X21" s="53"/>
+      <c r="Y21" s="53"/>
+      <c r="Z21" s="53"/>
+      <c r="AA21" s="53"/>
+      <c r="AB21" s="53"/>
+      <c r="AC21" s="53"/>
+      <c r="AD21" s="53"/>
+      <c r="AE21" s="53"/>
+      <c r="AF21" s="53"/>
+      <c r="AG21" s="53"/>
+      <c r="AH21" s="53"/>
+      <c r="AI21" s="53"/>
+      <c r="AJ21" s="53"/>
+      <c r="AK21" s="53"/>
+      <c r="AL21" s="53"/>
+      <c r="AM21" s="53"/>
+      <c r="AN21" s="53"/>
+      <c r="AO21" s="53"/>
+      <c r="AP21" s="53"/>
+      <c r="AQ21" s="53"/>
+      <c r="AR21" s="53"/>
+      <c r="AS21" s="53"/>
+      <c r="AT21" s="53"/>
+      <c r="AU21" s="53"/>
+      <c r="AV21" s="53"/>
+      <c r="AW21" s="53"/>
+      <c r="AX21" s="53"/>
+      <c r="AY21" s="53"/>
+      <c r="AZ21" s="53"/>
+      <c r="BA21" s="53"/>
+      <c r="BB21" s="53"/>
+      <c r="BC21" s="53"/>
+      <c r="BD21" s="53"/>
+      <c r="BE21" s="53"/>
+      <c r="BF21" s="53"/>
+      <c r="BG21" s="54"/>
       <c r="BH21" s="7"/>
       <c r="BI21" s="7"/>
       <c r="BJ21" s="7"/>
@@ -3017,63 +3014,63 @@
     <row r="22" spans="1:62" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
-      <c r="C22" s="48"/>
-      <c r="D22" s="49"/>
-      <c r="E22" s="49"/>
-      <c r="F22" s="49"/>
-      <c r="G22" s="49"/>
-      <c r="H22" s="49"/>
-      <c r="I22" s="49"/>
-      <c r="J22" s="49"/>
-      <c r="K22" s="49"/>
-      <c r="L22" s="49"/>
-      <c r="M22" s="49"/>
-      <c r="N22" s="49"/>
-      <c r="O22" s="49"/>
-      <c r="P22" s="49"/>
-      <c r="Q22" s="49"/>
-      <c r="R22" s="49"/>
-      <c r="S22" s="49"/>
-      <c r="T22" s="49"/>
-      <c r="U22" s="49"/>
-      <c r="V22" s="49"/>
-      <c r="W22" s="49"/>
-      <c r="X22" s="49"/>
-      <c r="Y22" s="49"/>
-      <c r="Z22" s="49"/>
-      <c r="AA22" s="49"/>
-      <c r="AB22" s="49"/>
-      <c r="AC22" s="49"/>
-      <c r="AD22" s="49"/>
-      <c r="AE22" s="49"/>
-      <c r="AF22" s="49"/>
-      <c r="AG22" s="49"/>
-      <c r="AH22" s="49"/>
-      <c r="AI22" s="49"/>
-      <c r="AJ22" s="49"/>
-      <c r="AK22" s="49"/>
-      <c r="AL22" s="49"/>
-      <c r="AM22" s="49"/>
-      <c r="AN22" s="49"/>
-      <c r="AO22" s="49"/>
-      <c r="AP22" s="49"/>
-      <c r="AQ22" s="49"/>
-      <c r="AR22" s="49"/>
-      <c r="AS22" s="49"/>
-      <c r="AT22" s="49"/>
-      <c r="AU22" s="49"/>
-      <c r="AV22" s="49"/>
-      <c r="AW22" s="49"/>
-      <c r="AX22" s="49"/>
-      <c r="AY22" s="49"/>
-      <c r="AZ22" s="49"/>
-      <c r="BA22" s="49"/>
-      <c r="BB22" s="49"/>
-      <c r="BC22" s="49"/>
-      <c r="BD22" s="49"/>
-      <c r="BE22" s="49"/>
-      <c r="BF22" s="49"/>
-      <c r="BG22" s="50"/>
+      <c r="C22" s="55"/>
+      <c r="D22" s="56"/>
+      <c r="E22" s="56"/>
+      <c r="F22" s="56"/>
+      <c r="G22" s="56"/>
+      <c r="H22" s="56"/>
+      <c r="I22" s="56"/>
+      <c r="J22" s="56"/>
+      <c r="K22" s="56"/>
+      <c r="L22" s="56"/>
+      <c r="M22" s="56"/>
+      <c r="N22" s="56"/>
+      <c r="O22" s="56"/>
+      <c r="P22" s="56"/>
+      <c r="Q22" s="56"/>
+      <c r="R22" s="56"/>
+      <c r="S22" s="56"/>
+      <c r="T22" s="56"/>
+      <c r="U22" s="56"/>
+      <c r="V22" s="56"/>
+      <c r="W22" s="56"/>
+      <c r="X22" s="56"/>
+      <c r="Y22" s="56"/>
+      <c r="Z22" s="56"/>
+      <c r="AA22" s="56"/>
+      <c r="AB22" s="56"/>
+      <c r="AC22" s="56"/>
+      <c r="AD22" s="56"/>
+      <c r="AE22" s="56"/>
+      <c r="AF22" s="56"/>
+      <c r="AG22" s="56"/>
+      <c r="AH22" s="56"/>
+      <c r="AI22" s="56"/>
+      <c r="AJ22" s="56"/>
+      <c r="AK22" s="56"/>
+      <c r="AL22" s="56"/>
+      <c r="AM22" s="56"/>
+      <c r="AN22" s="56"/>
+      <c r="AO22" s="56"/>
+      <c r="AP22" s="56"/>
+      <c r="AQ22" s="56"/>
+      <c r="AR22" s="56"/>
+      <c r="AS22" s="56"/>
+      <c r="AT22" s="56"/>
+      <c r="AU22" s="56"/>
+      <c r="AV22" s="56"/>
+      <c r="AW22" s="56"/>
+      <c r="AX22" s="56"/>
+      <c r="AY22" s="56"/>
+      <c r="AZ22" s="56"/>
+      <c r="BA22" s="56"/>
+      <c r="BB22" s="56"/>
+      <c r="BC22" s="56"/>
+      <c r="BD22" s="56"/>
+      <c r="BE22" s="56"/>
+      <c r="BF22" s="56"/>
+      <c r="BG22" s="57"/>
       <c r="BH22" s="7"/>
       <c r="BI22" s="7"/>
       <c r="BJ22" s="7"/>
@@ -3145,83 +3142,83 @@
     <row r="24" spans="1:62" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
-      <c r="C24" s="51" t="s">
+      <c r="C24" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="D24" s="29"/>
-      <c r="E24" s="51" t="s">
+      <c r="D24" s="27"/>
+      <c r="E24" s="58" t="s">
         <v>23</v>
       </c>
-      <c r="F24" s="23"/>
-      <c r="G24" s="23"/>
-      <c r="H24" s="29"/>
-      <c r="I24" s="51" t="s">
+      <c r="F24" s="21"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="27"/>
+      <c r="I24" s="58" t="s">
         <v>24</v>
       </c>
-      <c r="J24" s="23"/>
-      <c r="K24" s="23"/>
-      <c r="L24" s="55" t="s">
+      <c r="J24" s="21"/>
+      <c r="K24" s="21"/>
+      <c r="L24" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="M24" s="23"/>
-      <c r="N24" s="29"/>
-      <c r="O24" s="51" t="s">
+      <c r="M24" s="21"/>
+      <c r="N24" s="27"/>
+      <c r="O24" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="P24" s="23"/>
-      <c r="Q24" s="23"/>
-      <c r="R24" s="23"/>
-      <c r="S24" s="23"/>
-      <c r="T24" s="23"/>
-      <c r="U24" s="23"/>
-      <c r="V24" s="23"/>
-      <c r="W24" s="23"/>
-      <c r="X24" s="23"/>
-      <c r="Y24" s="23"/>
-      <c r="Z24" s="23"/>
-      <c r="AA24" s="23"/>
-      <c r="AB24" s="23"/>
-      <c r="AC24" s="23"/>
-      <c r="AD24" s="23"/>
-      <c r="AE24" s="23"/>
-      <c r="AF24" s="23"/>
-      <c r="AG24" s="23"/>
-      <c r="AH24" s="23"/>
-      <c r="AI24" s="23"/>
-      <c r="AJ24" s="23"/>
-      <c r="AK24" s="23"/>
-      <c r="AL24" s="23"/>
-      <c r="AM24" s="29"/>
-      <c r="AN24" s="51" t="s">
+      <c r="P24" s="21"/>
+      <c r="Q24" s="21"/>
+      <c r="R24" s="21"/>
+      <c r="S24" s="21"/>
+      <c r="T24" s="21"/>
+      <c r="U24" s="21"/>
+      <c r="V24" s="21"/>
+      <c r="W24" s="21"/>
+      <c r="X24" s="21"/>
+      <c r="Y24" s="21"/>
+      <c r="Z24" s="21"/>
+      <c r="AA24" s="21"/>
+      <c r="AB24" s="21"/>
+      <c r="AC24" s="21"/>
+      <c r="AD24" s="21"/>
+      <c r="AE24" s="21"/>
+      <c r="AF24" s="21"/>
+      <c r="AG24" s="21"/>
+      <c r="AH24" s="21"/>
+      <c r="AI24" s="21"/>
+      <c r="AJ24" s="21"/>
+      <c r="AK24" s="21"/>
+      <c r="AL24" s="21"/>
+      <c r="AM24" s="27"/>
+      <c r="AN24" s="58" t="s">
         <v>27</v>
       </c>
-      <c r="AO24" s="23"/>
-      <c r="AP24" s="29"/>
-      <c r="AQ24" s="51" t="s">
+      <c r="AO24" s="21"/>
+      <c r="AP24" s="27"/>
+      <c r="AQ24" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="AR24" s="23"/>
-      <c r="AS24" s="29"/>
-      <c r="AT24" s="51" t="s">
+      <c r="AR24" s="21"/>
+      <c r="AS24" s="27"/>
+      <c r="AT24" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="AU24" s="23"/>
-      <c r="AV24" s="23"/>
-      <c r="AW24" s="23"/>
-      <c r="AX24" s="29"/>
-      <c r="AY24" s="51" t="s">
+      <c r="AU24" s="21"/>
+      <c r="AV24" s="21"/>
+      <c r="AW24" s="21"/>
+      <c r="AX24" s="27"/>
+      <c r="AY24" s="58" t="s">
         <v>30</v>
       </c>
-      <c r="AZ24" s="23"/>
-      <c r="BA24" s="51" t="s">
+      <c r="AZ24" s="21"/>
+      <c r="BA24" s="58" t="s">
         <v>31</v>
       </c>
-      <c r="BB24" s="23"/>
-      <c r="BC24" s="23"/>
-      <c r="BD24" s="23"/>
-      <c r="BE24" s="23"/>
-      <c r="BF24" s="23"/>
-      <c r="BG24" s="29"/>
+      <c r="BB24" s="21"/>
+      <c r="BC24" s="21"/>
+      <c r="BD24" s="21"/>
+      <c r="BE24" s="21"/>
+      <c r="BF24" s="21"/>
+      <c r="BG24" s="27"/>
       <c r="BH24" s="7"/>
       <c r="BI24" s="7"/>
       <c r="BJ24" s="7"/>
@@ -3229,1072 +3226,1072 @@
     <row r="25" spans="1:62" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="7"/>
       <c r="B25" s="7"/>
-      <c r="C25" s="52"/>
-      <c r="D25" s="53"/>
-      <c r="E25" s="52"/>
-      <c r="F25" s="54"/>
-      <c r="G25" s="54"/>
-      <c r="H25" s="53"/>
-      <c r="I25" s="52"/>
-      <c r="J25" s="54"/>
-      <c r="K25" s="54"/>
-      <c r="L25" s="52"/>
-      <c r="M25" s="54"/>
-      <c r="N25" s="53"/>
-      <c r="O25" s="52"/>
-      <c r="P25" s="54"/>
-      <c r="Q25" s="54"/>
-      <c r="R25" s="54"/>
-      <c r="S25" s="54"/>
-      <c r="T25" s="54"/>
-      <c r="U25" s="54"/>
-      <c r="V25" s="54"/>
-      <c r="W25" s="54"/>
-      <c r="X25" s="54"/>
-      <c r="Y25" s="54"/>
-      <c r="Z25" s="54"/>
-      <c r="AA25" s="54"/>
-      <c r="AB25" s="54"/>
-      <c r="AC25" s="54"/>
-      <c r="AD25" s="54"/>
-      <c r="AE25" s="54"/>
-      <c r="AF25" s="54"/>
-      <c r="AG25" s="54"/>
-      <c r="AH25" s="54"/>
-      <c r="AI25" s="54"/>
-      <c r="AJ25" s="54"/>
-      <c r="AK25" s="54"/>
-      <c r="AL25" s="54"/>
-      <c r="AM25" s="53"/>
-      <c r="AN25" s="52"/>
-      <c r="AO25" s="54"/>
-      <c r="AP25" s="53"/>
-      <c r="AQ25" s="52"/>
-      <c r="AR25" s="54"/>
-      <c r="AS25" s="53"/>
-      <c r="AT25" s="52"/>
-      <c r="AU25" s="54"/>
-      <c r="AV25" s="54"/>
-      <c r="AW25" s="54"/>
-      <c r="AX25" s="53"/>
-      <c r="AY25" s="52"/>
-      <c r="AZ25" s="54"/>
-      <c r="BA25" s="52"/>
-      <c r="BB25" s="54"/>
-      <c r="BC25" s="54"/>
-      <c r="BD25" s="54"/>
-      <c r="BE25" s="54"/>
-      <c r="BF25" s="54"/>
-      <c r="BG25" s="53"/>
+      <c r="C25" s="59"/>
+      <c r="D25" s="60"/>
+      <c r="E25" s="59"/>
+      <c r="F25" s="61"/>
+      <c r="G25" s="61"/>
+      <c r="H25" s="60"/>
+      <c r="I25" s="59"/>
+      <c r="J25" s="61"/>
+      <c r="K25" s="61"/>
+      <c r="L25" s="59"/>
+      <c r="M25" s="61"/>
+      <c r="N25" s="60"/>
+      <c r="O25" s="59"/>
+      <c r="P25" s="61"/>
+      <c r="Q25" s="61"/>
+      <c r="R25" s="61"/>
+      <c r="S25" s="61"/>
+      <c r="T25" s="61"/>
+      <c r="U25" s="61"/>
+      <c r="V25" s="61"/>
+      <c r="W25" s="61"/>
+      <c r="X25" s="61"/>
+      <c r="Y25" s="61"/>
+      <c r="Z25" s="61"/>
+      <c r="AA25" s="61"/>
+      <c r="AB25" s="61"/>
+      <c r="AC25" s="61"/>
+      <c r="AD25" s="61"/>
+      <c r="AE25" s="61"/>
+      <c r="AF25" s="61"/>
+      <c r="AG25" s="61"/>
+      <c r="AH25" s="61"/>
+      <c r="AI25" s="61"/>
+      <c r="AJ25" s="61"/>
+      <c r="AK25" s="61"/>
+      <c r="AL25" s="61"/>
+      <c r="AM25" s="60"/>
+      <c r="AN25" s="59"/>
+      <c r="AO25" s="61"/>
+      <c r="AP25" s="60"/>
+      <c r="AQ25" s="59"/>
+      <c r="AR25" s="61"/>
+      <c r="AS25" s="60"/>
+      <c r="AT25" s="59"/>
+      <c r="AU25" s="61"/>
+      <c r="AV25" s="61"/>
+      <c r="AW25" s="61"/>
+      <c r="AX25" s="60"/>
+      <c r="AY25" s="59"/>
+      <c r="AZ25" s="61"/>
+      <c r="BA25" s="59"/>
+      <c r="BB25" s="61"/>
+      <c r="BC25" s="61"/>
+      <c r="BD25" s="61"/>
+      <c r="BE25" s="61"/>
+      <c r="BF25" s="61"/>
+      <c r="BG25" s="60"/>
       <c r="BH25" s="7"/>
       <c r="BI25" s="7"/>
       <c r="BJ25" s="7"/>
     </row>
-    <row r="26" spans="1:62" s="10" customFormat="1" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:62" s="9" customFormat="1" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
-      <c r="C26" s="31" t="s">
+      <c r="C26" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="D26" s="31"/>
-      <c r="E26" s="31" t="s">
+      <c r="D26" s="38"/>
+      <c r="E26" s="38" t="s">
         <v>55</v>
       </c>
-      <c r="F26" s="31"/>
-      <c r="G26" s="31"/>
-      <c r="H26" s="31"/>
-      <c r="I26" s="31" t="s">
+      <c r="F26" s="38"/>
+      <c r="G26" s="38"/>
+      <c r="H26" s="38"/>
+      <c r="I26" s="38" t="s">
         <v>67</v>
       </c>
-      <c r="J26" s="31"/>
-      <c r="K26" s="31"/>
-      <c r="L26" s="31" t="s">
+      <c r="J26" s="38"/>
+      <c r="K26" s="38"/>
+      <c r="L26" s="38" t="s">
         <v>79</v>
       </c>
-      <c r="M26" s="31"/>
-      <c r="N26" s="31"/>
-      <c r="O26" s="31" t="s">
+      <c r="M26" s="38"/>
+      <c r="N26" s="38"/>
+      <c r="O26" s="38" t="s">
         <v>91</v>
       </c>
-      <c r="P26" s="31"/>
-      <c r="Q26" s="31"/>
-      <c r="R26" s="31"/>
-      <c r="S26" s="31"/>
-      <c r="T26" s="31"/>
-      <c r="U26" s="31"/>
-      <c r="V26" s="31"/>
-      <c r="W26" s="31"/>
-      <c r="X26" s="31"/>
-      <c r="Y26" s="31"/>
-      <c r="Z26" s="31"/>
-      <c r="AA26" s="31"/>
-      <c r="AB26" s="31"/>
-      <c r="AC26" s="31"/>
-      <c r="AD26" s="31"/>
-      <c r="AE26" s="31"/>
-      <c r="AF26" s="31"/>
-      <c r="AG26" s="31"/>
-      <c r="AH26" s="31"/>
-      <c r="AI26" s="31"/>
-      <c r="AJ26" s="31"/>
-      <c r="AK26" s="31"/>
-      <c r="AL26" s="31"/>
-      <c r="AM26" s="31"/>
-      <c r="AN26" s="30" t="s">
+      <c r="P26" s="38"/>
+      <c r="Q26" s="38"/>
+      <c r="R26" s="38"/>
+      <c r="S26" s="38"/>
+      <c r="T26" s="38"/>
+      <c r="U26" s="38"/>
+      <c r="V26" s="38"/>
+      <c r="W26" s="38"/>
+      <c r="X26" s="38"/>
+      <c r="Y26" s="38"/>
+      <c r="Z26" s="38"/>
+      <c r="AA26" s="38"/>
+      <c r="AB26" s="38"/>
+      <c r="AC26" s="38"/>
+      <c r="AD26" s="38"/>
+      <c r="AE26" s="38"/>
+      <c r="AF26" s="38"/>
+      <c r="AG26" s="38"/>
+      <c r="AH26" s="38"/>
+      <c r="AI26" s="38"/>
+      <c r="AJ26" s="38"/>
+      <c r="AK26" s="38"/>
+      <c r="AL26" s="38"/>
+      <c r="AM26" s="38"/>
+      <c r="AN26" s="37" t="s">
         <v>103</v>
       </c>
-      <c r="AO26" s="33"/>
-      <c r="AP26" s="33"/>
-      <c r="AQ26" s="31" t="s">
+      <c r="AO26" s="40"/>
+      <c r="AP26" s="40"/>
+      <c r="AQ26" s="38" t="s">
         <v>115</v>
       </c>
-      <c r="AR26" s="31"/>
-      <c r="AS26" s="31"/>
-      <c r="AT26" s="30" t="s">
+      <c r="AR26" s="38"/>
+      <c r="AS26" s="38"/>
+      <c r="AT26" s="37" t="s">
         <v>127</v>
       </c>
-      <c r="AU26" s="30"/>
-      <c r="AV26" s="30"/>
-      <c r="AW26" s="30"/>
-      <c r="AX26" s="30"/>
-      <c r="AY26" s="31" t="s">
+      <c r="AU26" s="37"/>
+      <c r="AV26" s="37"/>
+      <c r="AW26" s="37"/>
+      <c r="AX26" s="37"/>
+      <c r="AY26" s="38" t="s">
         <v>139</v>
       </c>
-      <c r="AZ26" s="32"/>
-      <c r="BA26" s="30" t="s">
+      <c r="AZ26" s="39"/>
+      <c r="BA26" s="37" t="s">
         <v>151</v>
       </c>
-      <c r="BB26" s="33"/>
-      <c r="BC26" s="33"/>
-      <c r="BD26" s="33"/>
-      <c r="BE26" s="33"/>
-      <c r="BF26" s="33"/>
-      <c r="BG26" s="33"/>
+      <c r="BB26" s="40"/>
+      <c r="BC26" s="40"/>
+      <c r="BD26" s="40"/>
+      <c r="BE26" s="40"/>
+      <c r="BF26" s="40"/>
+      <c r="BG26" s="40"/>
       <c r="BH26" s="5"/>
       <c r="BI26" s="5"/>
       <c r="BJ26" s="5"/>
     </row>
-    <row r="27" spans="1:62" s="10" customFormat="1" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:62" s="9" customFormat="1" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5"/>
       <c r="B27" s="5"/>
-      <c r="C27" s="31" t="s">
+      <c r="C27" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="D27" s="31"/>
-      <c r="E27" s="31" t="s">
+      <c r="D27" s="38"/>
+      <c r="E27" s="38" t="s">
         <v>56</v>
       </c>
-      <c r="F27" s="31"/>
-      <c r="G27" s="31"/>
-      <c r="H27" s="31"/>
-      <c r="I27" s="31" t="s">
+      <c r="F27" s="38"/>
+      <c r="G27" s="38"/>
+      <c r="H27" s="38"/>
+      <c r="I27" s="38" t="s">
         <v>68</v>
       </c>
-      <c r="J27" s="31"/>
-      <c r="K27" s="31"/>
-      <c r="L27" s="31" t="s">
+      <c r="J27" s="38"/>
+      <c r="K27" s="38"/>
+      <c r="L27" s="38" t="s">
         <v>80</v>
       </c>
-      <c r="M27" s="31"/>
-      <c r="N27" s="31"/>
-      <c r="O27" s="31" t="s">
+      <c r="M27" s="38"/>
+      <c r="N27" s="38"/>
+      <c r="O27" s="38" t="s">
         <v>92</v>
       </c>
-      <c r="P27" s="31"/>
-      <c r="Q27" s="31"/>
-      <c r="R27" s="31"/>
-      <c r="S27" s="31"/>
-      <c r="T27" s="31"/>
-      <c r="U27" s="31"/>
-      <c r="V27" s="31"/>
-      <c r="W27" s="31"/>
-      <c r="X27" s="31"/>
-      <c r="Y27" s="31"/>
-      <c r="Z27" s="31"/>
-      <c r="AA27" s="31"/>
-      <c r="AB27" s="31"/>
-      <c r="AC27" s="31"/>
-      <c r="AD27" s="31"/>
-      <c r="AE27" s="31"/>
-      <c r="AF27" s="31"/>
-      <c r="AG27" s="31"/>
-      <c r="AH27" s="31"/>
-      <c r="AI27" s="31"/>
-      <c r="AJ27" s="31"/>
-      <c r="AK27" s="31"/>
-      <c r="AL27" s="31"/>
-      <c r="AM27" s="31"/>
-      <c r="AN27" s="30" t="s">
+      <c r="P27" s="38"/>
+      <c r="Q27" s="38"/>
+      <c r="R27" s="38"/>
+      <c r="S27" s="38"/>
+      <c r="T27" s="38"/>
+      <c r="U27" s="38"/>
+      <c r="V27" s="38"/>
+      <c r="W27" s="38"/>
+      <c r="X27" s="38"/>
+      <c r="Y27" s="38"/>
+      <c r="Z27" s="38"/>
+      <c r="AA27" s="38"/>
+      <c r="AB27" s="38"/>
+      <c r="AC27" s="38"/>
+      <c r="AD27" s="38"/>
+      <c r="AE27" s="38"/>
+      <c r="AF27" s="38"/>
+      <c r="AG27" s="38"/>
+      <c r="AH27" s="38"/>
+      <c r="AI27" s="38"/>
+      <c r="AJ27" s="38"/>
+      <c r="AK27" s="38"/>
+      <c r="AL27" s="38"/>
+      <c r="AM27" s="38"/>
+      <c r="AN27" s="37" t="s">
         <v>104</v>
       </c>
-      <c r="AO27" s="33"/>
-      <c r="AP27" s="33"/>
-      <c r="AQ27" s="31" t="s">
+      <c r="AO27" s="40"/>
+      <c r="AP27" s="40"/>
+      <c r="AQ27" s="38" t="s">
         <v>116</v>
       </c>
-      <c r="AR27" s="31"/>
-      <c r="AS27" s="31"/>
-      <c r="AT27" s="30" t="s">
+      <c r="AR27" s="38"/>
+      <c r="AS27" s="38"/>
+      <c r="AT27" s="37" t="s">
         <v>128</v>
       </c>
-      <c r="AU27" s="30"/>
-      <c r="AV27" s="30"/>
-      <c r="AW27" s="30"/>
-      <c r="AX27" s="30"/>
-      <c r="AY27" s="31" t="s">
+      <c r="AU27" s="37"/>
+      <c r="AV27" s="37"/>
+      <c r="AW27" s="37"/>
+      <c r="AX27" s="37"/>
+      <c r="AY27" s="38" t="s">
         <v>140</v>
       </c>
-      <c r="AZ27" s="32"/>
-      <c r="BA27" s="30" t="s">
+      <c r="AZ27" s="39"/>
+      <c r="BA27" s="37" t="s">
         <v>152</v>
       </c>
-      <c r="BB27" s="33"/>
-      <c r="BC27" s="33"/>
-      <c r="BD27" s="33"/>
-      <c r="BE27" s="33"/>
-      <c r="BF27" s="33"/>
-      <c r="BG27" s="33"/>
+      <c r="BB27" s="40"/>
+      <c r="BC27" s="40"/>
+      <c r="BD27" s="40"/>
+      <c r="BE27" s="40"/>
+      <c r="BF27" s="40"/>
+      <c r="BG27" s="40"/>
       <c r="BH27" s="5"/>
       <c r="BI27" s="5"/>
       <c r="BJ27" s="5"/>
     </row>
-    <row r="28" spans="1:62" s="10" customFormat="1" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:62" s="9" customFormat="1" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5"/>
       <c r="B28" s="5"/>
-      <c r="C28" s="31" t="s">
+      <c r="C28" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31" t="s">
+      <c r="D28" s="38"/>
+      <c r="E28" s="38" t="s">
         <v>57</v>
       </c>
-      <c r="F28" s="31"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="31"/>
-      <c r="I28" s="31" t="s">
+      <c r="F28" s="38"/>
+      <c r="G28" s="38"/>
+      <c r="H28" s="38"/>
+      <c r="I28" s="38" t="s">
         <v>69</v>
       </c>
-      <c r="J28" s="31"/>
-      <c r="K28" s="31"/>
-      <c r="L28" s="31" t="s">
+      <c r="J28" s="38"/>
+      <c r="K28" s="38"/>
+      <c r="L28" s="38" t="s">
         <v>81</v>
       </c>
-      <c r="M28" s="31"/>
-      <c r="N28" s="31"/>
-      <c r="O28" s="31" t="s">
+      <c r="M28" s="38"/>
+      <c r="N28" s="38"/>
+      <c r="O28" s="38" t="s">
         <v>93</v>
       </c>
-      <c r="P28" s="31"/>
-      <c r="Q28" s="31"/>
-      <c r="R28" s="31"/>
-      <c r="S28" s="31"/>
-      <c r="T28" s="31"/>
-      <c r="U28" s="31"/>
-      <c r="V28" s="31"/>
-      <c r="W28" s="31"/>
-      <c r="X28" s="31"/>
-      <c r="Y28" s="31"/>
-      <c r="Z28" s="31"/>
-      <c r="AA28" s="31"/>
-      <c r="AB28" s="31"/>
-      <c r="AC28" s="31"/>
-      <c r="AD28" s="31"/>
-      <c r="AE28" s="31"/>
-      <c r="AF28" s="31"/>
-      <c r="AG28" s="31"/>
-      <c r="AH28" s="31"/>
-      <c r="AI28" s="31"/>
-      <c r="AJ28" s="31"/>
-      <c r="AK28" s="31"/>
-      <c r="AL28" s="31"/>
-      <c r="AM28" s="31"/>
-      <c r="AN28" s="30" t="s">
+      <c r="P28" s="38"/>
+      <c r="Q28" s="38"/>
+      <c r="R28" s="38"/>
+      <c r="S28" s="38"/>
+      <c r="T28" s="38"/>
+      <c r="U28" s="38"/>
+      <c r="V28" s="38"/>
+      <c r="W28" s="38"/>
+      <c r="X28" s="38"/>
+      <c r="Y28" s="38"/>
+      <c r="Z28" s="38"/>
+      <c r="AA28" s="38"/>
+      <c r="AB28" s="38"/>
+      <c r="AC28" s="38"/>
+      <c r="AD28" s="38"/>
+      <c r="AE28" s="38"/>
+      <c r="AF28" s="38"/>
+      <c r="AG28" s="38"/>
+      <c r="AH28" s="38"/>
+      <c r="AI28" s="38"/>
+      <c r="AJ28" s="38"/>
+      <c r="AK28" s="38"/>
+      <c r="AL28" s="38"/>
+      <c r="AM28" s="38"/>
+      <c r="AN28" s="37" t="s">
         <v>105</v>
       </c>
-      <c r="AO28" s="33"/>
-      <c r="AP28" s="33"/>
-      <c r="AQ28" s="31" t="s">
+      <c r="AO28" s="40"/>
+      <c r="AP28" s="40"/>
+      <c r="AQ28" s="38" t="s">
         <v>117</v>
       </c>
-      <c r="AR28" s="31"/>
-      <c r="AS28" s="31"/>
-      <c r="AT28" s="30" t="s">
+      <c r="AR28" s="38"/>
+      <c r="AS28" s="38"/>
+      <c r="AT28" s="37" t="s">
         <v>129</v>
       </c>
-      <c r="AU28" s="30"/>
-      <c r="AV28" s="30"/>
-      <c r="AW28" s="30"/>
-      <c r="AX28" s="30"/>
-      <c r="AY28" s="31" t="s">
+      <c r="AU28" s="37"/>
+      <c r="AV28" s="37"/>
+      <c r="AW28" s="37"/>
+      <c r="AX28" s="37"/>
+      <c r="AY28" s="38" t="s">
         <v>141</v>
       </c>
-      <c r="AZ28" s="32"/>
-      <c r="BA28" s="30" t="s">
+      <c r="AZ28" s="39"/>
+      <c r="BA28" s="37" t="s">
         <v>153</v>
       </c>
-      <c r="BB28" s="33"/>
-      <c r="BC28" s="33"/>
-      <c r="BD28" s="33"/>
-      <c r="BE28" s="33"/>
-      <c r="BF28" s="33"/>
-      <c r="BG28" s="33"/>
+      <c r="BB28" s="40"/>
+      <c r="BC28" s="40"/>
+      <c r="BD28" s="40"/>
+      <c r="BE28" s="40"/>
+      <c r="BF28" s="40"/>
+      <c r="BG28" s="40"/>
       <c r="BH28" s="5"/>
       <c r="BI28" s="5"/>
       <c r="BJ28" s="5"/>
     </row>
-    <row r="29" spans="1:62" s="10" customFormat="1" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:62" s="9" customFormat="1" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5"/>
       <c r="B29" s="5"/>
-      <c r="C29" s="31" t="s">
+      <c r="C29" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="D29" s="31"/>
-      <c r="E29" s="31" t="s">
+      <c r="D29" s="38"/>
+      <c r="E29" s="38" t="s">
         <v>58</v>
       </c>
-      <c r="F29" s="31"/>
-      <c r="G29" s="31"/>
-      <c r="H29" s="31"/>
-      <c r="I29" s="31" t="s">
+      <c r="F29" s="38"/>
+      <c r="G29" s="38"/>
+      <c r="H29" s="38"/>
+      <c r="I29" s="38" t="s">
         <v>70</v>
       </c>
-      <c r="J29" s="31"/>
-      <c r="K29" s="31"/>
-      <c r="L29" s="31" t="s">
+      <c r="J29" s="38"/>
+      <c r="K29" s="38"/>
+      <c r="L29" s="38" t="s">
         <v>82</v>
       </c>
-      <c r="M29" s="31"/>
-      <c r="N29" s="31"/>
-      <c r="O29" s="31" t="s">
+      <c r="M29" s="38"/>
+      <c r="N29" s="38"/>
+      <c r="O29" s="38" t="s">
         <v>94</v>
       </c>
-      <c r="P29" s="31"/>
-      <c r="Q29" s="31"/>
-      <c r="R29" s="31"/>
-      <c r="S29" s="31"/>
-      <c r="T29" s="31"/>
-      <c r="U29" s="31"/>
-      <c r="V29" s="31"/>
-      <c r="W29" s="31"/>
-      <c r="X29" s="31"/>
-      <c r="Y29" s="31"/>
-      <c r="Z29" s="31"/>
-      <c r="AA29" s="31"/>
-      <c r="AB29" s="31"/>
-      <c r="AC29" s="31"/>
-      <c r="AD29" s="31"/>
-      <c r="AE29" s="31"/>
-      <c r="AF29" s="31"/>
-      <c r="AG29" s="31"/>
-      <c r="AH29" s="31"/>
-      <c r="AI29" s="31"/>
-      <c r="AJ29" s="31"/>
-      <c r="AK29" s="31"/>
-      <c r="AL29" s="31"/>
-      <c r="AM29" s="31"/>
-      <c r="AN29" s="30" t="s">
+      <c r="P29" s="38"/>
+      <c r="Q29" s="38"/>
+      <c r="R29" s="38"/>
+      <c r="S29" s="38"/>
+      <c r="T29" s="38"/>
+      <c r="U29" s="38"/>
+      <c r="V29" s="38"/>
+      <c r="W29" s="38"/>
+      <c r="X29" s="38"/>
+      <c r="Y29" s="38"/>
+      <c r="Z29" s="38"/>
+      <c r="AA29" s="38"/>
+      <c r="AB29" s="38"/>
+      <c r="AC29" s="38"/>
+      <c r="AD29" s="38"/>
+      <c r="AE29" s="38"/>
+      <c r="AF29" s="38"/>
+      <c r="AG29" s="38"/>
+      <c r="AH29" s="38"/>
+      <c r="AI29" s="38"/>
+      <c r="AJ29" s="38"/>
+      <c r="AK29" s="38"/>
+      <c r="AL29" s="38"/>
+      <c r="AM29" s="38"/>
+      <c r="AN29" s="37" t="s">
         <v>106</v>
       </c>
-      <c r="AO29" s="33"/>
-      <c r="AP29" s="33"/>
-      <c r="AQ29" s="31" t="s">
+      <c r="AO29" s="40"/>
+      <c r="AP29" s="40"/>
+      <c r="AQ29" s="38" t="s">
         <v>118</v>
       </c>
-      <c r="AR29" s="31"/>
-      <c r="AS29" s="31"/>
-      <c r="AT29" s="30" t="s">
+      <c r="AR29" s="38"/>
+      <c r="AS29" s="38"/>
+      <c r="AT29" s="37" t="s">
         <v>130</v>
       </c>
-      <c r="AU29" s="30"/>
-      <c r="AV29" s="30"/>
-      <c r="AW29" s="30"/>
-      <c r="AX29" s="30"/>
-      <c r="AY29" s="31" t="s">
+      <c r="AU29" s="37"/>
+      <c r="AV29" s="37"/>
+      <c r="AW29" s="37"/>
+      <c r="AX29" s="37"/>
+      <c r="AY29" s="38" t="s">
         <v>142</v>
       </c>
-      <c r="AZ29" s="32"/>
-      <c r="BA29" s="30" t="s">
+      <c r="AZ29" s="39"/>
+      <c r="BA29" s="37" t="s">
         <v>154</v>
       </c>
-      <c r="BB29" s="33"/>
-      <c r="BC29" s="33"/>
-      <c r="BD29" s="33"/>
-      <c r="BE29" s="33"/>
-      <c r="BF29" s="33"/>
-      <c r="BG29" s="33"/>
+      <c r="BB29" s="40"/>
+      <c r="BC29" s="40"/>
+      <c r="BD29" s="40"/>
+      <c r="BE29" s="40"/>
+      <c r="BF29" s="40"/>
+      <c r="BG29" s="40"/>
       <c r="BH29" s="5"/>
       <c r="BI29" s="5"/>
       <c r="BJ29" s="5"/>
     </row>
-    <row r="30" spans="1:62" s="10" customFormat="1" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:62" s="9" customFormat="1" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5"/>
       <c r="B30" s="5"/>
-      <c r="C30" s="31" t="s">
+      <c r="C30" s="38" t="s">
         <v>47</v>
       </c>
-      <c r="D30" s="31"/>
-      <c r="E30" s="31" t="s">
+      <c r="D30" s="38"/>
+      <c r="E30" s="38" t="s">
         <v>59</v>
       </c>
-      <c r="F30" s="31"/>
-      <c r="G30" s="31"/>
-      <c r="H30" s="31"/>
-      <c r="I30" s="31" t="s">
+      <c r="F30" s="38"/>
+      <c r="G30" s="38"/>
+      <c r="H30" s="38"/>
+      <c r="I30" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="J30" s="31"/>
-      <c r="K30" s="31"/>
-      <c r="L30" s="31" t="s">
+      <c r="J30" s="38"/>
+      <c r="K30" s="38"/>
+      <c r="L30" s="38" t="s">
         <v>83</v>
       </c>
-      <c r="M30" s="31"/>
-      <c r="N30" s="31"/>
-      <c r="O30" s="31" t="s">
+      <c r="M30" s="38"/>
+      <c r="N30" s="38"/>
+      <c r="O30" s="38" t="s">
         <v>95</v>
       </c>
-      <c r="P30" s="31"/>
-      <c r="Q30" s="31"/>
-      <c r="R30" s="31"/>
-      <c r="S30" s="31"/>
-      <c r="T30" s="31"/>
-      <c r="U30" s="31"/>
-      <c r="V30" s="31"/>
-      <c r="W30" s="31"/>
-      <c r="X30" s="31"/>
-      <c r="Y30" s="31"/>
-      <c r="Z30" s="31"/>
-      <c r="AA30" s="31"/>
-      <c r="AB30" s="31"/>
-      <c r="AC30" s="31"/>
-      <c r="AD30" s="31"/>
-      <c r="AE30" s="31"/>
-      <c r="AF30" s="31"/>
-      <c r="AG30" s="31"/>
-      <c r="AH30" s="31"/>
-      <c r="AI30" s="31"/>
-      <c r="AJ30" s="31"/>
-      <c r="AK30" s="31"/>
-      <c r="AL30" s="31"/>
-      <c r="AM30" s="31"/>
-      <c r="AN30" s="30" t="s">
+      <c r="P30" s="38"/>
+      <c r="Q30" s="38"/>
+      <c r="R30" s="38"/>
+      <c r="S30" s="38"/>
+      <c r="T30" s="38"/>
+      <c r="U30" s="38"/>
+      <c r="V30" s="38"/>
+      <c r="W30" s="38"/>
+      <c r="X30" s="38"/>
+      <c r="Y30" s="38"/>
+      <c r="Z30" s="38"/>
+      <c r="AA30" s="38"/>
+      <c r="AB30" s="38"/>
+      <c r="AC30" s="38"/>
+      <c r="AD30" s="38"/>
+      <c r="AE30" s="38"/>
+      <c r="AF30" s="38"/>
+      <c r="AG30" s="38"/>
+      <c r="AH30" s="38"/>
+      <c r="AI30" s="38"/>
+      <c r="AJ30" s="38"/>
+      <c r="AK30" s="38"/>
+      <c r="AL30" s="38"/>
+      <c r="AM30" s="38"/>
+      <c r="AN30" s="37" t="s">
         <v>107</v>
       </c>
-      <c r="AO30" s="33"/>
-      <c r="AP30" s="33"/>
-      <c r="AQ30" s="31" t="s">
+      <c r="AO30" s="40"/>
+      <c r="AP30" s="40"/>
+      <c r="AQ30" s="38" t="s">
         <v>119</v>
       </c>
-      <c r="AR30" s="31"/>
-      <c r="AS30" s="31"/>
-      <c r="AT30" s="30" t="s">
+      <c r="AR30" s="38"/>
+      <c r="AS30" s="38"/>
+      <c r="AT30" s="37" t="s">
         <v>131</v>
       </c>
-      <c r="AU30" s="30"/>
-      <c r="AV30" s="30"/>
-      <c r="AW30" s="30"/>
-      <c r="AX30" s="30"/>
-      <c r="AY30" s="31" t="s">
+      <c r="AU30" s="37"/>
+      <c r="AV30" s="37"/>
+      <c r="AW30" s="37"/>
+      <c r="AX30" s="37"/>
+      <c r="AY30" s="38" t="s">
         <v>143</v>
       </c>
-      <c r="AZ30" s="32"/>
-      <c r="BA30" s="30" t="s">
+      <c r="AZ30" s="39"/>
+      <c r="BA30" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="BB30" s="33"/>
-      <c r="BC30" s="33"/>
-      <c r="BD30" s="33"/>
-      <c r="BE30" s="33"/>
-      <c r="BF30" s="33"/>
-      <c r="BG30" s="33"/>
+      <c r="BB30" s="40"/>
+      <c r="BC30" s="40"/>
+      <c r="BD30" s="40"/>
+      <c r="BE30" s="40"/>
+      <c r="BF30" s="40"/>
+      <c r="BG30" s="40"/>
       <c r="BH30" s="5"/>
       <c r="BI30" s="5"/>
       <c r="BJ30" s="5"/>
     </row>
-    <row r="31" spans="1:62" s="10" customFormat="1" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:62" s="9" customFormat="1" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5"/>
       <c r="B31" s="5"/>
-      <c r="C31" s="31" t="s">
+      <c r="C31" s="38" t="s">
         <v>48</v>
       </c>
-      <c r="D31" s="31"/>
-      <c r="E31" s="31" t="s">
+      <c r="D31" s="38"/>
+      <c r="E31" s="38" t="s">
         <v>60</v>
       </c>
-      <c r="F31" s="31"/>
-      <c r="G31" s="31"/>
-      <c r="H31" s="31"/>
-      <c r="I31" s="31" t="s">
+      <c r="F31" s="38"/>
+      <c r="G31" s="38"/>
+      <c r="H31" s="38"/>
+      <c r="I31" s="38" t="s">
         <v>72</v>
       </c>
-      <c r="J31" s="31"/>
-      <c r="K31" s="31"/>
-      <c r="L31" s="31" t="s">
+      <c r="J31" s="38"/>
+      <c r="K31" s="38"/>
+      <c r="L31" s="38" t="s">
         <v>84</v>
       </c>
-      <c r="M31" s="31"/>
-      <c r="N31" s="31"/>
-      <c r="O31" s="31" t="s">
+      <c r="M31" s="38"/>
+      <c r="N31" s="38"/>
+      <c r="O31" s="38" t="s">
         <v>96</v>
       </c>
-      <c r="P31" s="31"/>
-      <c r="Q31" s="31"/>
-      <c r="R31" s="31"/>
-      <c r="S31" s="31"/>
-      <c r="T31" s="31"/>
-      <c r="U31" s="31"/>
-      <c r="V31" s="31"/>
-      <c r="W31" s="31"/>
-      <c r="X31" s="31"/>
-      <c r="Y31" s="31"/>
-      <c r="Z31" s="31"/>
-      <c r="AA31" s="31"/>
-      <c r="AB31" s="31"/>
-      <c r="AC31" s="31"/>
-      <c r="AD31" s="31"/>
-      <c r="AE31" s="31"/>
-      <c r="AF31" s="31"/>
-      <c r="AG31" s="31"/>
-      <c r="AH31" s="31"/>
-      <c r="AI31" s="31"/>
-      <c r="AJ31" s="31"/>
-      <c r="AK31" s="31"/>
-      <c r="AL31" s="31"/>
-      <c r="AM31" s="31"/>
-      <c r="AN31" s="30" t="s">
+      <c r="P31" s="38"/>
+      <c r="Q31" s="38"/>
+      <c r="R31" s="38"/>
+      <c r="S31" s="38"/>
+      <c r="T31" s="38"/>
+      <c r="U31" s="38"/>
+      <c r="V31" s="38"/>
+      <c r="W31" s="38"/>
+      <c r="X31" s="38"/>
+      <c r="Y31" s="38"/>
+      <c r="Z31" s="38"/>
+      <c r="AA31" s="38"/>
+      <c r="AB31" s="38"/>
+      <c r="AC31" s="38"/>
+      <c r="AD31" s="38"/>
+      <c r="AE31" s="38"/>
+      <c r="AF31" s="38"/>
+      <c r="AG31" s="38"/>
+      <c r="AH31" s="38"/>
+      <c r="AI31" s="38"/>
+      <c r="AJ31" s="38"/>
+      <c r="AK31" s="38"/>
+      <c r="AL31" s="38"/>
+      <c r="AM31" s="38"/>
+      <c r="AN31" s="37" t="s">
         <v>108</v>
       </c>
-      <c r="AO31" s="33"/>
-      <c r="AP31" s="33"/>
-      <c r="AQ31" s="31" t="s">
+      <c r="AO31" s="40"/>
+      <c r="AP31" s="40"/>
+      <c r="AQ31" s="38" t="s">
         <v>120</v>
       </c>
-      <c r="AR31" s="31"/>
-      <c r="AS31" s="31"/>
-      <c r="AT31" s="30" t="s">
+      <c r="AR31" s="38"/>
+      <c r="AS31" s="38"/>
+      <c r="AT31" s="37" t="s">
         <v>132</v>
       </c>
-      <c r="AU31" s="30"/>
-      <c r="AV31" s="30"/>
-      <c r="AW31" s="30"/>
-      <c r="AX31" s="30"/>
-      <c r="AY31" s="31" t="s">
+      <c r="AU31" s="37"/>
+      <c r="AV31" s="37"/>
+      <c r="AW31" s="37"/>
+      <c r="AX31" s="37"/>
+      <c r="AY31" s="38" t="s">
         <v>144</v>
       </c>
-      <c r="AZ31" s="32"/>
-      <c r="BA31" s="30" t="s">
+      <c r="AZ31" s="39"/>
+      <c r="BA31" s="37" t="s">
         <v>156</v>
       </c>
-      <c r="BB31" s="33"/>
-      <c r="BC31" s="33"/>
-      <c r="BD31" s="33"/>
-      <c r="BE31" s="33"/>
-      <c r="BF31" s="33"/>
-      <c r="BG31" s="33"/>
+      <c r="BB31" s="40"/>
+      <c r="BC31" s="40"/>
+      <c r="BD31" s="40"/>
+      <c r="BE31" s="40"/>
+      <c r="BF31" s="40"/>
+      <c r="BG31" s="40"/>
       <c r="BH31" s="5"/>
       <c r="BI31" s="5"/>
       <c r="BJ31" s="5"/>
     </row>
-    <row r="32" spans="1:62" s="10" customFormat="1" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:62" s="9" customFormat="1" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5"/>
       <c r="B32" s="5"/>
-      <c r="C32" s="31" t="s">
+      <c r="C32" s="38" t="s">
         <v>49</v>
       </c>
-      <c r="D32" s="31"/>
-      <c r="E32" s="31" t="s">
+      <c r="D32" s="38"/>
+      <c r="E32" s="38" t="s">
         <v>61</v>
       </c>
-      <c r="F32" s="31"/>
-      <c r="G32" s="31"/>
-      <c r="H32" s="31"/>
-      <c r="I32" s="31" t="s">
+      <c r="F32" s="38"/>
+      <c r="G32" s="38"/>
+      <c r="H32" s="38"/>
+      <c r="I32" s="38" t="s">
         <v>73</v>
       </c>
-      <c r="J32" s="31"/>
-      <c r="K32" s="31"/>
-      <c r="L32" s="31" t="s">
+      <c r="J32" s="38"/>
+      <c r="K32" s="38"/>
+      <c r="L32" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="M32" s="31"/>
-      <c r="N32" s="31"/>
-      <c r="O32" s="31" t="s">
+      <c r="M32" s="38"/>
+      <c r="N32" s="38"/>
+      <c r="O32" s="38" t="s">
         <v>97</v>
       </c>
-      <c r="P32" s="31"/>
-      <c r="Q32" s="31"/>
-      <c r="R32" s="31"/>
-      <c r="S32" s="31"/>
-      <c r="T32" s="31"/>
-      <c r="U32" s="31"/>
-      <c r="V32" s="31"/>
-      <c r="W32" s="31"/>
-      <c r="X32" s="31"/>
-      <c r="Y32" s="31"/>
-      <c r="Z32" s="31"/>
-      <c r="AA32" s="31"/>
-      <c r="AB32" s="31"/>
-      <c r="AC32" s="31"/>
-      <c r="AD32" s="31"/>
-      <c r="AE32" s="31"/>
-      <c r="AF32" s="31"/>
-      <c r="AG32" s="31"/>
-      <c r="AH32" s="31"/>
-      <c r="AI32" s="31"/>
-      <c r="AJ32" s="31"/>
-      <c r="AK32" s="31"/>
-      <c r="AL32" s="31"/>
-      <c r="AM32" s="31"/>
-      <c r="AN32" s="30" t="s">
+      <c r="P32" s="38"/>
+      <c r="Q32" s="38"/>
+      <c r="R32" s="38"/>
+      <c r="S32" s="38"/>
+      <c r="T32" s="38"/>
+      <c r="U32" s="38"/>
+      <c r="V32" s="38"/>
+      <c r="W32" s="38"/>
+      <c r="X32" s="38"/>
+      <c r="Y32" s="38"/>
+      <c r="Z32" s="38"/>
+      <c r="AA32" s="38"/>
+      <c r="AB32" s="38"/>
+      <c r="AC32" s="38"/>
+      <c r="AD32" s="38"/>
+      <c r="AE32" s="38"/>
+      <c r="AF32" s="38"/>
+      <c r="AG32" s="38"/>
+      <c r="AH32" s="38"/>
+      <c r="AI32" s="38"/>
+      <c r="AJ32" s="38"/>
+      <c r="AK32" s="38"/>
+      <c r="AL32" s="38"/>
+      <c r="AM32" s="38"/>
+      <c r="AN32" s="37" t="s">
         <v>109</v>
       </c>
-      <c r="AO32" s="33"/>
-      <c r="AP32" s="33"/>
-      <c r="AQ32" s="31" t="s">
+      <c r="AO32" s="40"/>
+      <c r="AP32" s="40"/>
+      <c r="AQ32" s="38" t="s">
         <v>121</v>
       </c>
-      <c r="AR32" s="31"/>
-      <c r="AS32" s="31"/>
-      <c r="AT32" s="30" t="s">
+      <c r="AR32" s="38"/>
+      <c r="AS32" s="38"/>
+      <c r="AT32" s="37" t="s">
         <v>133</v>
       </c>
-      <c r="AU32" s="30"/>
-      <c r="AV32" s="30"/>
-      <c r="AW32" s="30"/>
-      <c r="AX32" s="30"/>
-      <c r="AY32" s="31" t="s">
+      <c r="AU32" s="37"/>
+      <c r="AV32" s="37"/>
+      <c r="AW32" s="37"/>
+      <c r="AX32" s="37"/>
+      <c r="AY32" s="38" t="s">
         <v>145</v>
       </c>
-      <c r="AZ32" s="32"/>
-      <c r="BA32" s="30" t="s">
+      <c r="AZ32" s="39"/>
+      <c r="BA32" s="37" t="s">
         <v>157</v>
       </c>
-      <c r="BB32" s="33"/>
-      <c r="BC32" s="33"/>
-      <c r="BD32" s="33"/>
-      <c r="BE32" s="33"/>
-      <c r="BF32" s="33"/>
-      <c r="BG32" s="33"/>
+      <c r="BB32" s="40"/>
+      <c r="BC32" s="40"/>
+      <c r="BD32" s="40"/>
+      <c r="BE32" s="40"/>
+      <c r="BF32" s="40"/>
+      <c r="BG32" s="40"/>
       <c r="BH32" s="5"/>
       <c r="BI32" s="5"/>
       <c r="BJ32" s="5"/>
     </row>
-    <row r="33" spans="1:63" s="10" customFormat="1" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:63" s="9" customFormat="1" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5"/>
       <c r="B33" s="5"/>
-      <c r="C33" s="31" t="s">
+      <c r="C33" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="D33" s="31"/>
-      <c r="E33" s="31" t="s">
+      <c r="D33" s="38"/>
+      <c r="E33" s="38" t="s">
         <v>62</v>
       </c>
-      <c r="F33" s="31"/>
-      <c r="G33" s="31"/>
-      <c r="H33" s="31"/>
-      <c r="I33" s="31" t="s">
+      <c r="F33" s="38"/>
+      <c r="G33" s="38"/>
+      <c r="H33" s="38"/>
+      <c r="I33" s="38" t="s">
         <v>74</v>
       </c>
-      <c r="J33" s="31"/>
-      <c r="K33" s="31"/>
-      <c r="L33" s="31" t="s">
+      <c r="J33" s="38"/>
+      <c r="K33" s="38"/>
+      <c r="L33" s="38" t="s">
         <v>86</v>
       </c>
-      <c r="M33" s="31"/>
-      <c r="N33" s="31"/>
-      <c r="O33" s="31" t="s">
+      <c r="M33" s="38"/>
+      <c r="N33" s="38"/>
+      <c r="O33" s="38" t="s">
         <v>98</v>
       </c>
-      <c r="P33" s="31"/>
-      <c r="Q33" s="31"/>
-      <c r="R33" s="31"/>
-      <c r="S33" s="31"/>
-      <c r="T33" s="31"/>
-      <c r="U33" s="31"/>
-      <c r="V33" s="31"/>
-      <c r="W33" s="31"/>
-      <c r="X33" s="31"/>
-      <c r="Y33" s="31"/>
-      <c r="Z33" s="31"/>
-      <c r="AA33" s="31"/>
-      <c r="AB33" s="31"/>
-      <c r="AC33" s="31"/>
-      <c r="AD33" s="31"/>
-      <c r="AE33" s="31"/>
-      <c r="AF33" s="31"/>
-      <c r="AG33" s="31"/>
-      <c r="AH33" s="31"/>
-      <c r="AI33" s="31"/>
-      <c r="AJ33" s="31"/>
-      <c r="AK33" s="31"/>
-      <c r="AL33" s="31"/>
-      <c r="AM33" s="31"/>
-      <c r="AN33" s="30" t="s">
+      <c r="P33" s="38"/>
+      <c r="Q33" s="38"/>
+      <c r="R33" s="38"/>
+      <c r="S33" s="38"/>
+      <c r="T33" s="38"/>
+      <c r="U33" s="38"/>
+      <c r="V33" s="38"/>
+      <c r="W33" s="38"/>
+      <c r="X33" s="38"/>
+      <c r="Y33" s="38"/>
+      <c r="Z33" s="38"/>
+      <c r="AA33" s="38"/>
+      <c r="AB33" s="38"/>
+      <c r="AC33" s="38"/>
+      <c r="AD33" s="38"/>
+      <c r="AE33" s="38"/>
+      <c r="AF33" s="38"/>
+      <c r="AG33" s="38"/>
+      <c r="AH33" s="38"/>
+      <c r="AI33" s="38"/>
+      <c r="AJ33" s="38"/>
+      <c r="AK33" s="38"/>
+      <c r="AL33" s="38"/>
+      <c r="AM33" s="38"/>
+      <c r="AN33" s="37" t="s">
         <v>110</v>
       </c>
-      <c r="AO33" s="33"/>
-      <c r="AP33" s="33"/>
-      <c r="AQ33" s="31" t="s">
+      <c r="AO33" s="40"/>
+      <c r="AP33" s="40"/>
+      <c r="AQ33" s="38" t="s">
         <v>122</v>
       </c>
-      <c r="AR33" s="31"/>
-      <c r="AS33" s="31"/>
-      <c r="AT33" s="30" t="s">
+      <c r="AR33" s="38"/>
+      <c r="AS33" s="38"/>
+      <c r="AT33" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="AU33" s="30"/>
-      <c r="AV33" s="30"/>
-      <c r="AW33" s="30"/>
-      <c r="AX33" s="30"/>
-      <c r="AY33" s="31" t="s">
+      <c r="AU33" s="37"/>
+      <c r="AV33" s="37"/>
+      <c r="AW33" s="37"/>
+      <c r="AX33" s="37"/>
+      <c r="AY33" s="38" t="s">
         <v>146</v>
       </c>
-      <c r="AZ33" s="32"/>
-      <c r="BA33" s="30" t="s">
+      <c r="AZ33" s="39"/>
+      <c r="BA33" s="37" t="s">
         <v>158</v>
       </c>
-      <c r="BB33" s="33"/>
-      <c r="BC33" s="33"/>
-      <c r="BD33" s="33"/>
-      <c r="BE33" s="33"/>
-      <c r="BF33" s="33"/>
-      <c r="BG33" s="33"/>
+      <c r="BB33" s="40"/>
+      <c r="BC33" s="40"/>
+      <c r="BD33" s="40"/>
+      <c r="BE33" s="40"/>
+      <c r="BF33" s="40"/>
+      <c r="BG33" s="40"/>
       <c r="BH33" s="5"/>
       <c r="BI33" s="5"/>
       <c r="BJ33" s="5"/>
     </row>
-    <row r="34" spans="1:63" s="10" customFormat="1" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:63" s="9" customFormat="1" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5"/>
       <c r="B34" s="5"/>
-      <c r="C34" s="31" t="s">
+      <c r="C34" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="D34" s="31"/>
-      <c r="E34" s="31" t="s">
+      <c r="D34" s="38"/>
+      <c r="E34" s="38" t="s">
         <v>63</v>
       </c>
-      <c r="F34" s="31"/>
-      <c r="G34" s="31"/>
-      <c r="H34" s="31"/>
-      <c r="I34" s="31" t="s">
+      <c r="F34" s="38"/>
+      <c r="G34" s="38"/>
+      <c r="H34" s="38"/>
+      <c r="I34" s="38" t="s">
         <v>75</v>
       </c>
-      <c r="J34" s="31"/>
-      <c r="K34" s="31"/>
-      <c r="L34" s="31" t="s">
+      <c r="J34" s="38"/>
+      <c r="K34" s="38"/>
+      <c r="L34" s="38" t="s">
         <v>87</v>
       </c>
-      <c r="M34" s="31"/>
-      <c r="N34" s="31"/>
-      <c r="O34" s="31" t="s">
+      <c r="M34" s="38"/>
+      <c r="N34" s="38"/>
+      <c r="O34" s="38" t="s">
         <v>99</v>
       </c>
-      <c r="P34" s="31"/>
-      <c r="Q34" s="31"/>
-      <c r="R34" s="31"/>
-      <c r="S34" s="31"/>
-      <c r="T34" s="31"/>
-      <c r="U34" s="31"/>
-      <c r="V34" s="31"/>
-      <c r="W34" s="31"/>
-      <c r="X34" s="31"/>
-      <c r="Y34" s="31"/>
-      <c r="Z34" s="31"/>
-      <c r="AA34" s="31"/>
-      <c r="AB34" s="31"/>
-      <c r="AC34" s="31"/>
-      <c r="AD34" s="31"/>
-      <c r="AE34" s="31"/>
-      <c r="AF34" s="31"/>
-      <c r="AG34" s="31"/>
-      <c r="AH34" s="31"/>
-      <c r="AI34" s="31"/>
-      <c r="AJ34" s="31"/>
-      <c r="AK34" s="31"/>
-      <c r="AL34" s="31"/>
-      <c r="AM34" s="31"/>
-      <c r="AN34" s="30" t="s">
+      <c r="P34" s="38"/>
+      <c r="Q34" s="38"/>
+      <c r="R34" s="38"/>
+      <c r="S34" s="38"/>
+      <c r="T34" s="38"/>
+      <c r="U34" s="38"/>
+      <c r="V34" s="38"/>
+      <c r="W34" s="38"/>
+      <c r="X34" s="38"/>
+      <c r="Y34" s="38"/>
+      <c r="Z34" s="38"/>
+      <c r="AA34" s="38"/>
+      <c r="AB34" s="38"/>
+      <c r="AC34" s="38"/>
+      <c r="AD34" s="38"/>
+      <c r="AE34" s="38"/>
+      <c r="AF34" s="38"/>
+      <c r="AG34" s="38"/>
+      <c r="AH34" s="38"/>
+      <c r="AI34" s="38"/>
+      <c r="AJ34" s="38"/>
+      <c r="AK34" s="38"/>
+      <c r="AL34" s="38"/>
+      <c r="AM34" s="38"/>
+      <c r="AN34" s="37" t="s">
         <v>111</v>
       </c>
-      <c r="AO34" s="33"/>
-      <c r="AP34" s="33"/>
-      <c r="AQ34" s="31" t="s">
+      <c r="AO34" s="40"/>
+      <c r="AP34" s="40"/>
+      <c r="AQ34" s="38" t="s">
         <v>123</v>
       </c>
-      <c r="AR34" s="31"/>
-      <c r="AS34" s="31"/>
-      <c r="AT34" s="30" t="s">
+      <c r="AR34" s="38"/>
+      <c r="AS34" s="38"/>
+      <c r="AT34" s="37" t="s">
         <v>135</v>
       </c>
-      <c r="AU34" s="30"/>
-      <c r="AV34" s="30"/>
-      <c r="AW34" s="30"/>
-      <c r="AX34" s="30"/>
-      <c r="AY34" s="31" t="s">
+      <c r="AU34" s="37"/>
+      <c r="AV34" s="37"/>
+      <c r="AW34" s="37"/>
+      <c r="AX34" s="37"/>
+      <c r="AY34" s="38" t="s">
         <v>147</v>
       </c>
-      <c r="AZ34" s="32"/>
-      <c r="BA34" s="30" t="s">
+      <c r="AZ34" s="39"/>
+      <c r="BA34" s="37" t="s">
         <v>159</v>
       </c>
-      <c r="BB34" s="33"/>
-      <c r="BC34" s="33"/>
-      <c r="BD34" s="33"/>
-      <c r="BE34" s="33"/>
-      <c r="BF34" s="33"/>
-      <c r="BG34" s="33"/>
+      <c r="BB34" s="40"/>
+      <c r="BC34" s="40"/>
+      <c r="BD34" s="40"/>
+      <c r="BE34" s="40"/>
+      <c r="BF34" s="40"/>
+      <c r="BG34" s="40"/>
       <c r="BH34" s="5"/>
       <c r="BI34" s="5"/>
       <c r="BJ34" s="5"/>
     </row>
-    <row r="35" spans="1:63" s="10" customFormat="1" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:63" s="9" customFormat="1" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="5"/>
       <c r="B35" s="5"/>
-      <c r="C35" s="31" t="s">
+      <c r="C35" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="D35" s="31"/>
-      <c r="E35" s="31" t="s">
+      <c r="D35" s="38"/>
+      <c r="E35" s="38" t="s">
         <v>64</v>
       </c>
-      <c r="F35" s="31"/>
-      <c r="G35" s="31"/>
-      <c r="H35" s="31"/>
-      <c r="I35" s="31" t="s">
+      <c r="F35" s="38"/>
+      <c r="G35" s="38"/>
+      <c r="H35" s="38"/>
+      <c r="I35" s="38" t="s">
         <v>76</v>
       </c>
-      <c r="J35" s="31"/>
-      <c r="K35" s="31"/>
-      <c r="L35" s="31" t="s">
+      <c r="J35" s="38"/>
+      <c r="K35" s="38"/>
+      <c r="L35" s="38" t="s">
         <v>88</v>
       </c>
-      <c r="M35" s="31"/>
-      <c r="N35" s="31"/>
-      <c r="O35" s="31" t="s">
+      <c r="M35" s="38"/>
+      <c r="N35" s="38"/>
+      <c r="O35" s="38" t="s">
         <v>100</v>
       </c>
-      <c r="P35" s="31"/>
-      <c r="Q35" s="31"/>
-      <c r="R35" s="31"/>
-      <c r="S35" s="31"/>
-      <c r="T35" s="31"/>
-      <c r="U35" s="31"/>
-      <c r="V35" s="31"/>
-      <c r="W35" s="31"/>
-      <c r="X35" s="31"/>
-      <c r="Y35" s="31"/>
-      <c r="Z35" s="31"/>
-      <c r="AA35" s="31"/>
-      <c r="AB35" s="31"/>
-      <c r="AC35" s="31"/>
-      <c r="AD35" s="31"/>
-      <c r="AE35" s="31"/>
-      <c r="AF35" s="31"/>
-      <c r="AG35" s="31"/>
-      <c r="AH35" s="31"/>
-      <c r="AI35" s="31"/>
-      <c r="AJ35" s="31"/>
-      <c r="AK35" s="31"/>
-      <c r="AL35" s="31"/>
-      <c r="AM35" s="31"/>
-      <c r="AN35" s="30" t="s">
+      <c r="P35" s="38"/>
+      <c r="Q35" s="38"/>
+      <c r="R35" s="38"/>
+      <c r="S35" s="38"/>
+      <c r="T35" s="38"/>
+      <c r="U35" s="38"/>
+      <c r="V35" s="38"/>
+      <c r="W35" s="38"/>
+      <c r="X35" s="38"/>
+      <c r="Y35" s="38"/>
+      <c r="Z35" s="38"/>
+      <c r="AA35" s="38"/>
+      <c r="AB35" s="38"/>
+      <c r="AC35" s="38"/>
+      <c r="AD35" s="38"/>
+      <c r="AE35" s="38"/>
+      <c r="AF35" s="38"/>
+      <c r="AG35" s="38"/>
+      <c r="AH35" s="38"/>
+      <c r="AI35" s="38"/>
+      <c r="AJ35" s="38"/>
+      <c r="AK35" s="38"/>
+      <c r="AL35" s="38"/>
+      <c r="AM35" s="38"/>
+      <c r="AN35" s="37" t="s">
         <v>112</v>
       </c>
-      <c r="AO35" s="33"/>
-      <c r="AP35" s="33"/>
-      <c r="AQ35" s="31" t="s">
+      <c r="AO35" s="40"/>
+      <c r="AP35" s="40"/>
+      <c r="AQ35" s="38" t="s">
         <v>124</v>
       </c>
-      <c r="AR35" s="31"/>
-      <c r="AS35" s="31"/>
-      <c r="AT35" s="30" t="s">
+      <c r="AR35" s="38"/>
+      <c r="AS35" s="38"/>
+      <c r="AT35" s="37" t="s">
         <v>136</v>
       </c>
-      <c r="AU35" s="30"/>
-      <c r="AV35" s="30"/>
-      <c r="AW35" s="30"/>
-      <c r="AX35" s="30"/>
-      <c r="AY35" s="31" t="s">
+      <c r="AU35" s="37"/>
+      <c r="AV35" s="37"/>
+      <c r="AW35" s="37"/>
+      <c r="AX35" s="37"/>
+      <c r="AY35" s="38" t="s">
         <v>148</v>
       </c>
-      <c r="AZ35" s="32"/>
-      <c r="BA35" s="30" t="s">
+      <c r="AZ35" s="39"/>
+      <c r="BA35" s="37" t="s">
         <v>160</v>
       </c>
-      <c r="BB35" s="33"/>
-      <c r="BC35" s="33"/>
-      <c r="BD35" s="33"/>
-      <c r="BE35" s="33"/>
-      <c r="BF35" s="33"/>
-      <c r="BG35" s="33"/>
+      <c r="BB35" s="40"/>
+      <c r="BC35" s="40"/>
+      <c r="BD35" s="40"/>
+      <c r="BE35" s="40"/>
+      <c r="BF35" s="40"/>
+      <c r="BG35" s="40"/>
       <c r="BH35" s="5"/>
       <c r="BI35" s="5"/>
       <c r="BJ35" s="5"/>
-      <c r="BK35" s="11"/>
-    </row>
-    <row r="36" spans="1:63" s="10" customFormat="1" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BK35" s="10"/>
+    </row>
+    <row r="36" spans="1:63" s="9" customFormat="1" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="5"/>
       <c r="B36" s="5"/>
-      <c r="C36" s="31" t="s">
+      <c r="C36" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="D36" s="31"/>
-      <c r="E36" s="31" t="s">
+      <c r="D36" s="38"/>
+      <c r="E36" s="38" t="s">
         <v>65</v>
       </c>
-      <c r="F36" s="31"/>
-      <c r="G36" s="31"/>
-      <c r="H36" s="31"/>
-      <c r="I36" s="31" t="s">
+      <c r="F36" s="38"/>
+      <c r="G36" s="38"/>
+      <c r="H36" s="38"/>
+      <c r="I36" s="38" t="s">
         <v>77</v>
       </c>
-      <c r="J36" s="31"/>
-      <c r="K36" s="31"/>
-      <c r="L36" s="31" t="s">
+      <c r="J36" s="38"/>
+      <c r="K36" s="38"/>
+      <c r="L36" s="38" t="s">
         <v>89</v>
       </c>
-      <c r="M36" s="31"/>
-      <c r="N36" s="31"/>
-      <c r="O36" s="31" t="s">
+      <c r="M36" s="38"/>
+      <c r="N36" s="38"/>
+      <c r="O36" s="38" t="s">
         <v>101</v>
       </c>
-      <c r="P36" s="31"/>
-      <c r="Q36" s="31"/>
-      <c r="R36" s="31"/>
-      <c r="S36" s="31"/>
-      <c r="T36" s="31"/>
-      <c r="U36" s="31"/>
-      <c r="V36" s="31"/>
-      <c r="W36" s="31"/>
-      <c r="X36" s="31"/>
-      <c r="Y36" s="31"/>
-      <c r="Z36" s="31"/>
-      <c r="AA36" s="31"/>
-      <c r="AB36" s="31"/>
-      <c r="AC36" s="31"/>
-      <c r="AD36" s="31"/>
-      <c r="AE36" s="31"/>
-      <c r="AF36" s="31"/>
-      <c r="AG36" s="31"/>
-      <c r="AH36" s="31"/>
-      <c r="AI36" s="31"/>
-      <c r="AJ36" s="31"/>
-      <c r="AK36" s="31"/>
-      <c r="AL36" s="31"/>
-      <c r="AM36" s="31"/>
-      <c r="AN36" s="30" t="s">
+      <c r="P36" s="38"/>
+      <c r="Q36" s="38"/>
+      <c r="R36" s="38"/>
+      <c r="S36" s="38"/>
+      <c r="T36" s="38"/>
+      <c r="U36" s="38"/>
+      <c r="V36" s="38"/>
+      <c r="W36" s="38"/>
+      <c r="X36" s="38"/>
+      <c r="Y36" s="38"/>
+      <c r="Z36" s="38"/>
+      <c r="AA36" s="38"/>
+      <c r="AB36" s="38"/>
+      <c r="AC36" s="38"/>
+      <c r="AD36" s="38"/>
+      <c r="AE36" s="38"/>
+      <c r="AF36" s="38"/>
+      <c r="AG36" s="38"/>
+      <c r="AH36" s="38"/>
+      <c r="AI36" s="38"/>
+      <c r="AJ36" s="38"/>
+      <c r="AK36" s="38"/>
+      <c r="AL36" s="38"/>
+      <c r="AM36" s="38"/>
+      <c r="AN36" s="37" t="s">
         <v>113</v>
       </c>
-      <c r="AO36" s="33"/>
-      <c r="AP36" s="33"/>
-      <c r="AQ36" s="31" t="s">
+      <c r="AO36" s="40"/>
+      <c r="AP36" s="40"/>
+      <c r="AQ36" s="38" t="s">
         <v>125</v>
       </c>
-      <c r="AR36" s="31"/>
-      <c r="AS36" s="31"/>
-      <c r="AT36" s="30" t="s">
+      <c r="AR36" s="38"/>
+      <c r="AS36" s="38"/>
+      <c r="AT36" s="37" t="s">
         <v>137</v>
       </c>
-      <c r="AU36" s="30"/>
-      <c r="AV36" s="30"/>
-      <c r="AW36" s="30"/>
-      <c r="AX36" s="30"/>
-      <c r="AY36" s="31" t="s">
+      <c r="AU36" s="37"/>
+      <c r="AV36" s="37"/>
+      <c r="AW36" s="37"/>
+      <c r="AX36" s="37"/>
+      <c r="AY36" s="38" t="s">
         <v>149</v>
       </c>
-      <c r="AZ36" s="32"/>
-      <c r="BA36" s="30" t="s">
+      <c r="AZ36" s="39"/>
+      <c r="BA36" s="37" t="s">
         <v>161</v>
       </c>
-      <c r="BB36" s="33"/>
-      <c r="BC36" s="33"/>
-      <c r="BD36" s="33"/>
-      <c r="BE36" s="33"/>
-      <c r="BF36" s="33"/>
-      <c r="BG36" s="33"/>
+      <c r="BB36" s="40"/>
+      <c r="BC36" s="40"/>
+      <c r="BD36" s="40"/>
+      <c r="BE36" s="40"/>
+      <c r="BF36" s="40"/>
+      <c r="BG36" s="40"/>
       <c r="BH36" s="5"/>
       <c r="BI36" s="5"/>
       <c r="BJ36" s="5"/>
     </row>
-    <row r="37" spans="1:63" s="10" customFormat="1" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:63" s="9" customFormat="1" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="5"/>
       <c r="B37" s="5"/>
-      <c r="C37" s="31" t="s">
+      <c r="C37" s="38" t="s">
         <v>54</v>
       </c>
-      <c r="D37" s="31"/>
-      <c r="E37" s="31" t="s">
+      <c r="D37" s="38"/>
+      <c r="E37" s="38" t="s">
         <v>66</v>
       </c>
-      <c r="F37" s="31"/>
-      <c r="G37" s="31"/>
-      <c r="H37" s="31"/>
-      <c r="I37" s="31" t="s">
+      <c r="F37" s="38"/>
+      <c r="G37" s="38"/>
+      <c r="H37" s="38"/>
+      <c r="I37" s="38" t="s">
         <v>78</v>
       </c>
-      <c r="J37" s="31"/>
-      <c r="K37" s="31"/>
-      <c r="L37" s="31" t="s">
+      <c r="J37" s="38"/>
+      <c r="K37" s="38"/>
+      <c r="L37" s="38" t="s">
         <v>90</v>
       </c>
-      <c r="M37" s="31"/>
-      <c r="N37" s="31"/>
-      <c r="O37" s="31" t="s">
+      <c r="M37" s="38"/>
+      <c r="N37" s="38"/>
+      <c r="O37" s="38" t="s">
         <v>102</v>
       </c>
-      <c r="P37" s="31"/>
-      <c r="Q37" s="31"/>
-      <c r="R37" s="31"/>
-      <c r="S37" s="31"/>
-      <c r="T37" s="31"/>
-      <c r="U37" s="31"/>
-      <c r="V37" s="31"/>
-      <c r="W37" s="31"/>
-      <c r="X37" s="31"/>
-      <c r="Y37" s="31"/>
-      <c r="Z37" s="31"/>
-      <c r="AA37" s="31"/>
-      <c r="AB37" s="31"/>
-      <c r="AC37" s="31"/>
-      <c r="AD37" s="31"/>
-      <c r="AE37" s="31"/>
-      <c r="AF37" s="31"/>
-      <c r="AG37" s="31"/>
-      <c r="AH37" s="31"/>
-      <c r="AI37" s="31"/>
-      <c r="AJ37" s="31"/>
-      <c r="AK37" s="31"/>
-      <c r="AL37" s="31"/>
-      <c r="AM37" s="31"/>
-      <c r="AN37" s="30" t="s">
+      <c r="P37" s="38"/>
+      <c r="Q37" s="38"/>
+      <c r="R37" s="38"/>
+      <c r="S37" s="38"/>
+      <c r="T37" s="38"/>
+      <c r="U37" s="38"/>
+      <c r="V37" s="38"/>
+      <c r="W37" s="38"/>
+      <c r="X37" s="38"/>
+      <c r="Y37" s="38"/>
+      <c r="Z37" s="38"/>
+      <c r="AA37" s="38"/>
+      <c r="AB37" s="38"/>
+      <c r="AC37" s="38"/>
+      <c r="AD37" s="38"/>
+      <c r="AE37" s="38"/>
+      <c r="AF37" s="38"/>
+      <c r="AG37" s="38"/>
+      <c r="AH37" s="38"/>
+      <c r="AI37" s="38"/>
+      <c r="AJ37" s="38"/>
+      <c r="AK37" s="38"/>
+      <c r="AL37" s="38"/>
+      <c r="AM37" s="38"/>
+      <c r="AN37" s="37" t="s">
         <v>114</v>
       </c>
-      <c r="AO37" s="33"/>
-      <c r="AP37" s="33"/>
-      <c r="AQ37" s="31" t="s">
+      <c r="AO37" s="40"/>
+      <c r="AP37" s="40"/>
+      <c r="AQ37" s="38" t="s">
         <v>126</v>
       </c>
-      <c r="AR37" s="31"/>
-      <c r="AS37" s="31"/>
-      <c r="AT37" s="30" t="s">
+      <c r="AR37" s="38"/>
+      <c r="AS37" s="38"/>
+      <c r="AT37" s="37" t="s">
         <v>138</v>
       </c>
-      <c r="AU37" s="30"/>
-      <c r="AV37" s="30"/>
-      <c r="AW37" s="30"/>
-      <c r="AX37" s="30"/>
-      <c r="AY37" s="31" t="s">
+      <c r="AU37" s="37"/>
+      <c r="AV37" s="37"/>
+      <c r="AW37" s="37"/>
+      <c r="AX37" s="37"/>
+      <c r="AY37" s="38" t="s">
         <v>150</v>
       </c>
-      <c r="AZ37" s="32"/>
-      <c r="BA37" s="30" t="s">
+      <c r="AZ37" s="39"/>
+      <c r="BA37" s="37" t="s">
         <v>162</v>
       </c>
-      <c r="BB37" s="33"/>
-      <c r="BC37" s="33"/>
-      <c r="BD37" s="33"/>
-      <c r="BE37" s="33"/>
-      <c r="BF37" s="33"/>
-      <c r="BG37" s="33"/>
+      <c r="BB37" s="40"/>
+      <c r="BC37" s="40"/>
+      <c r="BD37" s="40"/>
+      <c r="BE37" s="40"/>
+      <c r="BF37" s="40"/>
+      <c r="BG37" s="40"/>
       <c r="BH37" s="5"/>
       <c r="BI37" s="5"/>
       <c r="BJ37" s="5"/>
@@ -4402,35 +4399,35 @@
       <c r="AJ39" s="7"/>
       <c r="AK39" s="7"/>
       <c r="AL39" s="7"/>
-      <c r="AM39" s="34" t="s">
+      <c r="AM39" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="AN39" s="20"/>
-      <c r="AO39" s="20"/>
-      <c r="AP39" s="21"/>
+      <c r="AN39" s="18"/>
+      <c r="AO39" s="18"/>
+      <c r="AP39" s="19"/>
       <c r="AQ39" s="4"/>
       <c r="AR39" s="4"/>
       <c r="AS39" s="4"/>
-      <c r="AT39" s="35" t="s">
+      <c r="AT39" s="42" t="s">
         <v>163</v>
       </c>
-      <c r="AU39" s="36"/>
-      <c r="AV39" s="36"/>
-      <c r="AW39" s="36"/>
-      <c r="AX39" s="36"/>
-      <c r="AY39" s="37" t="s">
+      <c r="AU39" s="43"/>
+      <c r="AV39" s="43"/>
+      <c r="AW39" s="43"/>
+      <c r="AX39" s="43"/>
+      <c r="AY39" s="44" t="s">
         <v>164</v>
       </c>
-      <c r="AZ39" s="36"/>
-      <c r="BA39" s="35" t="s">
+      <c r="AZ39" s="43"/>
+      <c r="BA39" s="42" t="s">
         <v>165</v>
       </c>
-      <c r="BB39" s="36"/>
-      <c r="BC39" s="36"/>
-      <c r="BD39" s="36"/>
-      <c r="BE39" s="36"/>
-      <c r="BF39" s="36"/>
-      <c r="BG39" s="36"/>
+      <c r="BB39" s="43"/>
+      <c r="BC39" s="43"/>
+      <c r="BD39" s="43"/>
+      <c r="BE39" s="43"/>
+      <c r="BF39" s="43"/>
+      <c r="BG39" s="43"/>
       <c r="BH39" s="7"/>
       <c r="BI39" s="7"/>
       <c r="BJ39" s="7"/>
@@ -4502,67 +4499,67 @@
     <row r="41" spans="1:63" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="7"/>
       <c r="B41" s="7"/>
-      <c r="C41" s="27" t="s">
+      <c r="C41" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="D41" s="16"/>
-      <c r="E41" s="16"/>
-      <c r="F41" s="16"/>
-      <c r="G41" s="17"/>
+      <c r="D41" s="14"/>
+      <c r="E41" s="14"/>
+      <c r="F41" s="14"/>
+      <c r="G41" s="15"/>
       <c r="H41" s="7"/>
-      <c r="I41" s="38"/>
-      <c r="J41" s="25"/>
-      <c r="K41" s="25"/>
-      <c r="L41" s="25"/>
-      <c r="M41" s="25"/>
-      <c r="N41" s="25"/>
-      <c r="O41" s="25"/>
-      <c r="P41" s="25"/>
-      <c r="Q41" s="25"/>
-      <c r="R41" s="25"/>
-      <c r="S41" s="25"/>
-      <c r="T41" s="25"/>
-      <c r="U41" s="25"/>
-      <c r="V41" s="25"/>
-      <c r="W41" s="25"/>
-      <c r="X41" s="25"/>
-      <c r="Y41" s="25"/>
-      <c r="Z41" s="25"/>
-      <c r="AA41" s="25"/>
-      <c r="AB41" s="26"/>
+      <c r="I41" s="45"/>
+      <c r="J41" s="23"/>
+      <c r="K41" s="23"/>
+      <c r="L41" s="23"/>
+      <c r="M41" s="23"/>
+      <c r="N41" s="23"/>
+      <c r="O41" s="23"/>
+      <c r="P41" s="23"/>
+      <c r="Q41" s="23"/>
+      <c r="R41" s="23"/>
+      <c r="S41" s="23"/>
+      <c r="T41" s="23"/>
+      <c r="U41" s="23"/>
+      <c r="V41" s="23"/>
+      <c r="W41" s="23"/>
+      <c r="X41" s="23"/>
+      <c r="Y41" s="23"/>
+      <c r="Z41" s="23"/>
+      <c r="AA41" s="23"/>
+      <c r="AB41" s="24"/>
       <c r="AC41" s="7"/>
       <c r="AD41" s="7"/>
       <c r="AE41" s="7"/>
       <c r="AF41" s="7"/>
       <c r="AG41" s="7"/>
-      <c r="AH41" s="27" t="s">
+      <c r="AH41" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="AI41" s="16"/>
-      <c r="AJ41" s="16"/>
-      <c r="AK41" s="16"/>
-      <c r="AL41" s="17"/>
+      <c r="AI41" s="14"/>
+      <c r="AJ41" s="14"/>
+      <c r="AK41" s="14"/>
+      <c r="AL41" s="15"/>
       <c r="AM41" s="7"/>
-      <c r="AN41" s="39"/>
-      <c r="AO41" s="40"/>
-      <c r="AP41" s="40"/>
-      <c r="AQ41" s="40"/>
-      <c r="AR41" s="40"/>
-      <c r="AS41" s="40"/>
-      <c r="AT41" s="40"/>
-      <c r="AU41" s="40"/>
-      <c r="AV41" s="40"/>
-      <c r="AW41" s="40"/>
-      <c r="AX41" s="40"/>
-      <c r="AY41" s="40"/>
-      <c r="AZ41" s="40"/>
-      <c r="BA41" s="40"/>
-      <c r="BB41" s="40"/>
-      <c r="BC41" s="40"/>
-      <c r="BD41" s="40"/>
-      <c r="BE41" s="40"/>
-      <c r="BF41" s="40"/>
-      <c r="BG41" s="41"/>
+      <c r="AN41" s="46"/>
+      <c r="AO41" s="47"/>
+      <c r="AP41" s="47"/>
+      <c r="AQ41" s="47"/>
+      <c r="AR41" s="47"/>
+      <c r="AS41" s="47"/>
+      <c r="AT41" s="47"/>
+      <c r="AU41" s="47"/>
+      <c r="AV41" s="47"/>
+      <c r="AW41" s="47"/>
+      <c r="AX41" s="47"/>
+      <c r="AY41" s="47"/>
+      <c r="AZ41" s="47"/>
+      <c r="BA41" s="47"/>
+      <c r="BB41" s="47"/>
+      <c r="BC41" s="47"/>
+      <c r="BD41" s="47"/>
+      <c r="BE41" s="47"/>
+      <c r="BF41" s="47"/>
+      <c r="BG41" s="48"/>
       <c r="BH41" s="7"/>
       <c r="BI41" s="7"/>
       <c r="BJ41" s="7"/>
@@ -4570,71 +4567,71 @@
     <row r="42" spans="1:63" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="7"/>
       <c r="B42" s="7"/>
-      <c r="C42" s="18" t="s">
+      <c r="C42" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="16"/>
-      <c r="E42" s="16"/>
-      <c r="F42" s="16"/>
-      <c r="G42" s="17"/>
+      <c r="D42" s="14"/>
+      <c r="E42" s="14"/>
+      <c r="F42" s="14"/>
+      <c r="G42" s="15"/>
       <c r="H42" s="7"/>
-      <c r="I42" s="24" t="s">
+      <c r="I42" s="22" t="s">
         <v>174</v>
       </c>
-      <c r="J42" s="25"/>
-      <c r="K42" s="25"/>
-      <c r="L42" s="25"/>
-      <c r="M42" s="25"/>
-      <c r="N42" s="25"/>
-      <c r="O42" s="25"/>
-      <c r="P42" s="25"/>
-      <c r="Q42" s="25"/>
-      <c r="R42" s="25"/>
-      <c r="S42" s="25"/>
-      <c r="T42" s="25"/>
-      <c r="U42" s="25"/>
-      <c r="V42" s="25"/>
-      <c r="W42" s="25"/>
-      <c r="X42" s="25"/>
-      <c r="Y42" s="25"/>
-      <c r="Z42" s="25"/>
-      <c r="AA42" s="25"/>
-      <c r="AB42" s="26"/>
+      <c r="J42" s="23"/>
+      <c r="K42" s="23"/>
+      <c r="L42" s="23"/>
+      <c r="M42" s="23"/>
+      <c r="N42" s="23"/>
+      <c r="O42" s="23"/>
+      <c r="P42" s="23"/>
+      <c r="Q42" s="23"/>
+      <c r="R42" s="23"/>
+      <c r="S42" s="23"/>
+      <c r="T42" s="23"/>
+      <c r="U42" s="23"/>
+      <c r="V42" s="23"/>
+      <c r="W42" s="23"/>
+      <c r="X42" s="23"/>
+      <c r="Y42" s="23"/>
+      <c r="Z42" s="23"/>
+      <c r="AA42" s="23"/>
+      <c r="AB42" s="24"/>
       <c r="AC42" s="7"/>
       <c r="AD42" s="7"/>
       <c r="AE42" s="7"/>
       <c r="AF42" s="7"/>
       <c r="AG42" s="7"/>
-      <c r="AH42" s="18" t="s">
+      <c r="AH42" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="AI42" s="16"/>
-      <c r="AJ42" s="16"/>
-      <c r="AK42" s="16"/>
-      <c r="AL42" s="17"/>
+      <c r="AI42" s="14"/>
+      <c r="AJ42" s="14"/>
+      <c r="AK42" s="14"/>
+      <c r="AL42" s="15"/>
       <c r="AM42" s="7"/>
-      <c r="AN42" s="24" t="s">
+      <c r="AN42" s="22" t="s">
         <v>168</v>
       </c>
-      <c r="AO42" s="25"/>
-      <c r="AP42" s="25"/>
-      <c r="AQ42" s="25"/>
-      <c r="AR42" s="25"/>
-      <c r="AS42" s="25"/>
-      <c r="AT42" s="25"/>
-      <c r="AU42" s="25"/>
-      <c r="AV42" s="25"/>
-      <c r="AW42" s="25"/>
-      <c r="AX42" s="25"/>
-      <c r="AY42" s="25"/>
-      <c r="AZ42" s="25"/>
-      <c r="BA42" s="25"/>
-      <c r="BB42" s="25"/>
-      <c r="BC42" s="25"/>
-      <c r="BD42" s="25"/>
-      <c r="BE42" s="25"/>
-      <c r="BF42" s="25"/>
-      <c r="BG42" s="26"/>
+      <c r="AO42" s="23"/>
+      <c r="AP42" s="23"/>
+      <c r="AQ42" s="23"/>
+      <c r="AR42" s="23"/>
+      <c r="AS42" s="23"/>
+      <c r="AT42" s="23"/>
+      <c r="AU42" s="23"/>
+      <c r="AV42" s="23"/>
+      <c r="AW42" s="23"/>
+      <c r="AX42" s="23"/>
+      <c r="AY42" s="23"/>
+      <c r="AZ42" s="23"/>
+      <c r="BA42" s="23"/>
+      <c r="BB42" s="23"/>
+      <c r="BC42" s="23"/>
+      <c r="BD42" s="23"/>
+      <c r="BE42" s="23"/>
+      <c r="BF42" s="23"/>
+      <c r="BG42" s="24"/>
       <c r="BH42" s="7"/>
       <c r="BI42" s="7"/>
       <c r="BJ42" s="7"/>
@@ -4642,71 +4639,71 @@
     <row r="43" spans="1:63" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="7"/>
       <c r="B43" s="7"/>
-      <c r="C43" s="18" t="s">
+      <c r="C43" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="16"/>
-      <c r="E43" s="16"/>
-      <c r="F43" s="16"/>
-      <c r="G43" s="17"/>
+      <c r="D43" s="14"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="14"/>
+      <c r="G43" s="15"/>
       <c r="H43" s="7"/>
-      <c r="I43" s="24" t="s">
+      <c r="I43" s="22" t="s">
         <v>173</v>
       </c>
-      <c r="J43" s="25"/>
-      <c r="K43" s="25"/>
-      <c r="L43" s="25"/>
-      <c r="M43" s="25"/>
-      <c r="N43" s="25"/>
-      <c r="O43" s="25"/>
-      <c r="P43" s="25"/>
-      <c r="Q43" s="25"/>
-      <c r="R43" s="25"/>
-      <c r="S43" s="25"/>
-      <c r="T43" s="25"/>
-      <c r="U43" s="25"/>
-      <c r="V43" s="25"/>
-      <c r="W43" s="25"/>
-      <c r="X43" s="25"/>
-      <c r="Y43" s="25"/>
-      <c r="Z43" s="25"/>
-      <c r="AA43" s="25"/>
-      <c r="AB43" s="26"/>
+      <c r="J43" s="23"/>
+      <c r="K43" s="23"/>
+      <c r="L43" s="23"/>
+      <c r="M43" s="23"/>
+      <c r="N43" s="23"/>
+      <c r="O43" s="23"/>
+      <c r="P43" s="23"/>
+      <c r="Q43" s="23"/>
+      <c r="R43" s="23"/>
+      <c r="S43" s="23"/>
+      <c r="T43" s="23"/>
+      <c r="U43" s="23"/>
+      <c r="V43" s="23"/>
+      <c r="W43" s="23"/>
+      <c r="X43" s="23"/>
+      <c r="Y43" s="23"/>
+      <c r="Z43" s="23"/>
+      <c r="AA43" s="23"/>
+      <c r="AB43" s="24"/>
       <c r="AC43" s="7"/>
       <c r="AD43" s="7"/>
       <c r="AE43" s="7"/>
       <c r="AF43" s="7"/>
       <c r="AG43" s="7"/>
-      <c r="AH43" s="18" t="s">
+      <c r="AH43" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="AI43" s="16"/>
-      <c r="AJ43" s="16"/>
-      <c r="AK43" s="16"/>
-      <c r="AL43" s="17"/>
+      <c r="AI43" s="14"/>
+      <c r="AJ43" s="14"/>
+      <c r="AK43" s="14"/>
+      <c r="AL43" s="15"/>
       <c r="AM43" s="7"/>
-      <c r="AN43" s="24" t="s">
+      <c r="AN43" s="22" t="s">
         <v>169</v>
       </c>
-      <c r="AO43" s="25"/>
-      <c r="AP43" s="25"/>
-      <c r="AQ43" s="25"/>
-      <c r="AR43" s="25"/>
-      <c r="AS43" s="25"/>
-      <c r="AT43" s="25"/>
-      <c r="AU43" s="25"/>
-      <c r="AV43" s="25"/>
-      <c r="AW43" s="25"/>
-      <c r="AX43" s="25"/>
-      <c r="AY43" s="25"/>
-      <c r="AZ43" s="25"/>
-      <c r="BA43" s="25"/>
-      <c r="BB43" s="25"/>
-      <c r="BC43" s="25"/>
-      <c r="BD43" s="25"/>
-      <c r="BE43" s="25"/>
-      <c r="BF43" s="25"/>
-      <c r="BG43" s="26"/>
+      <c r="AO43" s="23"/>
+      <c r="AP43" s="23"/>
+      <c r="AQ43" s="23"/>
+      <c r="AR43" s="23"/>
+      <c r="AS43" s="23"/>
+      <c r="AT43" s="23"/>
+      <c r="AU43" s="23"/>
+      <c r="AV43" s="23"/>
+      <c r="AW43" s="23"/>
+      <c r="AX43" s="23"/>
+      <c r="AY43" s="23"/>
+      <c r="AZ43" s="23"/>
+      <c r="BA43" s="23"/>
+      <c r="BB43" s="23"/>
+      <c r="BC43" s="23"/>
+      <c r="BD43" s="23"/>
+      <c r="BE43" s="23"/>
+      <c r="BF43" s="23"/>
+      <c r="BG43" s="24"/>
       <c r="BH43" s="7"/>
       <c r="BI43" s="7"/>
       <c r="BJ43" s="7"/>
@@ -4778,34 +4775,34 @@
     <row r="45" spans="1:63" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="7"/>
       <c r="B45" s="7"/>
-      <c r="C45" s="27" t="s">
+      <c r="C45" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="D45" s="16"/>
-      <c r="E45" s="16"/>
-      <c r="F45" s="16"/>
-      <c r="G45" s="17"/>
+      <c r="D45" s="14"/>
+      <c r="E45" s="14"/>
+      <c r="F45" s="14"/>
+      <c r="G45" s="15"/>
       <c r="H45" s="7"/>
-      <c r="I45" s="28"/>
-      <c r="J45" s="23"/>
-      <c r="K45" s="23"/>
-      <c r="L45" s="23"/>
-      <c r="M45" s="23"/>
-      <c r="N45" s="23"/>
-      <c r="O45" s="23"/>
-      <c r="P45" s="23"/>
-      <c r="Q45" s="23"/>
-      <c r="R45" s="23"/>
-      <c r="S45" s="23"/>
-      <c r="T45" s="23"/>
-      <c r="U45" s="23"/>
-      <c r="V45" s="23"/>
-      <c r="W45" s="23"/>
-      <c r="X45" s="23"/>
-      <c r="Y45" s="23"/>
-      <c r="Z45" s="23"/>
-      <c r="AA45" s="23"/>
-      <c r="AB45" s="29"/>
+      <c r="I45" s="26"/>
+      <c r="J45" s="21"/>
+      <c r="K45" s="21"/>
+      <c r="L45" s="21"/>
+      <c r="M45" s="21"/>
+      <c r="N45" s="21"/>
+      <c r="O45" s="21"/>
+      <c r="P45" s="21"/>
+      <c r="Q45" s="21"/>
+      <c r="R45" s="21"/>
+      <c r="S45" s="21"/>
+      <c r="T45" s="21"/>
+      <c r="U45" s="21"/>
+      <c r="V45" s="21"/>
+      <c r="W45" s="21"/>
+      <c r="X45" s="21"/>
+      <c r="Y45" s="21"/>
+      <c r="Z45" s="21"/>
+      <c r="AA45" s="21"/>
+      <c r="AB45" s="27"/>
       <c r="AC45" s="7"/>
       <c r="AD45" s="7"/>
       <c r="AE45" s="7"/>
@@ -4844,36 +4841,36 @@
     <row r="46" spans="1:63" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="7"/>
       <c r="B46" s="7"/>
-      <c r="C46" s="18" t="s">
+      <c r="C46" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="D46" s="16"/>
-      <c r="E46" s="16"/>
-      <c r="F46" s="16"/>
-      <c r="G46" s="17"/>
+      <c r="D46" s="14"/>
+      <c r="E46" s="14"/>
+      <c r="F46" s="14"/>
+      <c r="G46" s="15"/>
       <c r="H46" s="7"/>
-      <c r="I46" s="19" t="s">
+      <c r="I46" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="J46" s="20"/>
-      <c r="K46" s="20"/>
-      <c r="L46" s="20"/>
-      <c r="M46" s="20"/>
-      <c r="N46" s="20"/>
-      <c r="O46" s="20"/>
-      <c r="P46" s="20"/>
-      <c r="Q46" s="20"/>
-      <c r="R46" s="20"/>
-      <c r="S46" s="20"/>
-      <c r="T46" s="20"/>
-      <c r="U46" s="20"/>
-      <c r="V46" s="20"/>
-      <c r="W46" s="20"/>
-      <c r="X46" s="20"/>
-      <c r="Y46" s="20"/>
-      <c r="Z46" s="20"/>
-      <c r="AA46" s="20"/>
-      <c r="AB46" s="21"/>
+      <c r="J46" s="18"/>
+      <c r="K46" s="18"/>
+      <c r="L46" s="18"/>
+      <c r="M46" s="18"/>
+      <c r="N46" s="18"/>
+      <c r="O46" s="18"/>
+      <c r="P46" s="18"/>
+      <c r="Q46" s="18"/>
+      <c r="R46" s="18"/>
+      <c r="S46" s="18"/>
+      <c r="T46" s="18"/>
+      <c r="U46" s="18"/>
+      <c r="V46" s="18"/>
+      <c r="W46" s="18"/>
+      <c r="X46" s="18"/>
+      <c r="Y46" s="18"/>
+      <c r="Z46" s="18"/>
+      <c r="AA46" s="18"/>
+      <c r="AB46" s="19"/>
       <c r="AC46" s="7"/>
       <c r="AD46" s="7"/>
       <c r="AE46" s="7"/>
@@ -4912,36 +4909,36 @@
     <row r="47" spans="1:63" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="7"/>
       <c r="B47" s="7"/>
-      <c r="C47" s="18" t="s">
+      <c r="C47" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="D47" s="16"/>
-      <c r="E47" s="16"/>
-      <c r="F47" s="16"/>
-      <c r="G47" s="17"/>
+      <c r="D47" s="14"/>
+      <c r="E47" s="14"/>
+      <c r="F47" s="14"/>
+      <c r="G47" s="15"/>
       <c r="H47" s="7"/>
-      <c r="I47" s="19" t="s">
+      <c r="I47" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="J47" s="20"/>
-      <c r="K47" s="20"/>
-      <c r="L47" s="20"/>
-      <c r="M47" s="20"/>
-      <c r="N47" s="20"/>
-      <c r="O47" s="20"/>
-      <c r="P47" s="20"/>
-      <c r="Q47" s="20"/>
-      <c r="R47" s="20"/>
-      <c r="S47" s="20"/>
-      <c r="T47" s="20"/>
-      <c r="U47" s="20"/>
-      <c r="V47" s="20"/>
-      <c r="W47" s="20"/>
-      <c r="X47" s="20"/>
-      <c r="Y47" s="20"/>
-      <c r="Z47" s="20"/>
-      <c r="AA47" s="20"/>
-      <c r="AB47" s="21"/>
+      <c r="J47" s="18"/>
+      <c r="K47" s="18"/>
+      <c r="L47" s="18"/>
+      <c r="M47" s="18"/>
+      <c r="N47" s="18"/>
+      <c r="O47" s="18"/>
+      <c r="P47" s="18"/>
+      <c r="Q47" s="18"/>
+      <c r="R47" s="18"/>
+      <c r="S47" s="18"/>
+      <c r="T47" s="18"/>
+      <c r="U47" s="18"/>
+      <c r="V47" s="18"/>
+      <c r="W47" s="18"/>
+      <c r="X47" s="18"/>
+      <c r="Y47" s="18"/>
+      <c r="Z47" s="18"/>
+      <c r="AA47" s="18"/>
+      <c r="AB47" s="19"/>
       <c r="AC47" s="7"/>
       <c r="AD47" s="7"/>
       <c r="AE47" s="7"/>
@@ -5044,65 +5041,65 @@
     <row r="49" spans="1:62" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="7"/>
       <c r="B49" s="7"/>
-      <c r="C49" s="22" t="s">
+      <c r="C49" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="D49" s="23"/>
-      <c r="E49" s="23"/>
-      <c r="F49" s="23"/>
-      <c r="G49" s="23"/>
-      <c r="H49" s="23"/>
-      <c r="I49" s="23"/>
-      <c r="J49" s="23"/>
-      <c r="K49" s="23"/>
-      <c r="L49" s="23"/>
-      <c r="M49" s="23"/>
-      <c r="N49" s="23"/>
-      <c r="O49" s="23"/>
-      <c r="P49" s="23"/>
-      <c r="Q49" s="23"/>
-      <c r="R49" s="23"/>
-      <c r="S49" s="23"/>
-      <c r="T49" s="23"/>
-      <c r="U49" s="23"/>
-      <c r="V49" s="23"/>
-      <c r="W49" s="23"/>
-      <c r="X49" s="23"/>
-      <c r="Y49" s="23"/>
-      <c r="Z49" s="23"/>
-      <c r="AA49" s="23"/>
-      <c r="AB49" s="23"/>
-      <c r="AC49" s="23"/>
-      <c r="AD49" s="23"/>
-      <c r="AE49" s="23"/>
-      <c r="AF49" s="23"/>
-      <c r="AG49" s="23"/>
-      <c r="AH49" s="23"/>
-      <c r="AI49" s="23"/>
-      <c r="AJ49" s="23"/>
-      <c r="AK49" s="23"/>
-      <c r="AL49" s="23"/>
-      <c r="AM49" s="23"/>
-      <c r="AN49" s="23"/>
-      <c r="AO49" s="23"/>
-      <c r="AP49" s="23"/>
-      <c r="AQ49" s="23"/>
-      <c r="AR49" s="23"/>
-      <c r="AS49" s="23"/>
-      <c r="AT49" s="23"/>
-      <c r="AU49" s="23"/>
-      <c r="AV49" s="23"/>
-      <c r="AW49" s="23"/>
-      <c r="AX49" s="23"/>
-      <c r="AY49" s="23"/>
-      <c r="AZ49" s="23"/>
-      <c r="BA49" s="23"/>
-      <c r="BB49" s="23"/>
-      <c r="BC49" s="23"/>
-      <c r="BD49" s="23"/>
-      <c r="BE49" s="23"/>
-      <c r="BF49" s="23"/>
-      <c r="BG49" s="17"/>
+      <c r="D49" s="21"/>
+      <c r="E49" s="21"/>
+      <c r="F49" s="21"/>
+      <c r="G49" s="21"/>
+      <c r="H49" s="21"/>
+      <c r="I49" s="21"/>
+      <c r="J49" s="21"/>
+      <c r="K49" s="21"/>
+      <c r="L49" s="21"/>
+      <c r="M49" s="21"/>
+      <c r="N49" s="21"/>
+      <c r="O49" s="21"/>
+      <c r="P49" s="21"/>
+      <c r="Q49" s="21"/>
+      <c r="R49" s="21"/>
+      <c r="S49" s="21"/>
+      <c r="T49" s="21"/>
+      <c r="U49" s="21"/>
+      <c r="V49" s="21"/>
+      <c r="W49" s="21"/>
+      <c r="X49" s="21"/>
+      <c r="Y49" s="21"/>
+      <c r="Z49" s="21"/>
+      <c r="AA49" s="21"/>
+      <c r="AB49" s="21"/>
+      <c r="AC49" s="21"/>
+      <c r="AD49" s="21"/>
+      <c r="AE49" s="21"/>
+      <c r="AF49" s="21"/>
+      <c r="AG49" s="21"/>
+      <c r="AH49" s="21"/>
+      <c r="AI49" s="21"/>
+      <c r="AJ49" s="21"/>
+      <c r="AK49" s="21"/>
+      <c r="AL49" s="21"/>
+      <c r="AM49" s="21"/>
+      <c r="AN49" s="21"/>
+      <c r="AO49" s="21"/>
+      <c r="AP49" s="21"/>
+      <c r="AQ49" s="21"/>
+      <c r="AR49" s="21"/>
+      <c r="AS49" s="21"/>
+      <c r="AT49" s="21"/>
+      <c r="AU49" s="21"/>
+      <c r="AV49" s="21"/>
+      <c r="AW49" s="21"/>
+      <c r="AX49" s="21"/>
+      <c r="AY49" s="21"/>
+      <c r="AZ49" s="21"/>
+      <c r="BA49" s="21"/>
+      <c r="BB49" s="21"/>
+      <c r="BC49" s="21"/>
+      <c r="BD49" s="21"/>
+      <c r="BE49" s="21"/>
+      <c r="BF49" s="21"/>
+      <c r="BG49" s="15"/>
       <c r="BH49" s="7"/>
       <c r="BI49" s="7"/>
       <c r="BJ49" s="7"/>
@@ -5110,329 +5107,329 @@
     <row r="50" spans="1:62" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="7"/>
       <c r="B50" s="5"/>
-      <c r="C50" s="82" t="s">
+      <c r="C50" s="28" t="s">
         <v>182</v>
       </c>
-      <c r="D50" s="83"/>
-      <c r="E50" s="83"/>
-      <c r="F50" s="83"/>
-      <c r="G50" s="83"/>
-      <c r="H50" s="83"/>
-      <c r="I50" s="83"/>
-      <c r="J50" s="83"/>
-      <c r="K50" s="83"/>
-      <c r="L50" s="83"/>
-      <c r="M50" s="83"/>
-      <c r="N50" s="83"/>
-      <c r="O50" s="83"/>
-      <c r="P50" s="83"/>
-      <c r="Q50" s="83"/>
-      <c r="R50" s="83"/>
-      <c r="S50" s="83"/>
-      <c r="T50" s="83"/>
-      <c r="U50" s="83"/>
-      <c r="V50" s="83"/>
-      <c r="W50" s="83"/>
-      <c r="X50" s="83"/>
-      <c r="Y50" s="83"/>
-      <c r="Z50" s="83"/>
-      <c r="AA50" s="83"/>
-      <c r="AB50" s="83"/>
-      <c r="AC50" s="83"/>
-      <c r="AD50" s="83"/>
-      <c r="AE50" s="83"/>
-      <c r="AF50" s="83"/>
-      <c r="AG50" s="83"/>
-      <c r="AH50" s="83"/>
-      <c r="AI50" s="83"/>
-      <c r="AJ50" s="83"/>
-      <c r="AK50" s="83"/>
-      <c r="AL50" s="83"/>
-      <c r="AM50" s="83"/>
-      <c r="AN50" s="83"/>
-      <c r="AO50" s="83"/>
-      <c r="AP50" s="83"/>
-      <c r="AQ50" s="83"/>
-      <c r="AR50" s="83"/>
-      <c r="AS50" s="83"/>
-      <c r="AT50" s="83"/>
-      <c r="AU50" s="83"/>
-      <c r="AV50" s="83"/>
-      <c r="AW50" s="83"/>
-      <c r="AX50" s="83"/>
-      <c r="AY50" s="83"/>
-      <c r="AZ50" s="83"/>
-      <c r="BA50" s="83"/>
-      <c r="BB50" s="83"/>
-      <c r="BC50" s="83"/>
-      <c r="BD50" s="83"/>
-      <c r="BE50" s="83"/>
-      <c r="BF50" s="84"/>
-      <c r="BG50" s="12"/>
+      <c r="D50" s="29"/>
+      <c r="E50" s="29"/>
+      <c r="F50" s="29"/>
+      <c r="G50" s="29"/>
+      <c r="H50" s="29"/>
+      <c r="I50" s="29"/>
+      <c r="J50" s="29"/>
+      <c r="K50" s="29"/>
+      <c r="L50" s="29"/>
+      <c r="M50" s="29"/>
+      <c r="N50" s="29"/>
+      <c r="O50" s="29"/>
+      <c r="P50" s="29"/>
+      <c r="Q50" s="29"/>
+      <c r="R50" s="29"/>
+      <c r="S50" s="29"/>
+      <c r="T50" s="29"/>
+      <c r="U50" s="29"/>
+      <c r="V50" s="29"/>
+      <c r="W50" s="29"/>
+      <c r="X50" s="29"/>
+      <c r="Y50" s="29"/>
+      <c r="Z50" s="29"/>
+      <c r="AA50" s="29"/>
+      <c r="AB50" s="29"/>
+      <c r="AC50" s="29"/>
+      <c r="AD50" s="29"/>
+      <c r="AE50" s="29"/>
+      <c r="AF50" s="29"/>
+      <c r="AG50" s="29"/>
+      <c r="AH50" s="29"/>
+      <c r="AI50" s="29"/>
+      <c r="AJ50" s="29"/>
+      <c r="AK50" s="29"/>
+      <c r="AL50" s="29"/>
+      <c r="AM50" s="29"/>
+      <c r="AN50" s="29"/>
+      <c r="AO50" s="29"/>
+      <c r="AP50" s="29"/>
+      <c r="AQ50" s="29"/>
+      <c r="AR50" s="29"/>
+      <c r="AS50" s="29"/>
+      <c r="AT50" s="29"/>
+      <c r="AU50" s="29"/>
+      <c r="AV50" s="29"/>
+      <c r="AW50" s="29"/>
+      <c r="AX50" s="29"/>
+      <c r="AY50" s="29"/>
+      <c r="AZ50" s="29"/>
+      <c r="BA50" s="29"/>
+      <c r="BB50" s="29"/>
+      <c r="BC50" s="29"/>
+      <c r="BD50" s="29"/>
+      <c r="BE50" s="29"/>
+      <c r="BF50" s="30"/>
+      <c r="BG50" s="11"/>
       <c r="BH50" s="7"/>
       <c r="BI50" s="7"/>
       <c r="BJ50" s="7"/>
     </row>
-    <row r="51" spans="1:62" s="13" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:62" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="7"/>
       <c r="B51" s="5"/>
-      <c r="C51" s="85" t="s">
+      <c r="C51" s="31" t="s">
         <v>183</v>
       </c>
-      <c r="D51" s="81"/>
-      <c r="E51" s="81"/>
-      <c r="F51" s="81"/>
-      <c r="G51" s="81"/>
-      <c r="H51" s="81"/>
-      <c r="I51" s="81"/>
-      <c r="J51" s="81"/>
-      <c r="K51" s="81"/>
-      <c r="L51" s="81"/>
-      <c r="M51" s="81"/>
-      <c r="N51" s="81"/>
-      <c r="O51" s="81"/>
-      <c r="P51" s="81"/>
-      <c r="Q51" s="81"/>
-      <c r="R51" s="81"/>
-      <c r="S51" s="81"/>
-      <c r="T51" s="81"/>
-      <c r="U51" s="81"/>
-      <c r="V51" s="81"/>
-      <c r="W51" s="81"/>
-      <c r="X51" s="81"/>
-      <c r="Y51" s="81"/>
-      <c r="Z51" s="81"/>
-      <c r="AA51" s="81"/>
-      <c r="AB51" s="81"/>
-      <c r="AC51" s="81"/>
-      <c r="AD51" s="81"/>
-      <c r="AE51" s="81"/>
-      <c r="AF51" s="81"/>
-      <c r="AG51" s="81"/>
-      <c r="AH51" s="81"/>
-      <c r="AI51" s="81"/>
-      <c r="AJ51" s="81"/>
-      <c r="AK51" s="81"/>
-      <c r="AL51" s="81"/>
-      <c r="AM51" s="81"/>
-      <c r="AN51" s="81"/>
-      <c r="AO51" s="81"/>
-      <c r="AP51" s="81"/>
-      <c r="AQ51" s="81"/>
-      <c r="AR51" s="81"/>
-      <c r="AS51" s="81"/>
-      <c r="AT51" s="81"/>
-      <c r="AU51" s="81"/>
-      <c r="AV51" s="81"/>
-      <c r="AW51" s="81"/>
-      <c r="AX51" s="81"/>
-      <c r="AY51" s="81"/>
-      <c r="AZ51" s="81"/>
-      <c r="BA51" s="81"/>
-      <c r="BB51" s="81"/>
-      <c r="BC51" s="81"/>
-      <c r="BD51" s="81"/>
-      <c r="BE51" s="81"/>
-      <c r="BF51" s="86"/>
-      <c r="BG51" s="14"/>
+      <c r="D51" s="32"/>
+      <c r="E51" s="32"/>
+      <c r="F51" s="32"/>
+      <c r="G51" s="32"/>
+      <c r="H51" s="32"/>
+      <c r="I51" s="32"/>
+      <c r="J51" s="32"/>
+      <c r="K51" s="32"/>
+      <c r="L51" s="32"/>
+      <c r="M51" s="32"/>
+      <c r="N51" s="32"/>
+      <c r="O51" s="32"/>
+      <c r="P51" s="32"/>
+      <c r="Q51" s="32"/>
+      <c r="R51" s="32"/>
+      <c r="S51" s="32"/>
+      <c r="T51" s="32"/>
+      <c r="U51" s="32"/>
+      <c r="V51" s="32"/>
+      <c r="W51" s="32"/>
+      <c r="X51" s="32"/>
+      <c r="Y51" s="32"/>
+      <c r="Z51" s="32"/>
+      <c r="AA51" s="32"/>
+      <c r="AB51" s="32"/>
+      <c r="AC51" s="32"/>
+      <c r="AD51" s="32"/>
+      <c r="AE51" s="32"/>
+      <c r="AF51" s="32"/>
+      <c r="AG51" s="32"/>
+      <c r="AH51" s="32"/>
+      <c r="AI51" s="32"/>
+      <c r="AJ51" s="32"/>
+      <c r="AK51" s="32"/>
+      <c r="AL51" s="32"/>
+      <c r="AM51" s="32"/>
+      <c r="AN51" s="32"/>
+      <c r="AO51" s="32"/>
+      <c r="AP51" s="32"/>
+      <c r="AQ51" s="32"/>
+      <c r="AR51" s="32"/>
+      <c r="AS51" s="32"/>
+      <c r="AT51" s="32"/>
+      <c r="AU51" s="32"/>
+      <c r="AV51" s="32"/>
+      <c r="AW51" s="32"/>
+      <c r="AX51" s="32"/>
+      <c r="AY51" s="32"/>
+      <c r="AZ51" s="32"/>
+      <c r="BA51" s="32"/>
+      <c r="BB51" s="32"/>
+      <c r="BC51" s="32"/>
+      <c r="BD51" s="32"/>
+      <c r="BE51" s="32"/>
+      <c r="BF51" s="33"/>
+      <c r="BG51" s="12"/>
       <c r="BH51" s="7"/>
       <c r="BI51" s="7"/>
       <c r="BJ51" s="7"/>
     </row>
-    <row r="52" spans="1:62" s="13" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:62" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="7"/>
       <c r="B52" s="5"/>
-      <c r="C52" s="85" t="s">
+      <c r="C52" s="31" t="s">
         <v>184</v>
       </c>
-      <c r="D52" s="81"/>
-      <c r="E52" s="81"/>
-      <c r="F52" s="81"/>
-      <c r="G52" s="81"/>
-      <c r="H52" s="81"/>
-      <c r="I52" s="81"/>
-      <c r="J52" s="81"/>
-      <c r="K52" s="81"/>
-      <c r="L52" s="81"/>
-      <c r="M52" s="81"/>
-      <c r="N52" s="81"/>
-      <c r="O52" s="81"/>
-      <c r="P52" s="81"/>
-      <c r="Q52" s="81"/>
-      <c r="R52" s="81"/>
-      <c r="S52" s="81"/>
-      <c r="T52" s="81"/>
-      <c r="U52" s="81"/>
-      <c r="V52" s="81"/>
-      <c r="W52" s="81"/>
-      <c r="X52" s="81"/>
-      <c r="Y52" s="81"/>
-      <c r="Z52" s="81"/>
-      <c r="AA52" s="81"/>
-      <c r="AB52" s="81"/>
-      <c r="AC52" s="81"/>
-      <c r="AD52" s="81"/>
-      <c r="AE52" s="81"/>
-      <c r="AF52" s="81"/>
-      <c r="AG52" s="81"/>
-      <c r="AH52" s="81"/>
-      <c r="AI52" s="81"/>
-      <c r="AJ52" s="81"/>
-      <c r="AK52" s="81"/>
-      <c r="AL52" s="81"/>
-      <c r="AM52" s="81"/>
-      <c r="AN52" s="81"/>
-      <c r="AO52" s="81"/>
-      <c r="AP52" s="81"/>
-      <c r="AQ52" s="81"/>
-      <c r="AR52" s="81"/>
-      <c r="AS52" s="81"/>
-      <c r="AT52" s="81"/>
-      <c r="AU52" s="81"/>
-      <c r="AV52" s="81"/>
-      <c r="AW52" s="81"/>
-      <c r="AX52" s="81"/>
-      <c r="AY52" s="81"/>
-      <c r="AZ52" s="81"/>
-      <c r="BA52" s="81"/>
-      <c r="BB52" s="81"/>
-      <c r="BC52" s="81"/>
-      <c r="BD52" s="81"/>
-      <c r="BE52" s="81"/>
-      <c r="BF52" s="86"/>
-      <c r="BG52" s="14"/>
+      <c r="D52" s="32"/>
+      <c r="E52" s="32"/>
+      <c r="F52" s="32"/>
+      <c r="G52" s="32"/>
+      <c r="H52" s="32"/>
+      <c r="I52" s="32"/>
+      <c r="J52" s="32"/>
+      <c r="K52" s="32"/>
+      <c r="L52" s="32"/>
+      <c r="M52" s="32"/>
+      <c r="N52" s="32"/>
+      <c r="O52" s="32"/>
+      <c r="P52" s="32"/>
+      <c r="Q52" s="32"/>
+      <c r="R52" s="32"/>
+      <c r="S52" s="32"/>
+      <c r="T52" s="32"/>
+      <c r="U52" s="32"/>
+      <c r="V52" s="32"/>
+      <c r="W52" s="32"/>
+      <c r="X52" s="32"/>
+      <c r="Y52" s="32"/>
+      <c r="Z52" s="32"/>
+      <c r="AA52" s="32"/>
+      <c r="AB52" s="32"/>
+      <c r="AC52" s="32"/>
+      <c r="AD52" s="32"/>
+      <c r="AE52" s="32"/>
+      <c r="AF52" s="32"/>
+      <c r="AG52" s="32"/>
+      <c r="AH52" s="32"/>
+      <c r="AI52" s="32"/>
+      <c r="AJ52" s="32"/>
+      <c r="AK52" s="32"/>
+      <c r="AL52" s="32"/>
+      <c r="AM52" s="32"/>
+      <c r="AN52" s="32"/>
+      <c r="AO52" s="32"/>
+      <c r="AP52" s="32"/>
+      <c r="AQ52" s="32"/>
+      <c r="AR52" s="32"/>
+      <c r="AS52" s="32"/>
+      <c r="AT52" s="32"/>
+      <c r="AU52" s="32"/>
+      <c r="AV52" s="32"/>
+      <c r="AW52" s="32"/>
+      <c r="AX52" s="32"/>
+      <c r="AY52" s="32"/>
+      <c r="AZ52" s="32"/>
+      <c r="BA52" s="32"/>
+      <c r="BB52" s="32"/>
+      <c r="BC52" s="32"/>
+      <c r="BD52" s="32"/>
+      <c r="BE52" s="32"/>
+      <c r="BF52" s="33"/>
+      <c r="BG52" s="12"/>
       <c r="BH52" s="7"/>
       <c r="BI52" s="7"/>
       <c r="BJ52" s="7"/>
     </row>
-    <row r="53" spans="1:62" s="13" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:62" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="7"/>
       <c r="B53" s="5"/>
-      <c r="C53" s="85" t="s">
+      <c r="C53" s="31" t="s">
         <v>185</v>
       </c>
-      <c r="D53" s="81"/>
-      <c r="E53" s="81"/>
-      <c r="F53" s="81"/>
-      <c r="G53" s="81"/>
-      <c r="H53" s="81"/>
-      <c r="I53" s="81"/>
-      <c r="J53" s="81"/>
-      <c r="K53" s="81"/>
-      <c r="L53" s="81"/>
-      <c r="M53" s="81"/>
-      <c r="N53" s="81"/>
-      <c r="O53" s="81"/>
-      <c r="P53" s="81"/>
-      <c r="Q53" s="81"/>
-      <c r="R53" s="81"/>
-      <c r="S53" s="81"/>
-      <c r="T53" s="81"/>
-      <c r="U53" s="81"/>
-      <c r="V53" s="81"/>
-      <c r="W53" s="81"/>
-      <c r="X53" s="81"/>
-      <c r="Y53" s="81"/>
-      <c r="Z53" s="81"/>
-      <c r="AA53" s="81"/>
-      <c r="AB53" s="81"/>
-      <c r="AC53" s="81"/>
-      <c r="AD53" s="81"/>
-      <c r="AE53" s="81"/>
-      <c r="AF53" s="81"/>
-      <c r="AG53" s="81"/>
-      <c r="AH53" s="81"/>
-      <c r="AI53" s="81"/>
-      <c r="AJ53" s="81"/>
-      <c r="AK53" s="81"/>
-      <c r="AL53" s="81"/>
-      <c r="AM53" s="81"/>
-      <c r="AN53" s="81"/>
-      <c r="AO53" s="81"/>
-      <c r="AP53" s="81"/>
-      <c r="AQ53" s="81"/>
-      <c r="AR53" s="81"/>
-      <c r="AS53" s="81"/>
-      <c r="AT53" s="81"/>
-      <c r="AU53" s="81"/>
-      <c r="AV53" s="81"/>
-      <c r="AW53" s="81"/>
-      <c r="AX53" s="81"/>
-      <c r="AY53" s="81"/>
-      <c r="AZ53" s="81"/>
-      <c r="BA53" s="81"/>
-      <c r="BB53" s="81"/>
-      <c r="BC53" s="81"/>
-      <c r="BD53" s="81"/>
-      <c r="BE53" s="81"/>
-      <c r="BF53" s="86"/>
-      <c r="BG53" s="14"/>
+      <c r="D53" s="32"/>
+      <c r="E53" s="32"/>
+      <c r="F53" s="32"/>
+      <c r="G53" s="32"/>
+      <c r="H53" s="32"/>
+      <c r="I53" s="32"/>
+      <c r="J53" s="32"/>
+      <c r="K53" s="32"/>
+      <c r="L53" s="32"/>
+      <c r="M53" s="32"/>
+      <c r="N53" s="32"/>
+      <c r="O53" s="32"/>
+      <c r="P53" s="32"/>
+      <c r="Q53" s="32"/>
+      <c r="R53" s="32"/>
+      <c r="S53" s="32"/>
+      <c r="T53" s="32"/>
+      <c r="U53" s="32"/>
+      <c r="V53" s="32"/>
+      <c r="W53" s="32"/>
+      <c r="X53" s="32"/>
+      <c r="Y53" s="32"/>
+      <c r="Z53" s="32"/>
+      <c r="AA53" s="32"/>
+      <c r="AB53" s="32"/>
+      <c r="AC53" s="32"/>
+      <c r="AD53" s="32"/>
+      <c r="AE53" s="32"/>
+      <c r="AF53" s="32"/>
+      <c r="AG53" s="32"/>
+      <c r="AH53" s="32"/>
+      <c r="AI53" s="32"/>
+      <c r="AJ53" s="32"/>
+      <c r="AK53" s="32"/>
+      <c r="AL53" s="32"/>
+      <c r="AM53" s="32"/>
+      <c r="AN53" s="32"/>
+      <c r="AO53" s="32"/>
+      <c r="AP53" s="32"/>
+      <c r="AQ53" s="32"/>
+      <c r="AR53" s="32"/>
+      <c r="AS53" s="32"/>
+      <c r="AT53" s="32"/>
+      <c r="AU53" s="32"/>
+      <c r="AV53" s="32"/>
+      <c r="AW53" s="32"/>
+      <c r="AX53" s="32"/>
+      <c r="AY53" s="32"/>
+      <c r="AZ53" s="32"/>
+      <c r="BA53" s="32"/>
+      <c r="BB53" s="32"/>
+      <c r="BC53" s="32"/>
+      <c r="BD53" s="32"/>
+      <c r="BE53" s="32"/>
+      <c r="BF53" s="33"/>
+      <c r="BG53" s="12"/>
       <c r="BH53" s="7"/>
       <c r="BI53" s="7"/>
       <c r="BJ53" s="7"/>
     </row>
-    <row r="54" spans="1:62" s="13" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:62" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="7"/>
       <c r="B54" s="5"/>
-      <c r="C54" s="87" t="s">
+      <c r="C54" s="34" t="s">
         <v>186</v>
       </c>
-      <c r="D54" s="88"/>
-      <c r="E54" s="88"/>
-      <c r="F54" s="88"/>
-      <c r="G54" s="88"/>
-      <c r="H54" s="88"/>
-      <c r="I54" s="88"/>
-      <c r="J54" s="88"/>
-      <c r="K54" s="88"/>
-      <c r="L54" s="88"/>
-      <c r="M54" s="88"/>
-      <c r="N54" s="88"/>
-      <c r="O54" s="88"/>
-      <c r="P54" s="88"/>
-      <c r="Q54" s="88"/>
-      <c r="R54" s="88"/>
-      <c r="S54" s="88"/>
-      <c r="T54" s="88"/>
-      <c r="U54" s="88"/>
-      <c r="V54" s="88"/>
-      <c r="W54" s="88"/>
-      <c r="X54" s="88"/>
-      <c r="Y54" s="88"/>
-      <c r="Z54" s="88"/>
-      <c r="AA54" s="88"/>
-      <c r="AB54" s="88"/>
-      <c r="AC54" s="88"/>
-      <c r="AD54" s="88"/>
-      <c r="AE54" s="88"/>
-      <c r="AF54" s="88"/>
-      <c r="AG54" s="88"/>
-      <c r="AH54" s="88"/>
-      <c r="AI54" s="88"/>
-      <c r="AJ54" s="88"/>
-      <c r="AK54" s="88"/>
-      <c r="AL54" s="88"/>
-      <c r="AM54" s="88"/>
-      <c r="AN54" s="88"/>
-      <c r="AO54" s="88"/>
-      <c r="AP54" s="88"/>
-      <c r="AQ54" s="88"/>
-      <c r="AR54" s="88"/>
-      <c r="AS54" s="88"/>
-      <c r="AT54" s="88"/>
-      <c r="AU54" s="88"/>
-      <c r="AV54" s="88"/>
-      <c r="AW54" s="88"/>
-      <c r="AX54" s="88"/>
-      <c r="AY54" s="88"/>
-      <c r="AZ54" s="88"/>
-      <c r="BA54" s="88"/>
-      <c r="BB54" s="88"/>
-      <c r="BC54" s="88"/>
-      <c r="BD54" s="88"/>
-      <c r="BE54" s="88"/>
-      <c r="BF54" s="89"/>
-      <c r="BG54" s="14"/>
+      <c r="D54" s="35"/>
+      <c r="E54" s="35"/>
+      <c r="F54" s="35"/>
+      <c r="G54" s="35"/>
+      <c r="H54" s="35"/>
+      <c r="I54" s="35"/>
+      <c r="J54" s="35"/>
+      <c r="K54" s="35"/>
+      <c r="L54" s="35"/>
+      <c r="M54" s="35"/>
+      <c r="N54" s="35"/>
+      <c r="O54" s="35"/>
+      <c r="P54" s="35"/>
+      <c r="Q54" s="35"/>
+      <c r="R54" s="35"/>
+      <c r="S54" s="35"/>
+      <c r="T54" s="35"/>
+      <c r="U54" s="35"/>
+      <c r="V54" s="35"/>
+      <c r="W54" s="35"/>
+      <c r="X54" s="35"/>
+      <c r="Y54" s="35"/>
+      <c r="Z54" s="35"/>
+      <c r="AA54" s="35"/>
+      <c r="AB54" s="35"/>
+      <c r="AC54" s="35"/>
+      <c r="AD54" s="35"/>
+      <c r="AE54" s="35"/>
+      <c r="AF54" s="35"/>
+      <c r="AG54" s="35"/>
+      <c r="AH54" s="35"/>
+      <c r="AI54" s="35"/>
+      <c r="AJ54" s="35"/>
+      <c r="AK54" s="35"/>
+      <c r="AL54" s="35"/>
+      <c r="AM54" s="35"/>
+      <c r="AN54" s="35"/>
+      <c r="AO54" s="35"/>
+      <c r="AP54" s="35"/>
+      <c r="AQ54" s="35"/>
+      <c r="AR54" s="35"/>
+      <c r="AS54" s="35"/>
+      <c r="AT54" s="35"/>
+      <c r="AU54" s="35"/>
+      <c r="AV54" s="35"/>
+      <c r="AW54" s="35"/>
+      <c r="AX54" s="35"/>
+      <c r="AY54" s="35"/>
+      <c r="AZ54" s="35"/>
+      <c r="BA54" s="35"/>
+      <c r="BB54" s="35"/>
+      <c r="BC54" s="35"/>
+      <c r="BD54" s="35"/>
+      <c r="BE54" s="35"/>
+      <c r="BF54" s="36"/>
+      <c r="BG54" s="12"/>
       <c r="BH54" s="7"/>
       <c r="BI54" s="7"/>
       <c r="BJ54" s="7"/>
@@ -5504,65 +5501,65 @@
     <row r="56" spans="1:62" ht="179.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="7"/>
       <c r="B56" s="7"/>
-      <c r="C56" s="15" t="s">
+      <c r="C56" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D56" s="16"/>
-      <c r="E56" s="16"/>
-      <c r="F56" s="16"/>
-      <c r="G56" s="16"/>
-      <c r="H56" s="16"/>
-      <c r="I56" s="16"/>
-      <c r="J56" s="16"/>
-      <c r="K56" s="16"/>
-      <c r="L56" s="16"/>
-      <c r="M56" s="16"/>
-      <c r="N56" s="16"/>
-      <c r="O56" s="16"/>
-      <c r="P56" s="16"/>
-      <c r="Q56" s="16"/>
-      <c r="R56" s="16"/>
-      <c r="S56" s="16"/>
-      <c r="T56" s="16"/>
-      <c r="U56" s="16"/>
-      <c r="V56" s="16"/>
-      <c r="W56" s="16"/>
-      <c r="X56" s="16"/>
-      <c r="Y56" s="16"/>
-      <c r="Z56" s="16"/>
-      <c r="AA56" s="16"/>
-      <c r="AB56" s="16"/>
-      <c r="AC56" s="16"/>
-      <c r="AD56" s="16"/>
-      <c r="AE56" s="16"/>
-      <c r="AF56" s="16"/>
-      <c r="AG56" s="16"/>
-      <c r="AH56" s="16"/>
-      <c r="AI56" s="16"/>
-      <c r="AJ56" s="16"/>
-      <c r="AK56" s="16"/>
-      <c r="AL56" s="16"/>
-      <c r="AM56" s="16"/>
-      <c r="AN56" s="16"/>
-      <c r="AO56" s="16"/>
-      <c r="AP56" s="16"/>
-      <c r="AQ56" s="16"/>
-      <c r="AR56" s="16"/>
-      <c r="AS56" s="16"/>
-      <c r="AT56" s="16"/>
-      <c r="AU56" s="16"/>
-      <c r="AV56" s="16"/>
-      <c r="AW56" s="16"/>
-      <c r="AX56" s="16"/>
-      <c r="AY56" s="16"/>
-      <c r="AZ56" s="16"/>
-      <c r="BA56" s="16"/>
-      <c r="BB56" s="16"/>
-      <c r="BC56" s="16"/>
-      <c r="BD56" s="16"/>
-      <c r="BE56" s="16"/>
-      <c r="BF56" s="16"/>
-      <c r="BG56" s="17"/>
+      <c r="D56" s="14"/>
+      <c r="E56" s="14"/>
+      <c r="F56" s="14"/>
+      <c r="G56" s="14"/>
+      <c r="H56" s="14"/>
+      <c r="I56" s="14"/>
+      <c r="J56" s="14"/>
+      <c r="K56" s="14"/>
+      <c r="L56" s="14"/>
+      <c r="M56" s="14"/>
+      <c r="N56" s="14"/>
+      <c r="O56" s="14"/>
+      <c r="P56" s="14"/>
+      <c r="Q56" s="14"/>
+      <c r="R56" s="14"/>
+      <c r="S56" s="14"/>
+      <c r="T56" s="14"/>
+      <c r="U56" s="14"/>
+      <c r="V56" s="14"/>
+      <c r="W56" s="14"/>
+      <c r="X56" s="14"/>
+      <c r="Y56" s="14"/>
+      <c r="Z56" s="14"/>
+      <c r="AA56" s="14"/>
+      <c r="AB56" s="14"/>
+      <c r="AC56" s="14"/>
+      <c r="AD56" s="14"/>
+      <c r="AE56" s="14"/>
+      <c r="AF56" s="14"/>
+      <c r="AG56" s="14"/>
+      <c r="AH56" s="14"/>
+      <c r="AI56" s="14"/>
+      <c r="AJ56" s="14"/>
+      <c r="AK56" s="14"/>
+      <c r="AL56" s="14"/>
+      <c r="AM56" s="14"/>
+      <c r="AN56" s="14"/>
+      <c r="AO56" s="14"/>
+      <c r="AP56" s="14"/>
+      <c r="AQ56" s="14"/>
+      <c r="AR56" s="14"/>
+      <c r="AS56" s="14"/>
+      <c r="AT56" s="14"/>
+      <c r="AU56" s="14"/>
+      <c r="AV56" s="14"/>
+      <c r="AW56" s="14"/>
+      <c r="AX56" s="14"/>
+      <c r="AY56" s="14"/>
+      <c r="AZ56" s="14"/>
+      <c r="BA56" s="14"/>
+      <c r="BB56" s="14"/>
+      <c r="BC56" s="14"/>
+      <c r="BD56" s="14"/>
+      <c r="BE56" s="14"/>
+      <c r="BF56" s="14"/>
+      <c r="BG56" s="15"/>
       <c r="BH56" s="7"/>
       <c r="BI56" s="7"/>
       <c r="BJ56" s="7"/>
@@ -66260,7 +66257,7 @@
     <mergeCell ref="C54:BF54"/>
   </mergeCells>
   <phoneticPr fontId="21" type="noConversion"/>
-  <conditionalFormatting sqref="BB39:BG39 BA26:BG37">
+  <conditionalFormatting sqref="BA26:BG37 BB39:BG39">
     <cfRule type="cellIs" dxfId="0" priority="8" operator="equal">
       <formula>0</formula>
     </cfRule>
@@ -66278,15 +66275,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100320AD32CA7D13C428F41506FB3B20FF9" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b1d4bcfeb6e57ef0f2c10847fd5fef86">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="901b0b58-9b0d-464f-9b46-6f4fc1b5bc1d" xmlns:ns4="44f3a8c7-9d91-4716-869b-a19c9534456e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8f2ec99d776ccc0407f4ec14f6803c3c" ns3:_="" ns4:_="">
     <xsd:import namespace="901b0b58-9b0d-464f-9b46-6f4fc1b5bc1d"/>
@@ -66503,21 +66491,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{216E58EA-66F7-419D-8772-5475D997B9F8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5EB5BAF7-0045-4CF6-9D92-6077E0C2BDCD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -66536,11 +66525,25 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C14C9907-F5E5-43A0-B6D9-0F78D35F06B5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{216E58EA-66F7-419D-8772-5475D997B9F8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{25a1e02b-2518-4cba-a1bf-7c39639f6abf}" enabled="1" method="Privileged" siteId="{a3c00101-0c80-45a9-9ed3-af5cf05dda19}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>